--- a/risk/Risk_Analysis_T3_100yrs_Future_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_100yrs_Future_Breaches.xlsx
@@ -25,18 +25,12 @@
     <sheet name="Kashmore_Exp" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="Kashmore_Vul" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="Kashmore_Dmg" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Naushahro Feroze_Exp" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Naushahro Feroze_Vul" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Naushahro Feroze_Dmg" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Qambar Shahdadkot_Exp" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Qambar Shahdadkot_Vul" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Qambar Shahdadkot_Dmg" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Shaheed Benazirabad_Exp" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Shaheed Benazirabad_Vul" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Shaheed Benazirabad_Dmg" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Shikarpur_Exp" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="Shikarpur_Vul" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="Shikarpur_Dmg" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Qambar Shahdadkot_Exp" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Qambar Shahdadkot_Vul" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Qambar Shahdadkot_Dmg" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Shikarpur_Exp" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Shikarpur_Vul" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Shikarpur_Dmg" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9772,7 +9766,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Exp</t>
+          <t>Region: Qambar Shahdadkot | Mode: Exp</t>
         </is>
       </c>
     </row>
@@ -9843,37 +9837,37 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>2047.95</v>
+        <v>28674.99</v>
       </c>
       <c r="C4" t="n">
-        <v>590688</v>
+        <v>5125680</v>
       </c>
       <c r="D4" t="n">
-        <v>464112</v>
+        <v>4027320</v>
       </c>
       <c r="E4" t="n">
-        <v>149400</v>
+        <v>1569600</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>6660</v>
+        <v>83520</v>
       </c>
       <c r="H4" t="n">
-        <v>300</v>
+        <v>7110</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>20730</v>
+        <v>172020</v>
       </c>
     </row>
     <row r="5">
@@ -9881,37 +9875,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3696.84</v>
+        <v>24021.63</v>
       </c>
       <c r="C5" t="n">
-        <v>667800</v>
+        <v>4244184</v>
       </c>
       <c r="D5" t="n">
-        <v>524700</v>
+        <v>3334716</v>
       </c>
       <c r="E5" t="n">
-        <v>133200</v>
+        <v>1050300</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="G5" t="n">
-        <v>8520</v>
+        <v>67140</v>
       </c>
       <c r="H5" t="n">
-        <v>30</v>
+        <v>6210</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>20580</v>
+        <v>162150</v>
       </c>
     </row>
     <row r="6">
@@ -9919,37 +9913,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>4051.08</v>
+        <v>24413.94</v>
       </c>
       <c r="C6" t="n">
-        <v>483840</v>
+        <v>3823848</v>
       </c>
       <c r="D6" t="n">
-        <v>380160</v>
+        <v>3004452</v>
       </c>
       <c r="E6" t="n">
-        <v>75600</v>
+        <v>861300</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G6" t="n">
-        <v>8130</v>
+        <v>68010</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>7710</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>22740</v>
+        <v>156240</v>
       </c>
     </row>
     <row r="7">
@@ -9957,37 +9951,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>3034.71</v>
+        <v>33603.3</v>
       </c>
       <c r="C7" t="n">
-        <v>271656</v>
+        <v>4560696</v>
       </c>
       <c r="D7" t="n">
-        <v>213444</v>
+        <v>3583404</v>
       </c>
       <c r="E7" t="n">
-        <v>41400</v>
+        <v>811800</v>
       </c>
       <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>88650</v>
+      </c>
+      <c r="H7" t="n">
+        <v>11820</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
         <v>1</v>
       </c>
-      <c r="G7" t="n">
-        <v>5460</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>13470</v>
+        <v>202350</v>
       </c>
     </row>
     <row r="8">
@@ -9995,37 +9989,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>1597.59</v>
+        <v>27767.61</v>
       </c>
       <c r="C8" t="n">
-        <v>90720</v>
+        <v>2317896</v>
       </c>
       <c r="D8" t="n">
-        <v>71280</v>
+        <v>1821204</v>
       </c>
       <c r="E8" t="n">
-        <v>19800</v>
+        <v>248400</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2370</v>
+        <v>58320</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2610</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>4800</v>
+        <v>127200</v>
       </c>
     </row>
     <row r="9">
@@ -10033,37 +10027,37 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>758.97</v>
+        <v>23434.47</v>
       </c>
       <c r="C9" t="n">
-        <v>38304</v>
+        <v>1693944</v>
       </c>
       <c r="D9" t="n">
-        <v>30096</v>
+        <v>1330956</v>
       </c>
       <c r="E9" t="n">
-        <v>9000</v>
+        <v>142200</v>
       </c>
       <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>34110</v>
+      </c>
+      <c r="H9" t="n">
+        <v>270</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="G9" t="n">
-        <v>1020</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>960</v>
+        <v>74580</v>
       </c>
     </row>
     <row r="10">
@@ -10071,22 +10065,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>430.65</v>
+        <v>13030.65</v>
       </c>
       <c r="C10" t="n">
-        <v>5040</v>
+        <v>872928</v>
       </c>
       <c r="D10" t="n">
-        <v>3960</v>
+        <v>685872</v>
       </c>
       <c r="E10" t="n">
-        <v>1800</v>
+        <v>48600</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>630</v>
+        <v>23010</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -10095,13 +10089,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>630</v>
+        <v>39240</v>
       </c>
     </row>
     <row r="11">
@@ -10109,25 +10103,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>276.39</v>
+        <v>1572.3</v>
       </c>
       <c r="C11" t="n">
-        <v>1512</v>
+        <v>111384</v>
       </c>
       <c r="D11" t="n">
-        <v>1188</v>
+        <v>87516</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>180</v>
+        <v>2640</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -10139,7 +10133,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>210</v>
+        <v>10200</v>
       </c>
     </row>
     <row r="12">
@@ -10147,22 +10141,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>162.54</v>
+        <v>344.79</v>
       </c>
       <c r="C12" t="n">
-        <v>2016</v>
+        <v>44856</v>
       </c>
       <c r="D12" t="n">
-        <v>1584</v>
+        <v>35244</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>120</v>
+        <v>1230</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -10177,7 +10171,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>240</v>
+        <v>4740</v>
       </c>
     </row>
     <row r="13">
@@ -10185,13 +10179,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>133.92</v>
+        <v>181.17</v>
       </c>
       <c r="C13" t="n">
-        <v>504</v>
+        <v>10080</v>
       </c>
       <c r="D13" t="n">
-        <v>396</v>
+        <v>7920</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -10200,7 +10194,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>120</v>
+        <v>270</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -10215,7 +10209,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>150</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="14">
@@ -10223,22 +10217,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>127.53</v>
+        <v>110.88</v>
       </c>
       <c r="C14" t="n">
-        <v>504</v>
+        <v>2016</v>
       </c>
       <c r="D14" t="n">
-        <v>396</v>
+        <v>1584</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>450</v>
+        <v>270</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -10253,7 +10247,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>540</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="15">
@@ -10261,13 +10255,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>6.3</v>
+        <v>11.97</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>3528</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>2772</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -10276,7 +10270,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -10291,7 +10285,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
     </row>
     <row r="16">
@@ -10299,13 +10293,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>1.35</v>
+        <v>17.91</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -10314,7 +10308,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -10329,7 +10323,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
     </row>
     <row r="17">
@@ -10337,13 +10331,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>1.26</v>
+        <v>10.8</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -10352,7 +10346,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -10367,7 +10361,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
     </row>
     <row r="18">
@@ -10375,13 +10369,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>1.44</v>
+        <v>5.22</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -10390,7 +10384,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -10405,7 +10399,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
     </row>
     <row r="19">
@@ -10413,7 +10407,7 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>0.18</v>
+        <v>1.62</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -10428,7 +10422,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -10443,7 +10437,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="20">
@@ -10451,13 +10445,13 @@
         <v>800</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>4536</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>3564</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -10466,7 +10460,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -10492,10 +10486,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -10530,10 +10524,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -10568,10 +10562,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -10606,10 +10600,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>2520</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1980</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -11636,7 +11630,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Vul</t>
+          <t>Region: Qambar Shahdadkot | Mode: Vul</t>
         </is>
       </c>
     </row>
@@ -11745,37 +11739,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>1663.58</v>
+        <v>10809.73</v>
       </c>
       <c r="C5" t="n">
-        <v>367290</v>
+        <v>2334301.2</v>
       </c>
       <c r="D5" t="n">
-        <v>173675.7</v>
+        <v>1103791</v>
       </c>
       <c r="E5" t="n">
-        <v>14691.96</v>
+        <v>115848.09</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06</v>
+        <v>0.4</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>10.8</v>
+        <v>2235.6</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>4321.8</v>
+        <v>34051.5</v>
       </c>
     </row>
     <row r="6">
@@ -11783,37 +11777,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>3240.86</v>
+        <v>19531.15</v>
       </c>
       <c r="C6" t="n">
-        <v>435456</v>
+        <v>3441463.2</v>
       </c>
       <c r="D6" t="n">
-        <v>192741.12</v>
+        <v>1523257.16</v>
       </c>
       <c r="E6" t="n">
-        <v>12776.4</v>
+        <v>145559.7</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="G6" t="n">
-        <v>406.5</v>
+        <v>3400.5</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>4394.7</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>8413.799999999999</v>
+        <v>57808.8</v>
       </c>
     </row>
     <row r="7">
@@ -11821,37 +11815,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>2882.97</v>
+        <v>31923.14</v>
       </c>
       <c r="C7" t="n">
-        <v>271656</v>
+        <v>4560696</v>
       </c>
       <c r="D7" t="n">
-        <v>136177.27</v>
+        <v>2286211.75</v>
       </c>
       <c r="E7" t="n">
-        <v>8805.780000000001</v>
+        <v>172669.86</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="G7" t="n">
-        <v>819</v>
+        <v>13297.5</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>8628.6</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>8082</v>
+        <v>121410</v>
       </c>
     </row>
     <row r="8">
@@ -11859,37 +11853,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>1597.59</v>
+        <v>27767.61</v>
       </c>
       <c r="C8" t="n">
-        <v>90720</v>
+        <v>2317896</v>
       </c>
       <c r="D8" t="n">
-        <v>52462.08</v>
+        <v>1340406.14</v>
       </c>
       <c r="E8" t="n">
-        <v>4856.94</v>
+        <v>60932.52</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1540.5</v>
+        <v>37908</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2218.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3408</v>
+        <v>90312</v>
       </c>
     </row>
     <row r="9">
@@ -11897,37 +11891,37 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>758.97</v>
+        <v>23434.47</v>
       </c>
       <c r="C9" t="n">
-        <v>38304</v>
+        <v>1693944</v>
       </c>
       <c r="D9" t="n">
-        <v>24167.09</v>
+        <v>1068757.67</v>
       </c>
       <c r="E9" t="n">
-        <v>2409.3</v>
+        <v>38066.94</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>867</v>
+        <v>28993.5</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>777.6</v>
+        <v>60409.8</v>
       </c>
     </row>
     <row r="10">
@@ -11935,22 +11929,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>430.65</v>
+        <v>13030.65</v>
       </c>
       <c r="C10" t="n">
-        <v>5040</v>
+        <v>872928</v>
       </c>
       <c r="D10" t="n">
-        <v>3445.2</v>
+        <v>596708.64</v>
       </c>
       <c r="E10" t="n">
-        <v>522</v>
+        <v>14094</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>630</v>
+        <v>23010</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -11959,13 +11953,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>560.7</v>
+        <v>34923.6</v>
       </c>
     </row>
     <row r="11">
@@ -11973,25 +11967,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>276.39</v>
+        <v>1572.3</v>
       </c>
       <c r="C11" t="n">
-        <v>1512</v>
+        <v>111384</v>
       </c>
       <c r="D11" t="n">
-        <v>1067.42</v>
+        <v>78633.13</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1475.28</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>180</v>
+        <v>2640</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -12003,7 +11997,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>210</v>
+        <v>10200</v>
       </c>
     </row>
     <row r="12">
@@ -12011,22 +12005,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>162.54</v>
+        <v>344.79</v>
       </c>
       <c r="C12" t="n">
-        <v>2016</v>
+        <v>44856</v>
       </c>
       <c r="D12" t="n">
-        <v>1468.37</v>
+        <v>32671.19</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>860.4</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>120</v>
+        <v>1230</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12041,7 +12035,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>240</v>
+        <v>4740</v>
       </c>
     </row>
     <row r="13">
@@ -12049,13 +12043,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>133.92</v>
+        <v>181.17</v>
       </c>
       <c r="C13" t="n">
-        <v>504</v>
+        <v>10080</v>
       </c>
       <c r="D13" t="n">
-        <v>376</v>
+        <v>7520.04</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12064,7 +12058,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>120</v>
+        <v>270</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -12079,7 +12073,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>150</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="14">
@@ -12087,22 +12081,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>127.53</v>
+        <v>110.88</v>
       </c>
       <c r="C14" t="n">
-        <v>504</v>
+        <v>2016</v>
       </c>
       <c r="D14" t="n">
-        <v>384.91</v>
+        <v>1539.65</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>512.37</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>450</v>
+        <v>270</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -12117,7 +12111,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>540</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="15">
@@ -12125,13 +12119,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>6.3</v>
+        <v>11.97</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>3528</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>2733.19</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -12140,7 +12134,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -12155,7 +12149,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
     </row>
     <row r="16">
@@ -12163,13 +12157,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>1.35</v>
+        <v>17.91</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -12178,7 +12172,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -12193,7 +12187,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
     </row>
     <row r="17">
@@ -12201,13 +12195,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>1.26</v>
+        <v>10.8</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -12216,7 +12210,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -12231,7 +12225,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
     </row>
     <row r="18">
@@ -12239,13 +12233,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>1.44</v>
+        <v>5.22</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -12254,7 +12248,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -12269,7 +12263,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
     </row>
     <row r="19">
@@ -12277,7 +12271,7 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>0.18</v>
+        <v>1.62</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -12292,7 +12286,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -12307,7 +12301,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="20">
@@ -12315,13 +12309,13 @@
         <v>800</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>4536</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>3564</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -12330,7 +12324,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -12356,10 +12350,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -12394,10 +12388,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -12432,10 +12426,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -12470,10 +12464,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>2520</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1980</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -12568,7 +12562,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Dmg</t>
+          <t>Region: Qambar Shahdadkot | Mode: Dmg</t>
         </is>
       </c>
     </row>
@@ -12677,37 +12671,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3659871.6</v>
+        <v>23781413.7</v>
       </c>
       <c r="C5" t="n">
-        <v>20200950</v>
+        <v>128386566</v>
       </c>
       <c r="D5" t="n">
-        <v>17598558.68</v>
+        <v>111847141.62</v>
       </c>
       <c r="E5" t="n">
-        <v>2706846.71</v>
+        <v>21343852.1</v>
       </c>
       <c r="F5" t="n">
-        <v>2500.02</v>
+        <v>16666.8</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2987.82</v>
+        <v>618478.74</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>174999</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>40711.36</v>
+        <v>320765.13</v>
       </c>
     </row>
     <row r="6">
@@ -12715,37 +12709,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>7129900.8</v>
+        <v>42968534.4</v>
       </c>
       <c r="C6" t="n">
-        <v>23950080</v>
+        <v>189280476</v>
       </c>
       <c r="D6" t="n">
-        <v>19530457.69</v>
+        <v>154351648.43</v>
       </c>
       <c r="E6" t="n">
-        <v>2353923.94</v>
+        <v>26817919.13</v>
       </c>
       <c r="F6" t="n">
-        <v>29166.9</v>
+        <v>58333.8</v>
       </c>
       <c r="G6" t="n">
-        <v>7520.25</v>
+        <v>62909.25</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1215793.75</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>174999</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>79258</v>
+        <v>544558.9</v>
       </c>
     </row>
     <row r="7">
@@ -12753,37 +12747,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>6342543.9</v>
+        <v>70230897</v>
       </c>
       <c r="C7" t="n">
-        <v>14941080</v>
+        <v>250838280</v>
       </c>
       <c r="D7" t="n">
-        <v>13798842.97</v>
+        <v>231661836.83</v>
       </c>
       <c r="E7" t="n">
-        <v>1622376.91</v>
+        <v>31812695.01</v>
       </c>
       <c r="F7" t="n">
-        <v>25000.2</v>
+        <v>50000.4</v>
       </c>
       <c r="G7" t="n">
-        <v>15151.5</v>
+        <v>246003.75</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2387102.19</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>40833.1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>76132.44</v>
+        <v>1143682.2</v>
       </c>
     </row>
     <row r="8">
@@ -12791,37 +12785,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>3514698</v>
+        <v>61088742</v>
       </c>
       <c r="C8" t="n">
-        <v>4989600</v>
+        <v>127484280</v>
       </c>
       <c r="D8" t="n">
-        <v>5315982.57</v>
+        <v>135823354.57</v>
       </c>
       <c r="E8" t="n">
-        <v>894842.63</v>
+        <v>11226207.48</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>28499.25</v>
+        <v>701298</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>613748.02</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>99166.10000000001</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>32103.36</v>
+        <v>850739.04</v>
       </c>
     </row>
     <row r="9">
@@ -12829,37 +12823,37 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>1669734</v>
+        <v>51555834</v>
       </c>
       <c r="C9" t="n">
-        <v>2106720</v>
+        <v>93166920</v>
       </c>
       <c r="D9" t="n">
-        <v>2448851.03</v>
+        <v>108297214.5</v>
       </c>
       <c r="E9" t="n">
-        <v>443889.43</v>
+        <v>7013453.03</v>
       </c>
       <c r="F9" t="n">
-        <v>41667</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>16039.5</v>
+        <v>536379.75</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>74695.5</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>55416.35</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>7324.99</v>
+        <v>569060.3199999999</v>
       </c>
     </row>
     <row r="10">
@@ -12867,22 +12861,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>947430</v>
+        <v>28667430</v>
       </c>
       <c r="C10" t="n">
-        <v>277200</v>
+        <v>48011040</v>
       </c>
       <c r="D10" t="n">
-        <v>349102.12</v>
+        <v>60464486.49</v>
       </c>
       <c r="E10" t="n">
-        <v>96173.28</v>
+        <v>2596678.56</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>11655</v>
+        <v>425685</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -12891,13 +12885,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>116666</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>5281.79</v>
+        <v>328980.31</v>
       </c>
     </row>
     <row r="11">
@@ -12905,25 +12899,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>608058</v>
+        <v>3459060</v>
       </c>
       <c r="C11" t="n">
-        <v>83160</v>
+        <v>6126120</v>
       </c>
       <c r="D11" t="n">
-        <v>108161.47</v>
+        <v>7967894.66</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>271805.59</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>3330</v>
+        <v>48840</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>8299.5</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -12935,7 +12929,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1978.2</v>
+        <v>96084</v>
       </c>
     </row>
     <row r="12">
@@ -12943,22 +12937,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>357588</v>
+        <v>758538</v>
       </c>
       <c r="C12" t="n">
-        <v>110880</v>
+        <v>2467080</v>
       </c>
       <c r="D12" t="n">
-        <v>148789.73</v>
+        <v>3310571.48</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>158520.1</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2220</v>
+        <v>22755</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12973,7 +12967,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2260.8</v>
+        <v>44650.8</v>
       </c>
     </row>
     <row r="13">
@@ -12981,13 +12975,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>294624</v>
+        <v>398574</v>
       </c>
       <c r="C13" t="n">
-        <v>27720</v>
+        <v>554400</v>
       </c>
       <c r="D13" t="n">
-        <v>38100.28</v>
+        <v>762005.65</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12996,7 +12990,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>2220</v>
+        <v>4995</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13011,7 +13005,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1413</v>
+        <v>31086</v>
       </c>
     </row>
     <row r="14">
@@ -13019,22 +13013,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>280566</v>
+        <v>243936</v>
       </c>
       <c r="C14" t="n">
-        <v>27720</v>
+        <v>110880</v>
       </c>
       <c r="D14" t="n">
-        <v>39003.13</v>
+        <v>156012.53</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>94399.05</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>8325</v>
+        <v>4995</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13049,7 +13043,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>5086.8</v>
+        <v>9891</v>
       </c>
     </row>
     <row r="15">
@@ -13057,13 +13051,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>13860</v>
+        <v>26334</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>194040</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>276954.35</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -13072,7 +13066,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1665</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -13087,7 +13081,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>8478</v>
       </c>
     </row>
     <row r="16">
@@ -13095,13 +13089,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>2970</v>
+        <v>39402</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -13110,7 +13104,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>2775</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -13125,7 +13119,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2260.8</v>
       </c>
     </row>
     <row r="17">
@@ -13133,13 +13127,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>2772</v>
+        <v>23760</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -13148,7 +13142,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1110</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -13163,7 +13157,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3673.8</v>
       </c>
     </row>
     <row r="18">
@@ -13171,13 +13165,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>3168</v>
+        <v>11484</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -13186,7 +13180,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>4440</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -13201,7 +13195,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>5652</v>
       </c>
     </row>
     <row r="19">
@@ -13209,7 +13203,7 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>396</v>
+        <v>3564</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -13224,7 +13218,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>3885</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -13239,7 +13233,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3391.2</v>
       </c>
     </row>
     <row r="20">
@@ -13247,13 +13241,13 @@
         <v>800</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>249480</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>361140.12</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -13262,7 +13256,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>66600</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -13288,10 +13282,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -13326,10 +13320,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -13364,10 +13358,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>27720</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>40126.68</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -13402,10 +13396,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>138600</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>200633.4</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -13500,7 +13494,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Exp</t>
+          <t>Region: Shikarpur | Mode: Exp</t>
         </is>
       </c>
     </row>
@@ -13571,37 +13565,37 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>28674.99</v>
+        <v>35666.91</v>
       </c>
       <c r="C4" t="n">
-        <v>5125680</v>
+        <v>3648960</v>
       </c>
       <c r="D4" t="n">
-        <v>4027320</v>
+        <v>2867040</v>
       </c>
       <c r="E4" t="n">
-        <v>1569600</v>
+        <v>1043100</v>
       </c>
       <c r="F4" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="G4" t="n">
-        <v>83520</v>
+        <v>107310</v>
       </c>
       <c r="H4" t="n">
-        <v>7110</v>
+        <v>13620</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>172020</v>
+        <v>343380</v>
       </c>
     </row>
     <row r="5">
@@ -13609,37 +13603,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>24021.63</v>
+        <v>11628.27</v>
       </c>
       <c r="C5" t="n">
-        <v>4244184</v>
+        <v>783720</v>
       </c>
       <c r="D5" t="n">
-        <v>3334716</v>
+        <v>615780</v>
       </c>
       <c r="E5" t="n">
-        <v>1050300</v>
+        <v>242100</v>
       </c>
       <c r="F5" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>67140</v>
+        <v>30300</v>
       </c>
       <c r="H5" t="n">
-        <v>6210</v>
+        <v>2940</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>162150</v>
+        <v>110970</v>
       </c>
     </row>
     <row r="6">
@@ -13647,37 +13641,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>24413.94</v>
+        <v>1144.8</v>
       </c>
       <c r="C6" t="n">
-        <v>3823848</v>
+        <v>109872</v>
       </c>
       <c r="D6" t="n">
-        <v>3004452</v>
+        <v>86328</v>
       </c>
       <c r="E6" t="n">
-        <v>861300</v>
+        <v>31500</v>
       </c>
       <c r="F6" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>68010</v>
+        <v>4140</v>
       </c>
       <c r="H6" t="n">
-        <v>7710</v>
+        <v>330</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>156240</v>
+        <v>18780</v>
       </c>
     </row>
     <row r="7">
@@ -13685,37 +13679,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>33603.3</v>
+        <v>150.3</v>
       </c>
       <c r="C7" t="n">
-        <v>4560696</v>
+        <v>26712</v>
       </c>
       <c r="D7" t="n">
-        <v>3583404</v>
+        <v>20988</v>
       </c>
       <c r="E7" t="n">
-        <v>811800</v>
+        <v>3600</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>88650</v>
+        <v>780</v>
       </c>
       <c r="H7" t="n">
-        <v>11820</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>202350</v>
+        <v>2940</v>
       </c>
     </row>
     <row r="8">
@@ -13723,37 +13717,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>27767.61</v>
+        <v>12.33</v>
       </c>
       <c r="C8" t="n">
-        <v>2317896</v>
+        <v>1008</v>
       </c>
       <c r="D8" t="n">
-        <v>1821204</v>
+        <v>792</v>
       </c>
       <c r="E8" t="n">
-        <v>248400</v>
+        <v>900</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>58320</v>
+        <v>270</v>
       </c>
       <c r="H8" t="n">
-        <v>2610</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>127200</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9">
@@ -13761,37 +13755,37 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>23434.47</v>
+        <v>0.09</v>
       </c>
       <c r="C9" t="n">
-        <v>1693944</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1330956</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>142200</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>34110</v>
+        <v>30</v>
       </c>
       <c r="H9" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>74580</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10">
@@ -13799,22 +13793,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>13030.65</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>872928</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>685872</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>48600</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>23010</v>
+        <v>30</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -13823,13 +13817,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>39240</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -13837,25 +13831,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>1572.3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>111384</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>87516</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>3600</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2640</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -13867,7 +13861,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>10200</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
@@ -13875,22 +13869,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>344.79</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>44856</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>35244</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>1230</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -13905,7 +13899,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>4740</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -13913,13 +13907,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>181.17</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>10080</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>7920</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -13928,7 +13922,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13943,7 +13937,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>3300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -13951,22 +13945,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>110.88</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>2016</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1584</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13981,7 +13975,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1050</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -13989,13 +13983,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>11.97</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>3528</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>2772</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14004,7 +13998,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -14019,7 +14013,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -14027,13 +14021,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>17.91</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -14042,7 +14036,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -14057,7 +14051,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -14065,13 +14059,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>10.8</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -14080,7 +14074,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -14095,7 +14089,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>390</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -14103,13 +14097,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -14118,7 +14112,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -14133,7 +14127,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -14141,7 +14135,7 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -14156,7 +14150,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -14171,7 +14165,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -14179,13 +14173,13 @@
         <v>800</v>
       </c>
       <c r="B20" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>4536</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>3564</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -14194,7 +14188,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>3600</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -14220,10 +14214,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -14258,10 +14252,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -14296,10 +14290,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -14334,10 +14328,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>2520</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>1980</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -14432,7 +14426,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Vul</t>
+          <t>Region: Shikarpur | Mode: Vul</t>
         </is>
       </c>
     </row>
@@ -14541,37 +14535,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>10809.73</v>
+        <v>5232.72</v>
       </c>
       <c r="C5" t="n">
-        <v>2334301.2</v>
+        <v>431046</v>
       </c>
       <c r="D5" t="n">
-        <v>1103791</v>
+        <v>203823.18</v>
       </c>
       <c r="E5" t="n">
-        <v>115848.09</v>
+        <v>26703.63</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2235.6</v>
+        <v>1058.4</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>34051.5</v>
+        <v>23303.7</v>
       </c>
     </row>
     <row r="6">
@@ -14579,37 +14573,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>19531.15</v>
+        <v>915.84</v>
       </c>
       <c r="C6" t="n">
-        <v>3441463.2</v>
+        <v>98884.8</v>
       </c>
       <c r="D6" t="n">
-        <v>1523257.16</v>
+        <v>43768.3</v>
       </c>
       <c r="E6" t="n">
-        <v>145559.7</v>
+        <v>5323.5</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>3400.5</v>
+        <v>207</v>
       </c>
       <c r="H6" t="n">
-        <v>4394.7</v>
+        <v>188.1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>57808.8</v>
+        <v>6948.6</v>
       </c>
     </row>
     <row r="7">
@@ -14617,37 +14611,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>31923.14</v>
+        <v>142.78</v>
       </c>
       <c r="C7" t="n">
-        <v>4560696</v>
+        <v>26712</v>
       </c>
       <c r="D7" t="n">
-        <v>2286211.75</v>
+        <v>13390.34</v>
       </c>
       <c r="E7" t="n">
-        <v>172669.86</v>
+        <v>765.72</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>13297.5</v>
+        <v>117</v>
       </c>
       <c r="H7" t="n">
-        <v>8628.6</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>121410</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="8">
@@ -14655,37 +14649,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>27767.61</v>
+        <v>12.33</v>
       </c>
       <c r="C8" t="n">
-        <v>2317896</v>
+        <v>1008</v>
       </c>
       <c r="D8" t="n">
-        <v>1340406.14</v>
+        <v>582.91</v>
       </c>
       <c r="E8" t="n">
-        <v>60932.52</v>
+        <v>220.77</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>37908</v>
+        <v>175.5</v>
       </c>
       <c r="H8" t="n">
-        <v>2218.5</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>90312</v>
+        <v>340.8</v>
       </c>
     </row>
     <row r="9">
@@ -14693,37 +14687,37 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>23434.47</v>
+        <v>0.09</v>
       </c>
       <c r="C9" t="n">
-        <v>1693944</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1068757.67</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>38066.94</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>28993.5</v>
+        <v>25.5</v>
       </c>
       <c r="H9" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>60409.8</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="10">
@@ -14731,22 +14725,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>13030.65</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>872928</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>596708.64</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>14094</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>23010</v>
+        <v>30</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -14755,13 +14749,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>34923.6</v>
+        <v>160.2</v>
       </c>
     </row>
     <row r="11">
@@ -14769,25 +14763,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>1572.3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>111384</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>78633.13</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>1475.28</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2640</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -14799,7 +14793,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>10200</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
@@ -14807,22 +14801,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>344.79</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>44856</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>32671.19</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>860.4</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>1230</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -14837,7 +14831,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>4740</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -14845,13 +14839,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>181.17</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>10080</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>7520.04</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -14860,7 +14854,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -14875,7 +14869,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>3300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -14883,22 +14877,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>110.88</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>2016</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1539.65</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>512.37</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -14913,7 +14907,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1050</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -14921,13 +14915,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>11.97</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>3528</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>2733.19</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14936,7 +14930,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -14951,7 +14945,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -14959,13 +14953,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>17.91</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -14974,7 +14968,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -14989,7 +14983,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -14997,13 +14991,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>10.8</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -15012,7 +15006,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -15027,7 +15021,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>390</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -15035,13 +15029,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -15050,7 +15044,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -15065,7 +15059,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -15073,7 +15067,7 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -15088,7 +15082,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -15103,7 +15097,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -15111,13 +15105,13 @@
         <v>800</v>
       </c>
       <c r="B20" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>4536</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>3564</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -15126,7 +15120,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>3600</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -15152,10 +15146,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -15190,10 +15184,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -15228,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -15266,10 +15260,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>2520</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>1980</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -15364,7 +15358,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Dmg</t>
+          <t>Region: Shikarpur | Mode: Dmg</t>
         </is>
       </c>
     </row>
@@ -15473,37 +15467,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>23781413.7</v>
+        <v>11511987.3</v>
       </c>
       <c r="C5" t="n">
-        <v>128386566</v>
+        <v>23707530</v>
       </c>
       <c r="D5" t="n">
-        <v>111847141.62</v>
+        <v>20653402.83</v>
       </c>
       <c r="E5" t="n">
-        <v>21343852.1</v>
+        <v>4919876.79</v>
       </c>
       <c r="F5" t="n">
-        <v>16666.8</v>
+        <v>7500.06</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>618478.74</v>
+        <v>292806.36</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>174999</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>320765.13</v>
+        <v>219520.85</v>
       </c>
     </row>
     <row r="6">
@@ -15511,37 +15505,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>42968534.4</v>
+        <v>2014848</v>
       </c>
       <c r="C6" t="n">
-        <v>189280476</v>
+        <v>5438664</v>
       </c>
       <c r="D6" t="n">
-        <v>154351648.43</v>
+        <v>4435041.43</v>
       </c>
       <c r="E6" t="n">
-        <v>26817919.13</v>
+        <v>980801.64</v>
       </c>
       <c r="F6" t="n">
-        <v>58333.8</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>62909.25</v>
+        <v>3829.5</v>
       </c>
       <c r="H6" t="n">
-        <v>1215793.75</v>
+        <v>52037.86</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>174999</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>544558.9</v>
+        <v>65455.81</v>
       </c>
     </row>
     <row r="7">
@@ -15549,37 +15543,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>70230897</v>
+        <v>314127</v>
       </c>
       <c r="C7" t="n">
-        <v>250838280</v>
+        <v>1469160</v>
       </c>
       <c r="D7" t="n">
-        <v>231661836.83</v>
+        <v>1356843.56</v>
       </c>
       <c r="E7" t="n">
-        <v>31812695.01</v>
+        <v>141076.25</v>
       </c>
       <c r="F7" t="n">
-        <v>50000.4</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>246003.75</v>
+        <v>2164.5</v>
       </c>
       <c r="H7" t="n">
-        <v>2387102.19</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>40833.1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1143682.2</v>
+        <v>16616.88</v>
       </c>
     </row>
     <row r="8">
@@ -15587,37 +15581,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>61088742</v>
+        <v>27126</v>
       </c>
       <c r="C8" t="n">
-        <v>127484280</v>
+        <v>55440</v>
       </c>
       <c r="D8" t="n">
-        <v>135823354.57</v>
+        <v>59066.47</v>
       </c>
       <c r="E8" t="n">
-        <v>11226207.48</v>
+        <v>40674.66</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>701298</v>
+        <v>3246.75</v>
       </c>
       <c r="H8" t="n">
-        <v>613748.02</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>99166.10000000001</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>850739.04</v>
+        <v>3210.34</v>
       </c>
     </row>
     <row r="9">
@@ -15625,37 +15619,37 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>51555834</v>
+        <v>198</v>
       </c>
       <c r="C9" t="n">
-        <v>93166920</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>108297214.5</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>7013453.03</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>536379.75</v>
+        <v>471.75</v>
       </c>
       <c r="H9" t="n">
-        <v>74695.5</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>55416.35</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>569060.3199999999</v>
+        <v>457.81</v>
       </c>
     </row>
     <row r="10">
@@ -15663,22 +15657,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>28667430</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>48011040</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>60464486.49</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>2596678.56</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>425685</v>
+        <v>555</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -15687,13 +15681,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>116666</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>328980.31</v>
+        <v>1509.08</v>
       </c>
     </row>
     <row r="11">
@@ -15701,25 +15695,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>3459060</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>6126120</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>7967894.66</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>271805.59</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>48840</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>8299.5</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -15731,4667 +15725,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>96084</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>758538</v>
-      </c>
-      <c r="C12" t="n">
-        <v>2467080</v>
-      </c>
-      <c r="D12" t="n">
-        <v>3310571.48</v>
-      </c>
-      <c r="E12" t="n">
-        <v>158520.1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>22755</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>44650.8</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>398574</v>
-      </c>
-      <c r="C13" t="n">
-        <v>554400</v>
-      </c>
-      <c r="D13" t="n">
-        <v>762005.65</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>4995</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>31086</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>243936</v>
-      </c>
-      <c r="C14" t="n">
-        <v>110880</v>
-      </c>
-      <c r="D14" t="n">
-        <v>156012.53</v>
-      </c>
-      <c r="E14" t="n">
-        <v>94399.05</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>4995</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>9891</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>26334</v>
-      </c>
-      <c r="C15" t="n">
-        <v>194040</v>
-      </c>
-      <c r="D15" t="n">
-        <v>276954.35</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1665</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>8478</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>39402</v>
-      </c>
-      <c r="C16" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D16" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>2775</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2260.8</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>23760</v>
-      </c>
-      <c r="C17" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D17" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1110</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>3673.8</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>11484</v>
-      </c>
-      <c r="C18" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D18" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>4440</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>5652</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>3564</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>3885</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>3391.2</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>198</v>
-      </c>
-      <c r="C20" t="n">
-        <v>249480</v>
-      </c>
-      <c r="D20" t="n">
-        <v>361140.12</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>66600</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D21" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D22" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D23" t="n">
-        <v>40126.68</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>138600</v>
-      </c>
-      <c r="D24" t="n">
-        <v>200633.4</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Exp</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>3740.94</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1100736</v>
-      </c>
-      <c r="D4" t="n">
-        <v>864864</v>
-      </c>
-      <c r="E4" t="n">
-        <v>363600</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" t="n">
-        <v>13350</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3330</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>34890</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>4808.34</v>
-      </c>
-      <c r="C5" t="n">
-        <v>924840</v>
-      </c>
-      <c r="D5" t="n">
-        <v>726660</v>
-      </c>
-      <c r="E5" t="n">
-        <v>213300</v>
-      </c>
-      <c r="F5" t="n">
-        <v>8</v>
-      </c>
-      <c r="G5" t="n">
-        <v>16200</v>
-      </c>
-      <c r="H5" t="n">
-        <v>3000</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>35220</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>4366.62</v>
-      </c>
-      <c r="C6" t="n">
-        <v>536256</v>
-      </c>
-      <c r="D6" t="n">
-        <v>421344</v>
-      </c>
-      <c r="E6" t="n">
-        <v>104400</v>
-      </c>
-      <c r="F6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G6" t="n">
-        <v>11640</v>
-      </c>
-      <c r="H6" t="n">
-        <v>930</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>22500</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>3925.17</v>
-      </c>
-      <c r="C7" t="n">
-        <v>341208</v>
-      </c>
-      <c r="D7" t="n">
-        <v>268092</v>
-      </c>
-      <c r="E7" t="n">
-        <v>69300</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4950</v>
-      </c>
-      <c r="H7" t="n">
-        <v>390</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>14820</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>4233.15</v>
-      </c>
-      <c r="C8" t="n">
-        <v>236880</v>
-      </c>
-      <c r="D8" t="n">
-        <v>186120</v>
-      </c>
-      <c r="E8" t="n">
-        <v>41400</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>3120</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>10530</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>4135.59</v>
-      </c>
-      <c r="C9" t="n">
-        <v>205632</v>
-      </c>
-      <c r="D9" t="n">
-        <v>161568</v>
-      </c>
-      <c r="E9" t="n">
-        <v>26100</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4140</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>11880</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>2817.09</v>
-      </c>
-      <c r="C10" t="n">
-        <v>98280</v>
-      </c>
-      <c r="D10" t="n">
-        <v>77220</v>
-      </c>
-      <c r="E10" t="n">
-        <v>7200</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2970</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>6060</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>2000.7</v>
-      </c>
-      <c r="C11" t="n">
-        <v>37296</v>
-      </c>
-      <c r="D11" t="n">
-        <v>29304</v>
-      </c>
-      <c r="E11" t="n">
-        <v>900</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>480</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1320</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>1100.25</v>
-      </c>
-      <c r="C12" t="n">
-        <v>10584</v>
-      </c>
-      <c r="D12" t="n">
-        <v>8316</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>300</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>664.5599999999999</v>
-      </c>
-      <c r="C13" t="n">
-        <v>4536</v>
-      </c>
-      <c r="D13" t="n">
-        <v>3564</v>
-      </c>
-      <c r="E13" t="n">
-        <v>900</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>457.02</v>
-      </c>
-      <c r="C14" t="n">
-        <v>2520</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1980</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>300.69</v>
-      </c>
-      <c r="C15" t="n">
-        <v>2016</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1584</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>331.83</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D16" t="n">
-        <v>792</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>373.86</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D17" t="n">
-        <v>792</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>141.75</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D18" t="n">
-        <v>792</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>37.71</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>14.58</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Vul</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>2163.75</v>
-      </c>
-      <c r="C5" t="n">
-        <v>508662</v>
-      </c>
-      <c r="D5" t="n">
-        <v>240524.46</v>
-      </c>
-      <c r="E5" t="n">
-        <v>23526.99</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1080</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>7396.2</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>3493.3</v>
-      </c>
-      <c r="C6" t="n">
-        <v>482630.4</v>
-      </c>
-      <c r="D6" t="n">
-        <v>213621.41</v>
-      </c>
-      <c r="E6" t="n">
-        <v>17643.6</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G6" t="n">
-        <v>582</v>
-      </c>
-      <c r="H6" t="n">
-        <v>530.1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>8325</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>3728.91</v>
-      </c>
-      <c r="C7" t="n">
-        <v>341208</v>
-      </c>
-      <c r="D7" t="n">
-        <v>171042.7</v>
-      </c>
-      <c r="E7" t="n">
-        <v>14740.11</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>742.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>284.7</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>8892</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>4233.15</v>
-      </c>
-      <c r="C8" t="n">
-        <v>236880</v>
-      </c>
-      <c r="D8" t="n">
-        <v>136984.32</v>
-      </c>
-      <c r="E8" t="n">
-        <v>10155.42</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2028</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>7476.3</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>4135.59</v>
-      </c>
-      <c r="C9" t="n">
-        <v>205632</v>
-      </c>
-      <c r="D9" t="n">
-        <v>129739.1</v>
-      </c>
-      <c r="E9" t="n">
-        <v>6986.97</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3519</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>9622.799999999999</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>2817.09</v>
-      </c>
-      <c r="C10" t="n">
-        <v>98280</v>
-      </c>
-      <c r="D10" t="n">
-        <v>67181.39999999999</v>
-      </c>
-      <c r="E10" t="n">
-        <v>2088</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2970</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>5393.4</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>2000.7</v>
-      </c>
-      <c r="C11" t="n">
-        <v>37296</v>
-      </c>
-      <c r="D11" t="n">
-        <v>26329.64</v>
-      </c>
-      <c r="E11" t="n">
-        <v>368.82</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>480</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1320</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>1100.25</v>
-      </c>
-      <c r="C12" t="n">
-        <v>10584</v>
-      </c>
-      <c r="D12" t="n">
-        <v>7708.93</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>300</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>664.5599999999999</v>
-      </c>
-      <c r="C13" t="n">
-        <v>4536</v>
-      </c>
-      <c r="D13" t="n">
-        <v>3384.02</v>
-      </c>
-      <c r="E13" t="n">
-        <v>476.28</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>457.02</v>
-      </c>
-      <c r="C14" t="n">
-        <v>2520</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1924.56</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>300.69</v>
-      </c>
-      <c r="C15" t="n">
-        <v>2016</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1561.82</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>331.83</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D16" t="n">
-        <v>792</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>373.86</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D17" t="n">
-        <v>792</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>141.75</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D18" t="n">
-        <v>792</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>37.71</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>14.58</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Dmg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>4760256.6</v>
-      </c>
-      <c r="C5" t="n">
-        <v>27976410</v>
-      </c>
-      <c r="D5" t="n">
-        <v>24372343.53</v>
-      </c>
-      <c r="E5" t="n">
-        <v>4334612.64</v>
-      </c>
-      <c r="F5" t="n">
-        <v>6666.72</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>298782</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>17499.9</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>69672.2</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>7685251.2</v>
-      </c>
-      <c r="C6" t="n">
-        <v>26544672</v>
-      </c>
-      <c r="D6" t="n">
-        <v>21646257.27</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3250656.86</v>
-      </c>
-      <c r="F6" t="n">
-        <v>25000.2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>10767</v>
-      </c>
-      <c r="H6" t="n">
-        <v>146652.16</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>78421.5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>8203605.3</v>
-      </c>
-      <c r="C7" t="n">
-        <v>18766440</v>
-      </c>
-      <c r="D7" t="n">
-        <v>17331756.39</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2715717.87</v>
-      </c>
-      <c r="F7" t="n">
-        <v>50000.4</v>
-      </c>
-      <c r="G7" t="n">
-        <v>13736.25</v>
-      </c>
-      <c r="H7" t="n">
-        <v>78762.25</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>83762.64</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>9312930</v>
-      </c>
-      <c r="C8" t="n">
-        <v>13028400</v>
-      </c>
-      <c r="D8" t="n">
-        <v>13880621.15</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1871034.58</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>37518</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>70426.75</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>9098298</v>
-      </c>
-      <c r="C9" t="n">
-        <v>11309760</v>
-      </c>
-      <c r="D9" t="n">
-        <v>13146463.41</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1287279.35</v>
-      </c>
-      <c r="F9" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G9" t="n">
-        <v>65101.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>90646.78</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>6197598</v>
-      </c>
-      <c r="C10" t="n">
-        <v>5405400</v>
-      </c>
-      <c r="D10" t="n">
-        <v>6807491.26</v>
-      </c>
-      <c r="E10" t="n">
-        <v>384693.12</v>
-      </c>
-      <c r="F10" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G10" t="n">
-        <v>54945</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>50805.83</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>4401540</v>
-      </c>
-      <c r="C11" t="n">
-        <v>2051280</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2667982.83</v>
-      </c>
-      <c r="E11" t="n">
-        <v>67951.39999999999</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>8880</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>12434.4</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>2420550</v>
-      </c>
-      <c r="C12" t="n">
-        <v>582120</v>
-      </c>
-      <c r="D12" t="n">
-        <v>781146.08</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>5550</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>3391.2</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>1462032</v>
-      </c>
-      <c r="C13" t="n">
-        <v>249480</v>
-      </c>
-      <c r="D13" t="n">
-        <v>342902.54</v>
-      </c>
-      <c r="E13" t="n">
-        <v>87749.83</v>
-      </c>
-      <c r="F13" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>1005444</v>
-      </c>
-      <c r="C14" t="n">
-        <v>138600</v>
-      </c>
-      <c r="D14" t="n">
-        <v>195015.66</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>661518</v>
-      </c>
-      <c r="C15" t="n">
-        <v>110880</v>
-      </c>
-      <c r="D15" t="n">
-        <v>158259.63</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>730026</v>
-      </c>
-      <c r="C16" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D16" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>822492</v>
-      </c>
-      <c r="C17" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D17" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>311850</v>
-      </c>
-      <c r="C18" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D18" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>82962</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>32076</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Exp</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>35666.91</v>
-      </c>
-      <c r="C4" t="n">
-        <v>3648960</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2867040</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1043100</v>
-      </c>
-      <c r="F4" t="n">
-        <v>35</v>
-      </c>
-      <c r="G4" t="n">
-        <v>107310</v>
-      </c>
-      <c r="H4" t="n">
-        <v>13620</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>4</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>343380</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>11628.27</v>
-      </c>
-      <c r="C5" t="n">
-        <v>783720</v>
-      </c>
-      <c r="D5" t="n">
-        <v>615780</v>
-      </c>
-      <c r="E5" t="n">
-        <v>242100</v>
-      </c>
-      <c r="F5" t="n">
-        <v>9</v>
-      </c>
-      <c r="G5" t="n">
-        <v>30300</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2940</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>110970</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>1144.8</v>
-      </c>
-      <c r="C6" t="n">
-        <v>109872</v>
-      </c>
-      <c r="D6" t="n">
-        <v>86328</v>
-      </c>
-      <c r="E6" t="n">
-        <v>31500</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>4140</v>
-      </c>
-      <c r="H6" t="n">
-        <v>330</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>18780</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>150.3</v>
-      </c>
-      <c r="C7" t="n">
-        <v>26712</v>
-      </c>
-      <c r="D7" t="n">
-        <v>20988</v>
-      </c>
-      <c r="E7" t="n">
-        <v>3600</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>780</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2940</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D8" t="n">
-        <v>792</v>
-      </c>
-      <c r="E8" t="n">
-        <v>900</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>270</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>30</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>30</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Vul</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>5232.72</v>
-      </c>
-      <c r="C5" t="n">
-        <v>431046</v>
-      </c>
-      <c r="D5" t="n">
-        <v>203823.18</v>
-      </c>
-      <c r="E5" t="n">
-        <v>26703.63</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1058.4</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>23303.7</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>915.84</v>
-      </c>
-      <c r="C6" t="n">
-        <v>98884.8</v>
-      </c>
-      <c r="D6" t="n">
-        <v>43768.3</v>
-      </c>
-      <c r="E6" t="n">
-        <v>5323.5</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>207</v>
-      </c>
-      <c r="H6" t="n">
-        <v>188.1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>6948.6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>142.78</v>
-      </c>
-      <c r="C7" t="n">
-        <v>26712</v>
-      </c>
-      <c r="D7" t="n">
-        <v>13390.34</v>
-      </c>
-      <c r="E7" t="n">
-        <v>765.72</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>117</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1764</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D8" t="n">
-        <v>582.91</v>
-      </c>
-      <c r="E8" t="n">
-        <v>220.77</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>175.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>340.8</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>48.6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>30</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>160.2</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>90</v>
+        <v>847.8</v>
       </c>
     </row>
     <row r="12">
@@ -21876,938 +17210,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Dmg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>11511987.3</v>
-      </c>
-      <c r="C5" t="n">
-        <v>23707530</v>
-      </c>
-      <c r="D5" t="n">
-        <v>20653402.83</v>
-      </c>
-      <c r="E5" t="n">
-        <v>4919876.79</v>
-      </c>
-      <c r="F5" t="n">
-        <v>7500.06</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>292806.36</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>219520.85</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>2014848</v>
-      </c>
-      <c r="C6" t="n">
-        <v>5438664</v>
-      </c>
-      <c r="D6" t="n">
-        <v>4435041.43</v>
-      </c>
-      <c r="E6" t="n">
-        <v>980801.64</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>3829.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>52037.86</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>65455.81</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>314127</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1469160</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1356843.56</v>
-      </c>
-      <c r="E7" t="n">
-        <v>141076.25</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2164.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>16616.88</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>27126</v>
-      </c>
-      <c r="C8" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D8" t="n">
-        <v>59066.47</v>
-      </c>
-      <c r="E8" t="n">
-        <v>40674.66</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>3246.75</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3210.34</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>198</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>471.75</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>457.81</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>555</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1509.08</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>847.8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/risk/Risk_Analysis_T3_100yrs_Future_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_100yrs_Future_Breaches.xlsx
@@ -538,7 +538,7 @@
         <v>61800</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J4" t="n">
         <v>39</v>
@@ -576,7 +576,7 @@
         <v>53760</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J5" t="n">
         <v>25</v>
@@ -614,7 +614,7 @@
         <v>45930</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>13</v>
@@ -652,7 +652,7 @@
         <v>42690</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
         <v>11</v>
@@ -690,7 +690,7 @@
         <v>27600</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
         <v>10</v>
@@ -728,7 +728,7 @@
         <v>9450</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>4</v>
@@ -804,7 +804,7 @@
         <v>4680</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
         <v>3</v>
@@ -918,7 +918,7 @@
         <v>720</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1660,7 +1660,7 @@
         <v>3690</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1736,7 +1736,7 @@
         <v>4260</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1850,7 +1850,7 @@
         <v>720</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2592,7 +2592,7 @@
         <v>3690</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -2668,7 +2668,7 @@
         <v>4260</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -2782,7 +2782,7 @@
         <v>720</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -3524,7 +3524,7 @@
         <v>1020838.5</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>337330.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
         <v>1178529</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>766660</v>
       </c>
       <c r="J11" t="n">
         <v>58333</v>
@@ -3714,7 +3714,7 @@
         <v>199188</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -9858,7 +9858,7 @@
         <v>7110</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
         <v>9</v>
@@ -9896,7 +9896,7 @@
         <v>6210</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J5" t="n">
         <v>10</v>
@@ -9934,7 +9934,7 @@
         <v>7710</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>6</v>
@@ -9972,7 +9972,7 @@
         <v>11820</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -10010,7 +10010,7 @@
         <v>2610</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
         <v>2</v>
@@ -10124,7 +10124,7 @@
         <v>30</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -10828,7 +10828,7 @@
         <v>19353.6</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="J5" t="n">
         <v>7.5</v>
@@ -10866,7 +10866,7 @@
         <v>26180.1</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="J6" t="n">
         <v>6.5</v>
@@ -10904,7 +10904,7 @@
         <v>31163.7</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="n">
         <v>7.7</v>
@@ -10942,7 +10942,7 @@
         <v>23460</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="J8" t="n">
         <v>8.5</v>
@@ -10980,7 +10980,7 @@
         <v>9450</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="J9" t="n">
         <v>3.8</v>
@@ -11056,7 +11056,7 @@
         <v>4680</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
         <v>3</v>
@@ -11170,7 +11170,7 @@
         <v>720</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -11760,7 +11760,7 @@
         <v>2235.6</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="J5" t="n">
         <v>3</v>
@@ -11798,7 +11798,7 @@
         <v>4394.7</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="J6" t="n">
         <v>3</v>
@@ -11836,7 +11836,7 @@
         <v>8628.6</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="n">
         <v>0.7</v>
@@ -11874,7 +11874,7 @@
         <v>2218.5</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="J8" t="n">
         <v>1.7</v>
@@ -11988,7 +11988,7 @@
         <v>30</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -12692,7 +12692,7 @@
         <v>618478.74</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>229998</v>
       </c>
       <c r="J5" t="n">
         <v>174999</v>
@@ -12730,7 +12730,7 @@
         <v>1215793.75</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>134165.5</v>
       </c>
       <c r="J6" t="n">
         <v>174999</v>
@@ -12768,7 +12768,7 @@
         <v>2387102.19</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>421663</v>
       </c>
       <c r="J7" t="n">
         <v>40833.1</v>
@@ -12806,7 +12806,7 @@
         <v>613748.02</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>551995.2</v>
       </c>
       <c r="J8" t="n">
         <v>99166.10000000001</v>
@@ -12920,7 +12920,7 @@
         <v>8299.5</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -13586,7 +13586,7 @@
         <v>13620</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>4</v>
@@ -16420,7 +16420,7 @@
         <v>5354173.44</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>287497.5</v>
       </c>
       <c r="J5" t="n">
         <v>437497.5</v>
@@ -16458,7 +16458,7 @@
         <v>7242724.66</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>134165.5</v>
       </c>
       <c r="J6" t="n">
         <v>379164.5</v>
@@ -16496,7 +16496,7 @@
         <v>8621437.6</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>421663</v>
       </c>
       <c r="J7" t="n">
         <v>449164.1</v>
@@ -16534,7 +16534,7 @@
         <v>6490209</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>827992.8</v>
       </c>
       <c r="J8" t="n">
         <v>495830.5</v>
@@ -16572,7 +16572,7 @@
         <v>2614342.5</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>337330.4</v>
       </c>
       <c r="J9" t="n">
         <v>221665.4</v>
@@ -16648,7 +16648,7 @@
         <v>1294722</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1149990</v>
       </c>
       <c r="J11" t="n">
         <v>174999</v>
@@ -16762,7 +16762,7 @@
         <v>199188</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -17314,7 +17314,7 @@
         <v>2880</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -17466,7 +17466,7 @@
         <v>20100</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>7</v>
@@ -18398,7 +18398,7 @@
         <v>17085</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="J8" t="n">
         <v>5.95</v>
@@ -19330,7 +19330,7 @@
         <v>4726565.25</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>275997.6</v>
       </c>
       <c r="J8" t="n">
         <v>347081.35</v>
@@ -20110,7 +20110,7 @@
         <v>17430</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>14</v>
@@ -20148,7 +20148,7 @@
         <v>22620</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>7</v>
@@ -21080,7 +21080,7 @@
         <v>8143.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="J5" t="n">
         <v>2.1</v>
@@ -22012,7 +22012,7 @@
         <v>2252816.28</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>57499.5</v>
       </c>
       <c r="J5" t="n">
         <v>122499.3</v>

--- a/risk/Risk_Analysis_T3_100yrs_Future_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_100yrs_Future_Breaches.xlsx
@@ -544,7 +544,7 @@
         <v>39</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1128</v>
       </c>
       <c r="L4" t="n">
         <v>1422210</v>
@@ -582,7 +582,7 @@
         <v>25</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>621</v>
       </c>
       <c r="L5" t="n">
         <v>890580</v>
@@ -620,7 +620,7 @@
         <v>13</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>431</v>
       </c>
       <c r="L6" t="n">
         <v>576900</v>
@@ -658,7 +658,7 @@
         <v>11</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>448</v>
       </c>
       <c r="L7" t="n">
         <v>534450</v>
@@ -696,7 +696,7 @@
         <v>10</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>355</v>
       </c>
       <c r="L8" t="n">
         <v>442920</v>
@@ -734,7 +734,7 @@
         <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>342</v>
       </c>
       <c r="L9" t="n">
         <v>377130</v>
@@ -772,7 +772,7 @@
         <v>11</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="L10" t="n">
         <v>299550</v>
@@ -810,7 +810,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="L11" t="n">
         <v>187590</v>
@@ -848,7 +848,7 @@
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="L12" t="n">
         <v>151800</v>
@@ -886,7 +886,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="L13" t="n">
         <v>102240</v>
@@ -924,7 +924,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="L14" t="n">
         <v>43560</v>
@@ -962,7 +962,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L15" t="n">
         <v>18390</v>
@@ -1000,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
         <v>8700</v>
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17" t="n">
         <v>2460</v>
@@ -1076,7 +1076,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18" t="n">
         <v>4620</v>
@@ -1476,7 +1476,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L4" t="n">
         <v>17160</v>
@@ -1514,7 +1514,7 @@
         <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L5" t="n">
         <v>20430</v>
@@ -1552,7 +1552,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L6" t="n">
         <v>21240</v>
@@ -1590,7 +1590,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L7" t="n">
         <v>26430</v>
@@ -1628,7 +1628,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L8" t="n">
         <v>36630</v>
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="L9" t="n">
         <v>45870</v>
@@ -1704,7 +1704,7 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L10" t="n">
         <v>43620</v>
@@ -1742,7 +1742,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="L11" t="n">
         <v>53730</v>
@@ -1780,7 +1780,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="L12" t="n">
         <v>91590</v>
@@ -1818,7 +1818,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="L13" t="n">
         <v>71640</v>
@@ -1856,7 +1856,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L14" t="n">
         <v>33870</v>
@@ -1894,7 +1894,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L15" t="n">
         <v>14460</v>
@@ -1932,7 +1932,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L16" t="n">
         <v>7500</v>
@@ -1970,7 +1970,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>1860</v>
@@ -2008,7 +2008,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>3810</v>
@@ -2446,7 +2446,7 @@
         <v>0.9</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="L5" t="n">
         <v>4290.3</v>
@@ -2484,7 +2484,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L6" t="n">
         <v>7858.8</v>
@@ -2522,7 +2522,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>16.4</v>
       </c>
       <c r="L7" t="n">
         <v>15858</v>
@@ -2560,7 +2560,7 @@
         <v>0.85</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>16.2</v>
       </c>
       <c r="L8" t="n">
         <v>26007.3</v>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="L9" t="n">
         <v>37154.7</v>
@@ -2636,7 +2636,7 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L10" t="n">
         <v>38821.8</v>
@@ -2674,7 +2674,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="L11" t="n">
         <v>53730</v>
@@ -2712,7 +2712,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="L12" t="n">
         <v>91590</v>
@@ -2750,7 +2750,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="L13" t="n">
         <v>71640</v>
@@ -2788,7 +2788,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L14" t="n">
         <v>33870</v>
@@ -2826,7 +2826,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L15" t="n">
         <v>14460</v>
@@ -2864,7 +2864,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L16" t="n">
         <v>7500</v>
@@ -2902,7 +2902,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>1860</v>
@@ -2940,7 +2940,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>3810</v>
@@ -3378,7 +3378,7 @@
         <v>52499.7</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>62721.96</v>
       </c>
       <c r="L5" t="n">
         <v>40414.63</v>
@@ -3416,7 +3416,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>277342</v>
       </c>
       <c r="L6" t="n">
         <v>74029.89999999999</v>
@@ -3454,7 +3454,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>349877.6</v>
       </c>
       <c r="L7" t="n">
         <v>149382.36</v>
@@ -3492,7 +3492,7 @@
         <v>49583.05</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>345610.8</v>
       </c>
       <c r="L8" t="n">
         <v>244988.77</v>
@@ -3530,7 +3530,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>597352</v>
       </c>
       <c r="L9" t="n">
         <v>349997.27</v>
@@ -3568,7 +3568,7 @@
         <v>291665</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>362678</v>
       </c>
       <c r="L10" t="n">
         <v>365701.36</v>
@@ -3606,7 +3606,7 @@
         <v>58333</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>618686</v>
       </c>
       <c r="L11" t="n">
         <v>506136.6</v>
@@ -3644,7 +3644,7 @@
         <v>58333</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>853360</v>
       </c>
       <c r="L12" t="n">
         <v>862777.8</v>
@@ -3682,7 +3682,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>661354</v>
       </c>
       <c r="L13" t="n">
         <v>674848.8</v>
@@ -3720,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>490682</v>
       </c>
       <c r="L14" t="n">
         <v>319055.4</v>
@@ -3758,7 +3758,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>192006</v>
       </c>
       <c r="L15" t="n">
         <v>136213.2</v>
@@ -3796,7 +3796,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>64002</v>
       </c>
       <c r="L16" t="n">
         <v>70650</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L17" t="n">
         <v>17521.2</v>
@@ -3872,7 +3872,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L18" t="n">
         <v>35890.2</v>
@@ -4272,7 +4272,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="L4" t="n">
         <v>145950</v>
@@ -4310,7 +4310,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="L5" t="n">
         <v>57990</v>
@@ -4348,7 +4348,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>11280</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>3090</v>
@@ -5242,7 +5242,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>12.18</v>
       </c>
       <c r="L5" t="n">
         <v>12177.9</v>
@@ -5280,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="L6" t="n">
         <v>4173.6</v>
@@ -5318,7 +5318,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="L7" t="n">
         <v>1854</v>
@@ -6174,7 +6174,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>259848.12</v>
       </c>
       <c r="L5" t="n">
         <v>114715.82</v>
@@ -6212,7 +6212,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>13867.1</v>
       </c>
       <c r="L6" t="n">
         <v>39315.31</v>
@@ -6250,7 +6250,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>17493.88</v>
       </c>
       <c r="L7" t="n">
         <v>17464.68</v>
@@ -7068,7 +7068,7 @@
         <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="L4" t="n">
         <v>138090</v>
@@ -7106,7 +7106,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="L5" t="n">
         <v>48120</v>
@@ -7144,7 +7144,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L6" t="n">
         <v>13800</v>
@@ -7182,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
         <v>3780</v>
@@ -7220,7 +7220,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
         <v>2040</v>
@@ -8038,7 +8038,7 @@
         <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>20.16</v>
       </c>
       <c r="L5" t="n">
         <v>10105.2</v>
@@ -8076,7 +8076,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="L6" t="n">
         <v>5106</v>
@@ -8114,7 +8114,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="L7" t="n">
         <v>2268</v>
@@ -8152,7 +8152,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="L8" t="n">
         <v>1448.4</v>
@@ -8970,7 +8970,7 @@
         <v>17499.9</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>430093.44</v>
       </c>
       <c r="L5" t="n">
         <v>95190.98</v>
@@ -9008,7 +9008,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>124803.9</v>
       </c>
       <c r="L6" t="n">
         <v>48098.52</v>
@@ -9046,7 +9046,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>34987.76</v>
       </c>
       <c r="L7" t="n">
         <v>21364.56</v>
@@ -9084,7 +9084,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>38401.2</v>
       </c>
       <c r="L8" t="n">
         <v>13643.93</v>
@@ -9864,7 +9864,7 @@
         <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="L4" t="n">
         <v>172020</v>
@@ -9902,7 +9902,7 @@
         <v>10</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="L5" t="n">
         <v>162150</v>
@@ -9940,7 +9940,7 @@
         <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="L6" t="n">
         <v>156240</v>
@@ -9978,7 +9978,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="L7" t="n">
         <v>202350</v>
@@ -10016,7 +10016,7 @@
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="L8" t="n">
         <v>127200</v>
@@ -10054,7 +10054,7 @@
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="L9" t="n">
         <v>74580</v>
@@ -10092,7 +10092,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="L10" t="n">
         <v>39240</v>
@@ -10130,7 +10130,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L11" t="n">
         <v>10200</v>
@@ -10168,7 +10168,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L12" t="n">
         <v>4740</v>
@@ -10396,7 +10396,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>600</v>
@@ -10834,7 +10834,7 @@
         <v>7.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>260.82</v>
       </c>
       <c r="L5" t="n">
         <v>187021.8</v>
@@ -10872,7 +10872,7 @@
         <v>6.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>280.15</v>
       </c>
       <c r="L6" t="n">
         <v>213453</v>
@@ -10910,7 +10910,7 @@
         <v>7.7</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>367.36</v>
       </c>
       <c r="L7" t="n">
         <v>320670</v>
@@ -10948,7 +10948,7 @@
         <v>8.5</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>319.5</v>
       </c>
       <c r="L8" t="n">
         <v>314473.2</v>
@@ -10986,7 +10986,7 @@
         <v>3.8</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>342</v>
       </c>
       <c r="L9" t="n">
         <v>305475.3</v>
@@ -11024,7 +11024,7 @@
         <v>11</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="L10" t="n">
         <v>266599.5</v>
@@ -11062,7 +11062,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="L11" t="n">
         <v>187590</v>
@@ -11100,7 +11100,7 @@
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="L12" t="n">
         <v>151800</v>
@@ -11138,7 +11138,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="L13" t="n">
         <v>102240</v>
@@ -11176,7 +11176,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="L14" t="n">
         <v>43560</v>
@@ -11214,7 +11214,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L15" t="n">
         <v>18390</v>
@@ -11252,7 +11252,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
         <v>8700</v>
@@ -11290,7 +11290,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17" t="n">
         <v>2460</v>
@@ -11328,7 +11328,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18" t="n">
         <v>4620</v>
@@ -11766,7 +11766,7 @@
         <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>67.62</v>
       </c>
       <c r="L5" t="n">
         <v>34051.5</v>
@@ -11804,7 +11804,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="L6" t="n">
         <v>57808.8</v>
@@ -11842,7 +11842,7 @@
         <v>0.7</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>167.28</v>
       </c>
       <c r="L7" t="n">
         <v>121410</v>
@@ -11880,7 +11880,7 @@
         <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>112.5</v>
       </c>
       <c r="L8" t="n">
         <v>90312</v>
@@ -11918,7 +11918,7 @@
         <v>0.95</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="L9" t="n">
         <v>60409.8</v>
@@ -11956,7 +11956,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="L10" t="n">
         <v>34923.6</v>
@@ -11994,7 +11994,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L11" t="n">
         <v>10200</v>
@@ -12032,7 +12032,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L12" t="n">
         <v>4740</v>
@@ -12260,7 +12260,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>600</v>
@@ -12698,7 +12698,7 @@
         <v>174999</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1442605.08</v>
       </c>
       <c r="L5" t="n">
         <v>320765.13</v>
@@ -12736,7 +12736,7 @@
         <v>174999</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2093932.1</v>
       </c>
       <c r="L6" t="n">
         <v>544558.9</v>
@@ -12774,7 +12774,7 @@
         <v>40833.1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3568751.52</v>
       </c>
       <c r="L7" t="n">
         <v>1143682.2</v>
@@ -12812,7 +12812,7 @@
         <v>99166.10000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2400075</v>
       </c>
       <c r="L8" t="n">
         <v>850739.04</v>
@@ -12850,7 +12850,7 @@
         <v>55416.35</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1962728</v>
       </c>
       <c r="L9" t="n">
         <v>569060.3199999999</v>
@@ -12888,7 +12888,7 @@
         <v>116666</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>960030</v>
       </c>
       <c r="L10" t="n">
         <v>328980.31</v>
@@ -12926,7 +12926,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>106670</v>
       </c>
       <c r="L11" t="n">
         <v>96084</v>
@@ -12964,7 +12964,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>42668</v>
       </c>
       <c r="L12" t="n">
         <v>44650.8</v>
@@ -13192,7 +13192,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L18" t="n">
         <v>5652</v>
@@ -13592,7 +13592,7 @@
         <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="L4" t="n">
         <v>343380</v>
@@ -13630,7 +13630,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="L5" t="n">
         <v>110970</v>
@@ -14562,7 +14562,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>13.44</v>
       </c>
       <c r="L5" t="n">
         <v>23303.7</v>
@@ -15494,7 +15494,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>286728.96</v>
       </c>
       <c r="L5" t="n">
         <v>219520.85</v>
@@ -16426,7 +16426,7 @@
         <v>437497.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>5564333.88</v>
       </c>
       <c r="L5" t="n">
         <v>1761745.36</v>
@@ -16464,7 +16464,7 @@
         <v>379164.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>5976720.1</v>
       </c>
       <c r="L6" t="n">
         <v>2010727.26</v>
@@ -16502,7 +16502,7 @@
         <v>449164.1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>7837258.24</v>
       </c>
       <c r="L7" t="n">
         <v>3020711.4</v>
@@ -16540,7 +16540,7 @@
         <v>495830.5</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>6816213</v>
       </c>
       <c r="L8" t="n">
         <v>2962337.54</v>
@@ -16578,7 +16578,7 @@
         <v>221665.4</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>7296228</v>
       </c>
       <c r="L9" t="n">
         <v>2877577.33</v>
@@ -16616,7 +16616,7 @@
         <v>641663</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>5440170</v>
       </c>
       <c r="L10" t="n">
         <v>2511367.29</v>
@@ -16654,7 +16654,7 @@
         <v>174999</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>3690782</v>
       </c>
       <c r="L11" t="n">
         <v>1767097.8</v>
@@ -16692,7 +16692,7 @@
         <v>116666</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>2432076</v>
       </c>
       <c r="L12" t="n">
         <v>1429956</v>
@@ -16730,7 +16730,7 @@
         <v>174999</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1194704</v>
       </c>
       <c r="L13" t="n">
         <v>963100.8</v>
@@ -16768,7 +16768,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>704022</v>
       </c>
       <c r="L14" t="n">
         <v>410335.2</v>
@@ -16806,7 +16806,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>192006</v>
       </c>
       <c r="L15" t="n">
         <v>173233.8</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>85336</v>
       </c>
       <c r="L16" t="n">
         <v>81954</v>
@@ -16882,7 +16882,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>42668</v>
       </c>
       <c r="L17" t="n">
         <v>23173.2</v>
@@ -16920,7 +16920,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>42668</v>
       </c>
       <c r="L18" t="n">
         <v>43520.4</v>
@@ -17320,7 +17320,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="L4" t="n">
         <v>138840</v>
@@ -17358,7 +17358,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="L5" t="n">
         <v>166950</v>
@@ -17396,7 +17396,7 @@
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="L6" t="n">
         <v>169050</v>
@@ -17434,7 +17434,7 @@
         <v>7</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="L7" t="n">
         <v>180720</v>
@@ -17472,7 +17472,7 @@
         <v>7</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="L8" t="n">
         <v>237450</v>
@@ -17510,7 +17510,7 @@
         <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="L9" t="n">
         <v>239250</v>
@@ -17548,7 +17548,7 @@
         <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="L10" t="n">
         <v>208230</v>
@@ -17586,7 +17586,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="L11" t="n">
         <v>121290</v>
@@ -17624,7 +17624,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="L12" t="n">
         <v>54630</v>
@@ -17662,7 +17662,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L13" t="n">
         <v>27150</v>
@@ -17700,7 +17700,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L14" t="n">
         <v>8100</v>
@@ -17776,7 +17776,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>960</v>
@@ -17814,7 +17814,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>210</v>
@@ -18290,7 +18290,7 @@
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>63.84</v>
       </c>
       <c r="L5" t="n">
         <v>35059.5</v>
@@ -18328,7 +18328,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="L6" t="n">
         <v>62548.5</v>
@@ -18366,7 +18366,7 @@
         <v>4.9</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>118.9</v>
       </c>
       <c r="L7" t="n">
         <v>108432</v>
@@ -18404,7 +18404,7 @@
         <v>5.95</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>180.9</v>
       </c>
       <c r="L8" t="n">
         <v>168589.5</v>
@@ -18442,7 +18442,7 @@
         <v>2.85</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="L9" t="n">
         <v>193792.5</v>
@@ -18480,7 +18480,7 @@
         <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="L10" t="n">
         <v>185324.7</v>
@@ -18518,7 +18518,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="L11" t="n">
         <v>121290</v>
@@ -18556,7 +18556,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="L12" t="n">
         <v>54630</v>
@@ -18594,7 +18594,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L13" t="n">
         <v>27150</v>
@@ -18632,7 +18632,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L14" t="n">
         <v>8100</v>
@@ -18708,7 +18708,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>960</v>
@@ -18746,7 +18746,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>210</v>
@@ -19222,7 +19222,7 @@
         <v>34999.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1361962.56</v>
       </c>
       <c r="L5" t="n">
         <v>330260.49</v>
@@ -19260,7 +19260,7 @@
         <v>116666</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1955261.1</v>
       </c>
       <c r="L6" t="n">
         <v>589206.87</v>
@@ -19298,7 +19298,7 @@
         <v>285831.7</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2536612.6</v>
       </c>
       <c r="L7" t="n">
         <v>1021429.44</v>
@@ -19336,7 +19336,7 @@
         <v>347081.35</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>3859320.6</v>
       </c>
       <c r="L8" t="n">
         <v>1588113.09</v>
@@ -19374,7 +19374,7 @@
         <v>166249.05</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>4672146</v>
       </c>
       <c r="L9" t="n">
         <v>1825525.35</v>
@@ -19412,7 +19412,7 @@
         <v>233332</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>4096128</v>
       </c>
       <c r="L10" t="n">
         <v>1745758.67</v>
@@ -19450,7 +19450,7 @@
         <v>116666</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>2965426</v>
       </c>
       <c r="L11" t="n">
         <v>1142551.8</v>
@@ -19488,7 +19488,7 @@
         <v>58333</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1536048</v>
       </c>
       <c r="L12" t="n">
         <v>514614.6</v>
@@ -19526,7 +19526,7 @@
         <v>174999</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>512016</v>
       </c>
       <c r="L13" t="n">
         <v>255753</v>
@@ -19564,7 +19564,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>213340</v>
       </c>
       <c r="L14" t="n">
         <v>76302</v>
@@ -19640,7 +19640,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L16" t="n">
         <v>9043.200000000001</v>
@@ -19678,7 +19678,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L17" t="n">
         <v>1978.2</v>
@@ -20116,7 +20116,7 @@
         <v>14</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>387</v>
       </c>
       <c r="L4" t="n">
         <v>408330</v>
@@ -20154,7 +20154,7 @@
         <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="L5" t="n">
         <v>262830</v>
@@ -20192,7 +20192,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="L6" t="n">
         <v>134520</v>
@@ -20230,7 +20230,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="L7" t="n">
         <v>79440</v>
@@ -20268,7 +20268,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L8" t="n">
         <v>21840</v>
@@ -21086,7 +21086,7 @@
         <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>80.22</v>
       </c>
       <c r="L5" t="n">
         <v>55194.3</v>
@@ -21124,7 +21124,7 @@
         <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>70.2</v>
       </c>
       <c r="L6" t="n">
         <v>49772.4</v>
@@ -21162,7 +21162,7 @@
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>60.68</v>
       </c>
       <c r="L7" t="n">
         <v>47664</v>
@@ -21200,7 +21200,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="L8" t="n">
         <v>15506.4</v>
@@ -22018,7 +22018,7 @@
         <v>122499.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1711413.48</v>
       </c>
       <c r="L5" t="n">
         <v>519930.31</v>
@@ -22056,7 +22056,7 @@
         <v>87499.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1497646.8</v>
       </c>
       <c r="L6" t="n">
         <v>468856.01</v>
@@ -22094,7 +22094,7 @@
         <v>122499.3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1294547.12</v>
       </c>
       <c r="L7" t="n">
         <v>448994.88</v>
@@ -22132,7 +22132,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>172805.4</v>
       </c>
       <c r="L8" t="n">
         <v>146070.29</v>

--- a/risk/Risk_Analysis_T3_100yrs_Future_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_100yrs_Future_Breaches.xlsx
@@ -549,7 +549,7 @@
         <v>39</v>
       </c>
       <c r="K4" t="n">
-        <v>1109</v>
+        <v>433</v>
       </c>
       <c r="L4" t="n">
         <v>1418940</v>
@@ -590,7 +590,7 @@
         <v>25</v>
       </c>
       <c r="K5" t="n">
-        <v>607</v>
+        <v>262</v>
       </c>
       <c r="L5" t="n">
         <v>888630</v>
@@ -631,7 +631,7 @@
         <v>13</v>
       </c>
       <c r="K6" t="n">
-        <v>426</v>
+        <v>165</v>
       </c>
       <c r="L6" t="n">
         <v>575160</v>
@@ -672,7 +672,7 @@
         <v>11</v>
       </c>
       <c r="K7" t="n">
-        <v>447</v>
+        <v>152</v>
       </c>
       <c r="L7" t="n">
         <v>533400</v>
@@ -713,7 +713,7 @@
         <v>10</v>
       </c>
       <c r="K8" t="n">
-        <v>355</v>
+        <v>102</v>
       </c>
       <c r="L8" t="n">
         <v>442200</v>
@@ -754,7 +754,7 @@
         <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>342</v>
+        <v>110</v>
       </c>
       <c r="L9" t="n">
         <v>376770</v>
@@ -795,7 +795,7 @@
         <v>11</v>
       </c>
       <c r="K10" t="n">
-        <v>255</v>
+        <v>59</v>
       </c>
       <c r="L10" t="n">
         <v>299460</v>
@@ -836,7 +836,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>173</v>
+        <v>35</v>
       </c>
       <c r="L11" t="n">
         <v>187320</v>
@@ -877,7 +877,7 @@
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="L12" t="n">
         <v>151590</v>
@@ -918,7 +918,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="L13" t="n">
         <v>102240</v>
@@ -959,7 +959,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>43560</v>
@@ -1000,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>18390</v>
@@ -1041,7 +1041,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>8700</v>
@@ -1082,7 +1082,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>2460</v>
@@ -1123,7 +1123,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>4620</v>
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="L4" t="n">
         <v>17280</v>
@@ -1594,7 +1594,7 @@
         <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
         <v>20400</v>
@@ -1635,7 +1635,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="L6" t="n">
         <v>21300</v>
@@ -1676,7 +1676,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L7" t="n">
         <v>26490</v>
@@ -1717,7 +1717,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L8" t="n">
         <v>36840</v>
@@ -1758,7 +1758,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="L9" t="n">
         <v>46050</v>
@@ -1799,7 +1799,7 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
         <v>43650</v>
@@ -1840,7 +1840,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="L11" t="n">
         <v>53910</v>
@@ -1881,7 +1881,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="L12" t="n">
         <v>91770</v>
@@ -1922,7 +1922,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="L13" t="n">
         <v>71700</v>
@@ -1963,7 +1963,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>33900</v>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>14520</v>
@@ -2045,7 +2045,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>7500</v>
@@ -2086,7 +2086,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>1860</v>
@@ -2127,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>3810</v>
@@ -2598,7 +2598,7 @@
         <v>0.9</v>
       </c>
       <c r="K5" t="n">
-        <v>1.99</v>
+        <v>0.99</v>
       </c>
       <c r="L5" t="n">
         <v>4284</v>
@@ -2639,7 +2639,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>10.14</v>
+        <v>4.56</v>
       </c>
       <c r="L6" t="n">
         <v>7881</v>
@@ -2680,7 +2680,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>12.76</v>
+        <v>6.38</v>
       </c>
       <c r="L7" t="n">
         <v>15894</v>
@@ -2721,7 +2721,7 @@
         <v>0.85</v>
       </c>
       <c r="K8" t="n">
-        <v>13.25</v>
+        <v>8.1</v>
       </c>
       <c r="L8" t="n">
         <v>26156.4</v>
@@ -2762,7 +2762,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>22.48</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="L9" t="n">
         <v>37300.5</v>
@@ -2803,7 +2803,7 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>14.79</v>
+        <v>1.74</v>
       </c>
       <c r="L10" t="n">
         <v>38848.5</v>
@@ -2844,7 +2844,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>26.06</v>
+        <v>2.7</v>
       </c>
       <c r="L11" t="n">
         <v>53910</v>
@@ -2885,7 +2885,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>37.08</v>
+        <v>5.56</v>
       </c>
       <c r="L12" t="n">
         <v>91770</v>
@@ -2926,7 +2926,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>29.43</v>
+        <v>4.75</v>
       </c>
       <c r="L13" t="n">
         <v>71700</v>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>22.36</v>
+        <v>0.97</v>
       </c>
       <c r="L14" t="n">
         <v>33900</v>
@@ -3008,7 +3008,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>8.869999999999999</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>14520</v>
@@ -3049,7 +3049,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>7500</v>
@@ -3090,7 +3090,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>1860</v>
@@ -3131,7 +3131,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>3810</v>
@@ -3602,7 +3602,7 @@
         <v>21850.2</v>
       </c>
       <c r="K5" t="n">
-        <v>96432.22</v>
+        <v>48216.11</v>
       </c>
       <c r="L5" t="n">
         <v>771120</v>
@@ -3643,7 +3643,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>492357.84</v>
+        <v>221561.03</v>
       </c>
       <c r="L6" t="n">
         <v>1418580</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>619574.5600000001</v>
+        <v>309787.28</v>
       </c>
       <c r="L7" t="n">
         <v>2860920</v>
@@ -3725,7 +3725,7 @@
         <v>20636.3</v>
       </c>
       <c r="K8" t="n">
-        <v>643269.89</v>
+        <v>393109.38</v>
       </c>
       <c r="L8" t="n">
         <v>4708152</v>
@@ -3766,7 +3766,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1091733.1</v>
+        <v>389904.68</v>
       </c>
       <c r="L9" t="n">
         <v>6714090</v>
@@ -3807,7 +3807,7 @@
         <v>121390</v>
       </c>
       <c r="K10" t="n">
-        <v>718143.24</v>
+        <v>84487.44</v>
       </c>
       <c r="L10" t="n">
         <v>6992730</v>
@@ -3848,7 +3848,7 @@
         <v>24278</v>
       </c>
       <c r="K11" t="n">
-        <v>1265199.41</v>
+        <v>130882.7</v>
       </c>
       <c r="L11" t="n">
         <v>9703800</v>
@@ -3889,7 +3889,7 @@
         <v>24278</v>
       </c>
       <c r="K12" t="n">
-        <v>1800456.48</v>
+        <v>270068.47</v>
       </c>
       <c r="L12" t="n">
         <v>16518600</v>
@@ -3930,7 +3930,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1429221.58</v>
+        <v>230519.61</v>
       </c>
       <c r="L13" t="n">
         <v>12906000</v>
@@ -3971,7 +3971,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1085517.94</v>
+        <v>47196.43</v>
       </c>
       <c r="L14" t="n">
         <v>6102000</v>
@@ -4012,7 +4012,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>430885.94</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>2613600</v>
@@ -4053,7 +4053,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>145668</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>1350000</v>
@@ -4094,7 +4094,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>48556</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>334800</v>
@@ -4135,7 +4135,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>48556</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>685800</v>
@@ -4565,7 +4565,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="L4" t="n">
         <v>145890</v>
@@ -4606,7 +4606,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="L5" t="n">
         <v>58680</v>
@@ -4647,7 +4647,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>11220</v>
@@ -5610,7 +5610,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>9.6</v>
+        <v>4.96</v>
       </c>
       <c r="L5" t="n">
         <v>12322.8</v>
@@ -5651,7 +5651,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>4151.4</v>
@@ -6614,7 +6614,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>466089.04</v>
+        <v>241080.54</v>
       </c>
       <c r="L5" t="n">
         <v>2218104</v>
@@ -6655,7 +6655,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>24617.89</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>747252</v>
@@ -7577,7 +7577,7 @@
         <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>175</v>
+        <v>37</v>
       </c>
       <c r="L4" t="n">
         <v>138300</v>
@@ -7618,7 +7618,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="L5" t="n">
         <v>48690</v>
@@ -7659,7 +7659,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>13890</v>
@@ -7700,7 +7700,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>3780</v>
@@ -7741,7 +7741,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>2040</v>
@@ -8622,7 +8622,7 @@
         <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>15.89</v>
+        <v>3.64</v>
       </c>
       <c r="L5" t="n">
         <v>10224.9</v>
@@ -8663,7 +8663,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>5139.3</v>
@@ -8704,7 +8704,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>2268</v>
@@ -8745,7 +8745,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>1448.4</v>
@@ -9626,7 +9626,7 @@
         <v>7283.4</v>
       </c>
       <c r="K5" t="n">
-        <v>771457.73</v>
+        <v>176792.4</v>
       </c>
       <c r="L5" t="n">
         <v>1840482</v>
@@ -9667,7 +9667,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>221561.03</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>925074</v>
@@ -9708,7 +9708,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>61957.46</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>408240</v>
@@ -9749,7 +9749,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>71474.42999999999</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>260712</v>
@@ -10589,7 +10589,7 @@
         <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>229</v>
+        <v>131</v>
       </c>
       <c r="L4" t="n">
         <v>172410</v>
@@ -10630,7 +10630,7 @@
         <v>10</v>
       </c>
       <c r="K5" t="n">
-        <v>161</v>
+        <v>88</v>
       </c>
       <c r="L5" t="n">
         <v>162240</v>
@@ -10671,7 +10671,7 @@
         <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>151</v>
+        <v>76</v>
       </c>
       <c r="L6" t="n">
         <v>156300</v>
@@ -10712,7 +10712,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>204</v>
+        <v>72</v>
       </c>
       <c r="L7" t="n">
         <v>202470</v>
@@ -10753,7 +10753,7 @@
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>125</v>
+        <v>42</v>
       </c>
       <c r="L8" t="n">
         <v>127230</v>
@@ -10794,7 +10794,7 @@
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>92</v>
+        <v>34</v>
       </c>
       <c r="L9" t="n">
         <v>74640</v>
@@ -10835,7 +10835,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
         <v>39240</v>
@@ -10876,7 +10876,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
         <v>10200</v>
@@ -11163,7 +11163,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>600</v>
@@ -11634,7 +11634,7 @@
         <v>7.5</v>
       </c>
       <c r="K5" t="n">
-        <v>200.92</v>
+        <v>86.72</v>
       </c>
       <c r="L5" t="n">
         <v>186612.3</v>
@@ -11675,7 +11675,7 @@
         <v>6.5</v>
       </c>
       <c r="K6" t="n">
-        <v>215.98</v>
+        <v>83.66</v>
       </c>
       <c r="L6" t="n">
         <v>212809.2</v>
@@ -11716,7 +11716,7 @@
         <v>7.7</v>
       </c>
       <c r="K7" t="n">
-        <v>285.19</v>
+        <v>96.98</v>
       </c>
       <c r="L7" t="n">
         <v>320040</v>
@@ -11757,7 +11757,7 @@
         <v>8.5</v>
       </c>
       <c r="K8" t="n">
-        <v>261.28</v>
+        <v>75.06999999999999</v>
       </c>
       <c r="L8" t="n">
         <v>313962</v>
@@ -11798,7 +11798,7 @@
         <v>3.8</v>
       </c>
       <c r="K9" t="n">
-        <v>274.63</v>
+        <v>88.33</v>
       </c>
       <c r="L9" t="n">
         <v>305183.7</v>
@@ -11839,7 +11839,7 @@
         <v>11</v>
       </c>
       <c r="K10" t="n">
-        <v>221.85</v>
+        <v>51.33</v>
       </c>
       <c r="L10" t="n">
         <v>266519.4</v>
@@ -11880,7 +11880,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>155.44</v>
+        <v>31.45</v>
       </c>
       <c r="L11" t="n">
         <v>187320</v>
@@ -11921,7 +11921,7 @@
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>105.68</v>
+        <v>15.76</v>
       </c>
       <c r="L12" t="n">
         <v>151590</v>
@@ -11962,7 +11962,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>53.17</v>
+        <v>5.7</v>
       </c>
       <c r="L13" t="n">
         <v>102240</v>
@@ -12003,7 +12003,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>32.08</v>
+        <v>0.97</v>
       </c>
       <c r="L14" t="n">
         <v>43560</v>
@@ -12044,7 +12044,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>8.869999999999999</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>18390</v>
@@ -12085,7 +12085,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>8700</v>
@@ -12126,7 +12126,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>2460</v>
@@ -12167,7 +12167,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>4620</v>
@@ -12638,7 +12638,7 @@
         <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>53.29</v>
+        <v>29.13</v>
       </c>
       <c r="L5" t="n">
         <v>34070.4</v>
@@ -12679,7 +12679,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>76.56</v>
+        <v>38.53</v>
       </c>
       <c r="L6" t="n">
         <v>57831</v>
@@ -12720,7 +12720,7 @@
         <v>0.7</v>
       </c>
       <c r="K7" t="n">
-        <v>130.15</v>
+        <v>45.94</v>
       </c>
       <c r="L7" t="n">
         <v>121482</v>
@@ -12761,7 +12761,7 @@
         <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>92</v>
+        <v>30.91</v>
       </c>
       <c r="L8" t="n">
         <v>90333.3</v>
@@ -12802,7 +12802,7 @@
         <v>0.95</v>
       </c>
       <c r="K9" t="n">
-        <v>73.88</v>
+        <v>27.3</v>
       </c>
       <c r="L9" t="n">
         <v>60458.4</v>
@@ -12843,7 +12843,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>40.02</v>
+        <v>4.35</v>
       </c>
       <c r="L10" t="n">
         <v>34923.6</v>
@@ -12884,7 +12884,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>4.49</v>
+        <v>1.8</v>
       </c>
       <c r="L11" t="n">
         <v>10200</v>
@@ -13171,7 +13171,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>600</v>
@@ -13642,7 +13642,7 @@
         <v>72834</v>
       </c>
       <c r="K5" t="n">
-        <v>2587597.8</v>
+        <v>1414339.17</v>
       </c>
       <c r="L5" t="n">
         <v>6132672</v>
@@ -13683,7 +13683,7 @@
         <v>72834</v>
       </c>
       <c r="K6" t="n">
-        <v>3717301.69</v>
+        <v>1870959.79</v>
       </c>
       <c r="L6" t="n">
         <v>10409580</v>
@@ -13724,7 +13724,7 @@
         <v>16994.6</v>
       </c>
       <c r="K7" t="n">
-        <v>6319660.51</v>
+        <v>2230468.42</v>
       </c>
       <c r="L7" t="n">
         <v>21866760</v>
@@ -13765,7 +13765,7 @@
         <v>41272.6</v>
       </c>
       <c r="K8" t="n">
-        <v>4467152</v>
+        <v>1500963.07</v>
       </c>
       <c r="L8" t="n">
         <v>16259994</v>
@@ -13806,7 +13806,7 @@
         <v>23064.1</v>
       </c>
       <c r="K9" t="n">
-        <v>3587123.06</v>
+        <v>1325675.91</v>
       </c>
       <c r="L9" t="n">
         <v>10882512</v>
@@ -13847,7 +13847,7 @@
         <v>48556</v>
       </c>
       <c r="K10" t="n">
-        <v>1943211.12</v>
+        <v>211218.6</v>
       </c>
       <c r="L10" t="n">
         <v>6286248</v>
@@ -13888,7 +13888,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>218137.83</v>
+        <v>87255.13</v>
       </c>
       <c r="L11" t="n">
         <v>1836000</v>
@@ -14175,7 +14175,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>48556</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>108000</v>
@@ -14605,7 +14605,7 @@
         <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>118</v>
+        <v>48</v>
       </c>
       <c r="L4" t="n">
         <v>345870</v>
@@ -14646,7 +14646,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="L5" t="n">
         <v>112080</v>
@@ -15650,7 +15650,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>10.59</v>
+        <v>4.96</v>
       </c>
       <c r="L5" t="n">
         <v>23536.8</v>
@@ -16654,7 +16654,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>514305.15</v>
+        <v>241080.54</v>
       </c>
       <c r="L5" t="n">
         <v>4236624</v>
@@ -17658,7 +17658,7 @@
         <v>182085</v>
       </c>
       <c r="K5" t="n">
-        <v>9755725.85</v>
+        <v>4210873.43</v>
       </c>
       <c r="L5" t="n">
         <v>33590214</v>
@@ -17699,7 +17699,7 @@
         <v>157807</v>
       </c>
       <c r="K6" t="n">
-        <v>10487221.99</v>
+        <v>4061952.18</v>
       </c>
       <c r="L6" t="n">
         <v>38305656</v>
@@ -17740,7 +17740,7 @@
         <v>186940.6</v>
       </c>
       <c r="K7" t="n">
-        <v>13847491.42</v>
+        <v>4708766.66</v>
       </c>
       <c r="L7" t="n">
         <v>57607200</v>
@@ -17781,7 +17781,7 @@
         <v>206363</v>
       </c>
       <c r="K8" t="n">
-        <v>12686711.68</v>
+        <v>3645196.03</v>
       </c>
       <c r="L8" t="n">
         <v>56513160</v>
@@ -17822,7 +17822,7 @@
         <v>92256.39999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>13334740.06</v>
+        <v>4288951.48</v>
       </c>
       <c r="L9" t="n">
         <v>54933066</v>
@@ -17863,7 +17863,7 @@
         <v>267058</v>
       </c>
       <c r="K10" t="n">
-        <v>10772148.6</v>
+        <v>2492379.48</v>
       </c>
       <c r="L10" t="n">
         <v>47973492</v>
@@ -17904,7 +17904,7 @@
         <v>72834</v>
       </c>
       <c r="K11" t="n">
-        <v>7547568.92</v>
+        <v>1526964.81</v>
       </c>
       <c r="L11" t="n">
         <v>33717600</v>
@@ -17945,7 +17945,7 @@
         <v>48556</v>
       </c>
       <c r="K12" t="n">
-        <v>5131300.97</v>
+        <v>765194</v>
       </c>
       <c r="L12" t="n">
         <v>27286200</v>
@@ -17986,7 +17986,7 @@
         <v>72834</v>
       </c>
       <c r="K13" t="n">
-        <v>2581819.63</v>
+        <v>276623.53</v>
       </c>
       <c r="L13" t="n">
         <v>18403200</v>
@@ -18027,7 +18027,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1557482.26</v>
+        <v>47196.43</v>
       </c>
       <c r="L14" t="n">
         <v>7840800</v>
@@ -18068,7 +18068,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>430885.94</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>3310200</v>
@@ -18109,7 +18109,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>194224</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>1566000</v>
@@ -18150,7 +18150,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>97112</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>442800</v>
@@ -18191,7 +18191,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>97112</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>831600</v>
@@ -18621,7 +18621,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>122</v>
+        <v>72</v>
       </c>
       <c r="L4" t="n">
         <v>135660</v>
@@ -18662,7 +18662,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>139</v>
+        <v>69</v>
       </c>
       <c r="L5" t="n">
         <v>165450</v>
@@ -18703,7 +18703,7 @@
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>136</v>
+        <v>53</v>
       </c>
       <c r="L6" t="n">
         <v>168420</v>
@@ -18744,7 +18744,7 @@
         <v>7</v>
       </c>
       <c r="K7" t="n">
-        <v>144</v>
+        <v>57</v>
       </c>
       <c r="L7" t="n">
         <v>179910</v>
@@ -18785,7 +18785,7 @@
         <v>7</v>
       </c>
       <c r="K8" t="n">
-        <v>201</v>
+        <v>48</v>
       </c>
       <c r="L8" t="n">
         <v>236760</v>
@@ -18826,7 +18826,7 @@
         <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>219</v>
+        <v>65</v>
       </c>
       <c r="L9" t="n">
         <v>238920</v>
@@ -18867,7 +18867,7 @@
         <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>192</v>
+        <v>52</v>
       </c>
       <c r="L10" t="n">
         <v>208200</v>
@@ -18908,7 +18908,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>139</v>
+        <v>30</v>
       </c>
       <c r="L11" t="n">
         <v>121080</v>
@@ -18949,7 +18949,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="L12" t="n">
         <v>54450</v>
@@ -18990,7 +18990,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>27270</v>
@@ -19031,7 +19031,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>8070</v>
@@ -19113,7 +19113,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>960</v>
@@ -19154,7 +19154,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>210</v>
@@ -19666,7 +19666,7 @@
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>46.01</v>
+        <v>22.84</v>
       </c>
       <c r="L5" t="n">
         <v>34744.5</v>
@@ -19707,7 +19707,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>68.95</v>
+        <v>26.87</v>
       </c>
       <c r="L6" t="n">
         <v>62315.4</v>
@@ -19748,7 +19748,7 @@
         <v>4.9</v>
       </c>
       <c r="K7" t="n">
-        <v>91.87</v>
+        <v>36.37</v>
       </c>
       <c r="L7" t="n">
         <v>107946</v>
@@ -19789,7 +19789,7 @@
         <v>5.95</v>
       </c>
       <c r="K8" t="n">
-        <v>147.94</v>
+        <v>35.33</v>
       </c>
       <c r="L8" t="n">
         <v>168099.6</v>
@@ -19830,7 +19830,7 @@
         <v>2.85</v>
       </c>
       <c r="K9" t="n">
-        <v>175.86</v>
+        <v>52.2</v>
       </c>
       <c r="L9" t="n">
         <v>193525.2</v>
@@ -19871,7 +19871,7 @@
         <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>167.04</v>
+        <v>45.24</v>
       </c>
       <c r="L10" t="n">
         <v>185298</v>
@@ -19912,7 +19912,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>124.89</v>
+        <v>26.96</v>
       </c>
       <c r="L11" t="n">
         <v>121080</v>
@@ -19953,7 +19953,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>66.73999999999999</v>
+        <v>8.34</v>
       </c>
       <c r="L12" t="n">
         <v>54450</v>
@@ -19994,7 +19994,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>23.74</v>
+        <v>0.95</v>
       </c>
       <c r="L13" t="n">
         <v>27270</v>
@@ -20035,7 +20035,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>9.720000000000001</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>8070</v>
@@ -20117,7 +20117,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>960</v>
@@ -20158,7 +20158,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>210</v>
@@ -20670,7 +20670,7 @@
         <v>14566.8</v>
       </c>
       <c r="K5" t="n">
-        <v>2234013</v>
+        <v>1108970.48</v>
       </c>
       <c r="L5" t="n">
         <v>6254010</v>
@@ -20711,7 +20711,7 @@
         <v>48556</v>
       </c>
       <c r="K6" t="n">
-        <v>3348033.31</v>
+        <v>1304748.28</v>
       </c>
       <c r="L6" t="n">
         <v>11216772</v>
@@ -20752,7 +20752,7 @@
         <v>118962.2</v>
       </c>
       <c r="K7" t="n">
-        <v>4460936.83</v>
+        <v>1765787.5</v>
       </c>
       <c r="L7" t="n">
         <v>19430280</v>
@@ -20793,7 +20793,7 @@
         <v>144454.1</v>
       </c>
       <c r="K8" t="n">
-        <v>7183180.42</v>
+        <v>1715386.37</v>
       </c>
       <c r="L8" t="n">
         <v>30257928</v>
@@ -20834,7 +20834,7 @@
         <v>69192.3</v>
       </c>
       <c r="K9" t="n">
-        <v>8538912.49</v>
+        <v>2534380.42</v>
       </c>
       <c r="L9" t="n">
         <v>34834536</v>
@@ -20875,7 +20875,7 @@
         <v>97112</v>
       </c>
       <c r="K10" t="n">
-        <v>8110794.24</v>
+        <v>2196673.44</v>
       </c>
       <c r="L10" t="n">
         <v>33353640</v>
@@ -20916,7 +20916,7 @@
         <v>48556</v>
       </c>
       <c r="K11" t="n">
-        <v>6064231.67</v>
+        <v>1308826.98</v>
       </c>
       <c r="L11" t="n">
         <v>21794400</v>
@@ -20957,7 +20957,7 @@
         <v>24278</v>
       </c>
       <c r="K12" t="n">
-        <v>3240821.66</v>
+        <v>405102.71</v>
       </c>
       <c r="L12" t="n">
         <v>9801000</v>
@@ -20998,7 +20998,7 @@
         <v>72834</v>
       </c>
       <c r="K13" t="n">
-        <v>1152598.05</v>
+        <v>46103.92</v>
       </c>
       <c r="L13" t="n">
         <v>4908600</v>
@@ -21039,7 +21039,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>471964.32</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>1452600</v>
@@ -21121,7 +21121,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>48556</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>172800</v>
@@ -21162,7 +21162,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>48556</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>37800</v>
@@ -21633,7 +21633,7 @@
         <v>14</v>
       </c>
       <c r="K4" t="n">
-        <v>388</v>
+        <v>96</v>
       </c>
       <c r="L4" t="n">
         <v>407070</v>
@@ -21674,7 +21674,7 @@
         <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>191</v>
+        <v>61</v>
       </c>
       <c r="L5" t="n">
         <v>261780</v>
@@ -21715,7 +21715,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>108</v>
+        <v>27</v>
       </c>
       <c r="L6" t="n">
         <v>135120</v>
@@ -21756,7 +21756,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="L7" t="n">
         <v>79380</v>
@@ -21797,7 +21797,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>21930</v>
@@ -22678,7 +22678,7 @@
         <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>63.22</v>
+        <v>20.19</v>
       </c>
       <c r="L5" t="n">
         <v>54973.8</v>
@@ -22719,7 +22719,7 @@
         <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>54.76</v>
+        <v>13.69</v>
       </c>
       <c r="L6" t="n">
         <v>49994.4</v>
@@ -22760,7 +22760,7 @@
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>47.21</v>
+        <v>7.66</v>
       </c>
       <c r="L7" t="n">
         <v>47628</v>
@@ -22801,7 +22801,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>6.62</v>
+        <v>0.74</v>
       </c>
       <c r="L8" t="n">
         <v>15570.3</v>
@@ -23682,7 +23682,7 @@
         <v>50983.8</v>
       </c>
       <c r="K5" t="n">
-        <v>3069758.88</v>
+        <v>980394.2</v>
       </c>
       <c r="L5" t="n">
         <v>9895284</v>
@@ -23723,7 +23723,7 @@
         <v>36417</v>
       </c>
       <c r="K6" t="n">
-        <v>2658732.34</v>
+        <v>664683.08</v>
       </c>
       <c r="L6" t="n">
         <v>8998992</v>
@@ -23764,7 +23764,7 @@
         <v>50983.8</v>
       </c>
       <c r="K7" t="n">
-        <v>2292425.87</v>
+        <v>371744.74</v>
       </c>
       <c r="L7" t="n">
         <v>8573040</v>
@@ -23805,7 +23805,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>321634.94</v>
+        <v>35737.22</v>
       </c>
       <c r="L8" t="n">
         <v>2802654</v>

--- a/risk/Risk_Analysis_T3_100yrs_Future_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_100yrs_Future_Breaches.xlsx
@@ -560,7 +560,7 @@
         <v>542490</v>
       </c>
       <c r="H4" t="n">
-        <v>61800</v>
+        <v>68880</v>
       </c>
       <c r="I4" t="n">
         <v>9</v>
@@ -572,22 +572,22 @@
         <v>433</v>
       </c>
       <c r="L4" t="n">
-        <v>1418940</v>
+        <v>1518150</v>
       </c>
       <c r="M4" t="n">
-        <v>71850</v>
+        <v>49620</v>
       </c>
       <c r="N4" t="n">
-        <v>81180</v>
+        <v>78780</v>
       </c>
       <c r="O4" t="n">
-        <v>222030</v>
+        <v>224190</v>
       </c>
       <c r="P4" t="n">
-        <v>41760</v>
+        <v>15210</v>
       </c>
       <c r="Q4" t="n">
-        <v>215717.78</v>
+        <v>2235462.46</v>
       </c>
     </row>
     <row r="5">
@@ -613,7 +613,7 @@
         <v>354570</v>
       </c>
       <c r="H5" t="n">
-        <v>53760</v>
+        <v>58770</v>
       </c>
       <c r="I5" t="n">
         <v>5</v>
@@ -625,22 +625,22 @@
         <v>262</v>
       </c>
       <c r="L5" t="n">
-        <v>888630</v>
+        <v>941580</v>
       </c>
       <c r="M5" t="n">
-        <v>50550</v>
+        <v>38730</v>
       </c>
       <c r="N5" t="n">
-        <v>75210</v>
+        <v>86880</v>
       </c>
       <c r="O5" t="n">
-        <v>182400</v>
+        <v>208320</v>
       </c>
       <c r="P5" t="n">
-        <v>52470</v>
+        <v>33960</v>
       </c>
       <c r="Q5" t="n">
-        <v>137321.01</v>
+        <v>1423044.34</v>
       </c>
     </row>
     <row r="6">
@@ -666,7 +666,7 @@
         <v>235290</v>
       </c>
       <c r="H6" t="n">
-        <v>45930</v>
+        <v>46590</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -678,22 +678,22 @@
         <v>165</v>
       </c>
       <c r="L6" t="n">
-        <v>575160</v>
+        <v>574680</v>
       </c>
       <c r="M6" t="n">
-        <v>33810</v>
+        <v>22920</v>
       </c>
       <c r="N6" t="n">
-        <v>26940</v>
+        <v>37980</v>
       </c>
       <c r="O6" t="n">
-        <v>114420</v>
+        <v>125040</v>
       </c>
       <c r="P6" t="n">
-        <v>51300</v>
+        <v>37470</v>
       </c>
       <c r="Q6" t="n">
-        <v>95066.00999999999</v>
+        <v>985159.9</v>
       </c>
     </row>
     <row r="7">
@@ -719,7 +719,7 @@
         <v>210900</v>
       </c>
       <c r="H7" t="n">
-        <v>42690</v>
+        <v>45270</v>
       </c>
       <c r="I7" t="n">
         <v>2</v>
@@ -731,22 +731,22 @@
         <v>152</v>
       </c>
       <c r="L7" t="n">
-        <v>533400</v>
+        <v>533220</v>
       </c>
       <c r="M7" t="n">
-        <v>23610</v>
+        <v>26130</v>
       </c>
       <c r="N7" t="n">
-        <v>9690</v>
+        <v>14430</v>
       </c>
       <c r="O7" t="n">
-        <v>83580</v>
+        <v>89790</v>
       </c>
       <c r="P7" t="n">
-        <v>61800</v>
+        <v>44520</v>
       </c>
       <c r="Q7" t="n">
-        <v>93333.64999999999</v>
+        <v>967207.55</v>
       </c>
     </row>
     <row r="8">
@@ -772,7 +772,7 @@
         <v>175890</v>
       </c>
       <c r="H8" t="n">
-        <v>27600</v>
+        <v>28710</v>
       </c>
       <c r="I8" t="n">
         <v>3</v>
@@ -784,22 +784,22 @@
         <v>102</v>
       </c>
       <c r="L8" t="n">
-        <v>442200</v>
+        <v>438630</v>
       </c>
       <c r="M8" t="n">
-        <v>18600</v>
+        <v>26160</v>
       </c>
       <c r="N8" t="n">
-        <v>2130</v>
+        <v>4350</v>
       </c>
       <c r="O8" t="n">
-        <v>60780</v>
+        <v>64650</v>
       </c>
       <c r="P8" t="n">
-        <v>69300</v>
+        <v>55170</v>
       </c>
       <c r="Q8" t="n">
-        <v>78362.95</v>
+        <v>812067.7</v>
       </c>
     </row>
     <row r="9">
@@ -825,7 +825,7 @@
         <v>156270</v>
       </c>
       <c r="H9" t="n">
-        <v>9450</v>
+        <v>12090</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -837,22 +837,22 @@
         <v>110</v>
       </c>
       <c r="L9" t="n">
-        <v>376770</v>
+        <v>392790</v>
       </c>
       <c r="M9" t="n">
-        <v>11430</v>
+        <v>33420</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="O9" t="n">
-        <v>54990</v>
+        <v>64350</v>
       </c>
       <c r="P9" t="n">
-        <v>67770</v>
+        <v>62400</v>
       </c>
       <c r="Q9" t="n">
-        <v>74903.35000000001</v>
+        <v>776216.2</v>
       </c>
     </row>
     <row r="10">
@@ -878,7 +878,7 @@
         <v>141930</v>
       </c>
       <c r="H10" t="n">
-        <v>3720</v>
+        <v>3480</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -890,22 +890,22 @@
         <v>59</v>
       </c>
       <c r="L10" t="n">
-        <v>299460</v>
+        <v>329490</v>
       </c>
       <c r="M10" t="n">
-        <v>9300</v>
+        <v>23970</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>33600</v>
+        <v>47130</v>
       </c>
       <c r="P10" t="n">
-        <v>76980</v>
+        <v>77370</v>
       </c>
       <c r="Q10" t="n">
-        <v>61927.73</v>
+        <v>641751.1</v>
       </c>
     </row>
     <row r="11">
@@ -931,7 +931,7 @@
         <v>78990</v>
       </c>
       <c r="H11" t="n">
-        <v>4680</v>
+        <v>4500</v>
       </c>
       <c r="I11" t="n">
         <v>3</v>
@@ -943,22 +943,22 @@
         <v>35</v>
       </c>
       <c r="L11" t="n">
-        <v>187320</v>
+        <v>224910</v>
       </c>
       <c r="M11" t="n">
-        <v>6120</v>
+        <v>24960</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>12270</v>
+        <v>22770</v>
       </c>
       <c r="P11" t="n">
-        <v>72570</v>
+        <v>89310</v>
       </c>
       <c r="Q11" t="n">
-        <v>40121.43</v>
+        <v>415774.47</v>
       </c>
     </row>
     <row r="12">
@@ -984,7 +984,7 @@
         <v>60480</v>
       </c>
       <c r="H12" t="n">
-        <v>5040</v>
+        <v>5850</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -996,22 +996,22 @@
         <v>17</v>
       </c>
       <c r="L12" t="n">
-        <v>151590</v>
+        <v>198930</v>
       </c>
       <c r="M12" t="n">
-        <v>3780</v>
+        <v>21660</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4590</v>
+        <v>12540</v>
       </c>
       <c r="P12" t="n">
-        <v>59610</v>
+        <v>98670</v>
       </c>
       <c r="Q12" t="n">
-        <v>28053</v>
+        <v>290710.56</v>
       </c>
     </row>
     <row r="13">
@@ -1037,7 +1037,7 @@
         <v>50400</v>
       </c>
       <c r="H13" t="n">
-        <v>1530</v>
+        <v>2070</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1049,22 +1049,22 @@
         <v>6</v>
       </c>
       <c r="L13" t="n">
-        <v>102240</v>
+        <v>138930</v>
       </c>
       <c r="M13" t="n">
-        <v>3210</v>
+        <v>16170</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2520</v>
+        <v>3720</v>
       </c>
       <c r="P13" t="n">
-        <v>42420</v>
+        <v>70260</v>
       </c>
       <c r="Q13" t="n">
-        <v>19369.3</v>
+        <v>200722.14</v>
       </c>
     </row>
     <row r="14">
@@ -1090,7 +1090,7 @@
         <v>24180</v>
       </c>
       <c r="H14" t="n">
-        <v>720</v>
+        <v>810</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
@@ -1102,22 +1102,22 @@
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>43560</v>
+        <v>60330</v>
       </c>
       <c r="M14" t="n">
-        <v>1710</v>
+        <v>17430</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3330</v>
+        <v>3030</v>
       </c>
       <c r="P14" t="n">
-        <v>28560</v>
+        <v>38100</v>
       </c>
       <c r="Q14" t="n">
-        <v>9466.25</v>
+        <v>98097.8</v>
       </c>
     </row>
     <row r="15">
@@ -1143,7 +1143,7 @@
         <v>6420</v>
       </c>
       <c r="H15" t="n">
-        <v>390</v>
+        <v>540</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1155,22 +1155,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>18390</v>
+        <v>32130</v>
       </c>
       <c r="M15" t="n">
-        <v>930</v>
+        <v>6750</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>1080</v>
+        <v>1920</v>
       </c>
       <c r="P15" t="n">
-        <v>28320</v>
+        <v>29640</v>
       </c>
       <c r="Q15" t="n">
-        <v>3346.88</v>
+        <v>34683.43</v>
       </c>
     </row>
     <row r="16">
@@ -1196,7 +1196,7 @@
         <v>3900</v>
       </c>
       <c r="H16" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1208,22 +1208,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>8700</v>
+        <v>25650</v>
       </c>
       <c r="M16" t="n">
-        <v>840</v>
+        <v>3570</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="P16" t="n">
-        <v>40200</v>
+        <v>57780</v>
       </c>
       <c r="Q16" t="n">
-        <v>2368.82</v>
+        <v>24547.87</v>
       </c>
     </row>
     <row r="17">
@@ -1249,7 +1249,7 @@
         <v>1320</v>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1261,22 +1261,22 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>2460</v>
+        <v>9900</v>
       </c>
       <c r="M17" t="n">
-        <v>180</v>
+        <v>1860</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="P17" t="n">
-        <v>20940</v>
+        <v>32760</v>
       </c>
       <c r="Q17" t="n">
-        <v>1192.33</v>
+        <v>12356.05</v>
       </c>
     </row>
     <row r="18">
@@ -1302,7 +1302,7 @@
         <v>360</v>
       </c>
       <c r="H18" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1314,10 +1314,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>4620</v>
+        <v>9210</v>
       </c>
       <c r="M18" t="n">
-        <v>3480</v>
+        <v>4440</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1326,10 +1326,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>21000</v>
+        <v>30150</v>
       </c>
       <c r="Q18" t="n">
-        <v>579.54</v>
+        <v>6005.7</v>
       </c>
     </row>
     <row r="19">
@@ -1367,22 +1367,22 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1140</v>
+        <v>4200</v>
       </c>
       <c r="M19" t="n">
+        <v>1230</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
         <v>150</v>
       </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>60</v>
-      </c>
       <c r="P19" t="n">
-        <v>19350</v>
+        <v>31620</v>
       </c>
       <c r="Q19" t="n">
-        <v>267.62</v>
+        <v>2773.29</v>
       </c>
     </row>
     <row r="20">
@@ -1408,7 +1408,7 @@
         <v>3660</v>
       </c>
       <c r="H20" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -1420,10 +1420,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>750</v>
+        <v>2760</v>
       </c>
       <c r="M20" t="n">
-        <v>30</v>
+        <v>1500</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -1432,10 +1432,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2760</v>
+        <v>7440</v>
       </c>
       <c r="Q20" t="n">
-        <v>82.92</v>
+        <v>859.28</v>
       </c>
     </row>
     <row r="21">
@@ -1461,7 +1461,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -1473,10 +1473,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>30</v>
+        <v>480</v>
       </c>
       <c r="M21" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -1485,10 +1485,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="Q21" t="n">
-        <v>17.63</v>
+        <v>182.73</v>
       </c>
     </row>
     <row r="22">
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.34</v>
+        <v>24.29</v>
       </c>
     </row>
     <row r="23">
@@ -1579,10 +1579,10 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M23" t="n">
-        <v>210</v>
+        <v>330</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -1594,7 +1594,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>8.15</v>
+        <v>84.42</v>
       </c>
     </row>
     <row r="24">
@@ -1852,7 +1852,7 @@
         <v>8070</v>
       </c>
       <c r="H4" t="n">
-        <v>3510</v>
+        <v>3600</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -1864,22 +1864,22 @@
         <v>9</v>
       </c>
       <c r="L4" t="n">
-        <v>17280</v>
+        <v>17880</v>
       </c>
       <c r="M4" t="n">
-        <v>3510</v>
+        <v>1590</v>
       </c>
       <c r="N4" t="n">
-        <v>1140</v>
+        <v>450</v>
       </c>
       <c r="O4" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>116.45</v>
+        <v>13197.78</v>
       </c>
     </row>
     <row r="5">
@@ -1905,7 +1905,7 @@
         <v>9300</v>
       </c>
       <c r="H5" t="n">
-        <v>4050</v>
+        <v>4920</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1917,13 +1917,13 @@
         <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>20400</v>
+        <v>17700</v>
       </c>
       <c r="M5" t="n">
-        <v>6810</v>
+        <v>4950</v>
       </c>
       <c r="N5" t="n">
-        <v>150</v>
+        <v>780</v>
       </c>
       <c r="O5" t="n">
         <v>30</v>
@@ -1932,7 +1932,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>230.96</v>
+        <v>26175.24</v>
       </c>
     </row>
     <row r="6">
@@ -1958,7 +1958,7 @@
         <v>8250</v>
       </c>
       <c r="H6" t="n">
-        <v>2970</v>
+        <v>3600</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1970,22 +1970,22 @@
         <v>9</v>
       </c>
       <c r="L6" t="n">
-        <v>21300</v>
+        <v>17640</v>
       </c>
       <c r="M6" t="n">
-        <v>9000</v>
+        <v>4770</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="O6" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>569.54</v>
+        <v>64547.64</v>
       </c>
     </row>
     <row r="7">
@@ -2011,7 +2011,7 @@
         <v>8280</v>
       </c>
       <c r="H7" t="n">
-        <v>3270</v>
+        <v>2670</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -2023,22 +2023,22 @@
         <v>10</v>
       </c>
       <c r="L7" t="n">
-        <v>26490</v>
+        <v>19920</v>
       </c>
       <c r="M7" t="n">
-        <v>7380</v>
+        <v>3840</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>840</v>
+        <v>720</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>950.67</v>
+        <v>107742.6</v>
       </c>
     </row>
     <row r="8">
@@ -2064,7 +2064,7 @@
         <v>15240</v>
       </c>
       <c r="H8" t="n">
-        <v>3810</v>
+        <v>3330</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -2076,22 +2076,22 @@
         <v>11</v>
       </c>
       <c r="L8" t="n">
-        <v>36840</v>
+        <v>32730</v>
       </c>
       <c r="M8" t="n">
-        <v>6090</v>
+        <v>2160</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1231.2</v>
+        <v>139536</v>
       </c>
     </row>
     <row r="9">
@@ -2117,7 +2117,7 @@
         <v>19200</v>
       </c>
       <c r="H9" t="n">
-        <v>3690</v>
+        <v>5190</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -2129,10 +2129,10 @@
         <v>10</v>
       </c>
       <c r="L9" t="n">
-        <v>46050</v>
+        <v>41370</v>
       </c>
       <c r="M9" t="n">
-        <v>3750</v>
+        <v>2190</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -2144,7 +2144,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1264.36</v>
+        <v>143293.68</v>
       </c>
     </row>
     <row r="10">
@@ -2170,7 +2170,7 @@
         <v>18180</v>
       </c>
       <c r="H10" t="n">
-        <v>3180</v>
+        <v>2760</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -2182,22 +2182,22 @@
         <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>43650</v>
+        <v>47220</v>
       </c>
       <c r="M10" t="n">
-        <v>2520</v>
+        <v>1230</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1295.73</v>
+        <v>146849.4</v>
       </c>
     </row>
     <row r="11">
@@ -2223,7 +2223,7 @@
         <v>19140</v>
       </c>
       <c r="H11" t="n">
-        <v>4260</v>
+        <v>3810</v>
       </c>
       <c r="I11" t="n">
         <v>2</v>
@@ -2235,22 +2235,22 @@
         <v>3</v>
       </c>
       <c r="L11" t="n">
-        <v>53910</v>
+        <v>51090</v>
       </c>
       <c r="M11" t="n">
-        <v>1620</v>
+        <v>2820</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1195.45</v>
+        <v>135484.56</v>
       </c>
     </row>
     <row r="12">
@@ -2276,7 +2276,7 @@
         <v>30960</v>
       </c>
       <c r="H12" t="n">
-        <v>4980</v>
+        <v>5430</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -2288,22 +2288,22 @@
         <v>6</v>
       </c>
       <c r="L12" t="n">
-        <v>91770</v>
+        <v>91530</v>
       </c>
       <c r="M12" t="n">
-        <v>1230</v>
+        <v>3480</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1758.81</v>
+        <v>199331.46</v>
       </c>
     </row>
     <row r="13">
@@ -2329,7 +2329,7 @@
         <v>29460</v>
       </c>
       <c r="H13" t="n">
-        <v>1530</v>
+        <v>2010</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -2341,10 +2341,10 @@
         <v>5</v>
       </c>
       <c r="L13" t="n">
-        <v>71700</v>
+        <v>82080</v>
       </c>
       <c r="M13" t="n">
-        <v>390</v>
+        <v>3390</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -2356,7 +2356,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1850.71</v>
+        <v>209747.7</v>
       </c>
     </row>
     <row r="14">
@@ -2382,7 +2382,7 @@
         <v>16770</v>
       </c>
       <c r="H14" t="n">
-        <v>720</v>
+        <v>810</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
@@ -2394,10 +2394,10 @@
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>33900</v>
+        <v>39990</v>
       </c>
       <c r="M14" t="n">
-        <v>450</v>
+        <v>3630</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2409,7 +2409,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1070.82</v>
+        <v>121359.6</v>
       </c>
     </row>
     <row r="15">
@@ -2435,7 +2435,7 @@
         <v>4770</v>
       </c>
       <c r="H15" t="n">
-        <v>390</v>
+        <v>540</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -2447,10 +2447,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>14520</v>
+        <v>19890</v>
       </c>
       <c r="M15" t="n">
-        <v>240</v>
+        <v>3330</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2462,7 +2462,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>405.92</v>
+        <v>46004.04</v>
       </c>
     </row>
     <row r="16">
@@ -2488,7 +2488,7 @@
         <v>3180</v>
       </c>
       <c r="H16" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -2500,10 +2500,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>7500</v>
+        <v>13230</v>
       </c>
       <c r="M16" t="n">
-        <v>810</v>
+        <v>2430</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>322.49</v>
+        <v>36548.64</v>
       </c>
     </row>
     <row r="17">
@@ -2541,7 +2541,7 @@
         <v>630</v>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -2553,10 +2553,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1860</v>
+        <v>4380</v>
       </c>
       <c r="M17" t="n">
-        <v>60</v>
+        <v>840</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>115.37</v>
+        <v>13075.38</v>
       </c>
     </row>
     <row r="18">
@@ -2594,7 +2594,7 @@
         <v>120</v>
       </c>
       <c r="H18" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -2606,10 +2606,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>3810</v>
+        <v>5130</v>
       </c>
       <c r="M18" t="n">
-        <v>2610</v>
+        <v>3360</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2621,7 +2621,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>57.7</v>
+        <v>6539.22</v>
       </c>
     </row>
     <row r="19">
@@ -2659,10 +2659,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>660</v>
+        <v>1590</v>
       </c>
       <c r="M19" t="n">
-        <v>30</v>
+        <v>1200</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>20.98</v>
+        <v>2377.62</v>
       </c>
     </row>
     <row r="20">
@@ -2700,7 +2700,7 @@
         <v>60</v>
       </c>
       <c r="H20" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2712,10 +2712,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>750</v>
+        <v>2550</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1380</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>8.42</v>
+        <v>954.72</v>
       </c>
     </row>
     <row r="21">
@@ -2753,7 +2753,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2765,10 +2765,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>30</v>
+        <v>480</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2780,7 +2780,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.92</v>
+        <v>217.26</v>
       </c>
     </row>
     <row r="22">
@@ -2818,7 +2818,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2833,7 +2833,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.49</v>
+        <v>55.08</v>
       </c>
     </row>
     <row r="23">
@@ -2871,7 +2871,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1458</v>
+        <v>1771.2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -3209,13 +3209,13 @@
         <v>0.99</v>
       </c>
       <c r="L5" t="n">
-        <v>4284</v>
+        <v>3717</v>
       </c>
       <c r="M5" t="n">
-        <v>136.2</v>
+        <v>99</v>
       </c>
       <c r="N5" t="n">
-        <v>1.5</v>
+        <v>7.8</v>
       </c>
       <c r="O5" t="n">
         <v>1.5</v>
@@ -3224,7 +3224,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>11.55</v>
+        <v>1308.76</v>
       </c>
     </row>
     <row r="6">
@@ -3250,7 +3250,7 @@
         <v>412.5</v>
       </c>
       <c r="H6" t="n">
-        <v>1692.9</v>
+        <v>2052</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -3262,22 +3262,22 @@
         <v>4.56</v>
       </c>
       <c r="L6" t="n">
-        <v>7881</v>
+        <v>6526.8</v>
       </c>
       <c r="M6" t="n">
-        <v>720</v>
+        <v>381.6</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>427.15</v>
+        <v>48410.73</v>
       </c>
     </row>
     <row r="7">
@@ -3303,7 +3303,7 @@
         <v>1242</v>
       </c>
       <c r="H7" t="n">
-        <v>2387.1</v>
+        <v>1949.1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -3315,22 +3315,22 @@
         <v>6.38</v>
       </c>
       <c r="L7" t="n">
-        <v>15894</v>
+        <v>11952</v>
       </c>
       <c r="M7" t="n">
-        <v>2583</v>
+        <v>1344</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>294</v>
+        <v>252</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>760.54</v>
+        <v>86194.08</v>
       </c>
     </row>
     <row r="8">
@@ -3356,7 +3356,7 @@
         <v>9906</v>
       </c>
       <c r="H8" t="n">
-        <v>3238.5</v>
+        <v>2830.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -3368,22 +3368,22 @@
         <v>8.1</v>
       </c>
       <c r="L8" t="n">
-        <v>26156.4</v>
+        <v>23238.3</v>
       </c>
       <c r="M8" t="n">
-        <v>3349.5</v>
+        <v>1188</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>162</v>
+        <v>189</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1169.64</v>
+        <v>132559.2</v>
       </c>
     </row>
     <row r="9">
@@ -3409,7 +3409,7 @@
         <v>16320</v>
       </c>
       <c r="H9" t="n">
-        <v>3690</v>
+        <v>5190</v>
       </c>
       <c r="I9" t="n">
         <v>0.8</v>
@@ -3421,10 +3421,10 @@
         <v>8.029999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>37300.5</v>
+        <v>33509.7</v>
       </c>
       <c r="M9" t="n">
-        <v>2625</v>
+        <v>1533</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -3436,7 +3436,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1226.43</v>
+        <v>138994.87</v>
       </c>
     </row>
     <row r="10">
@@ -3462,7 +3462,7 @@
         <v>18180</v>
       </c>
       <c r="H10" t="n">
-        <v>3180</v>
+        <v>2760</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -3474,22 +3474,22 @@
         <v>1.74</v>
       </c>
       <c r="L10" t="n">
-        <v>38848.5</v>
+        <v>42025.8</v>
       </c>
       <c r="M10" t="n">
-        <v>2142</v>
+        <v>1045.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1295.73</v>
+        <v>146849.4</v>
       </c>
     </row>
     <row r="11">
@@ -3515,7 +3515,7 @@
         <v>19140</v>
       </c>
       <c r="H11" t="n">
-        <v>4260</v>
+        <v>3810</v>
       </c>
       <c r="I11" t="n">
         <v>1.8</v>
@@ -3527,22 +3527,22 @@
         <v>2.7</v>
       </c>
       <c r="L11" t="n">
-        <v>53910</v>
+        <v>51090</v>
       </c>
       <c r="M11" t="n">
-        <v>1458</v>
+        <v>2538</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>102</v>
+        <v>51</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1195.45</v>
+        <v>135484.56</v>
       </c>
     </row>
     <row r="12">
@@ -3568,7 +3568,7 @@
         <v>30960</v>
       </c>
       <c r="H12" t="n">
-        <v>4980</v>
+        <v>5430</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -3580,22 +3580,22 @@
         <v>5.56</v>
       </c>
       <c r="L12" t="n">
-        <v>91770</v>
+        <v>91530</v>
       </c>
       <c r="M12" t="n">
-        <v>1168.5</v>
+        <v>3306</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1758.81</v>
+        <v>199331.46</v>
       </c>
     </row>
     <row r="13">
@@ -3621,7 +3621,7 @@
         <v>29460</v>
       </c>
       <c r="H13" t="n">
-        <v>1530</v>
+        <v>2010</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -3633,10 +3633,10 @@
         <v>4.75</v>
       </c>
       <c r="L13" t="n">
-        <v>71700</v>
+        <v>82080</v>
       </c>
       <c r="M13" t="n">
-        <v>390</v>
+        <v>3390</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1850.72</v>
+        <v>209747.7</v>
       </c>
     </row>
     <row r="14">
@@ -3674,7 +3674,7 @@
         <v>16770</v>
       </c>
       <c r="H14" t="n">
-        <v>720</v>
+        <v>810</v>
       </c>
       <c r="I14" t="n">
         <v>0.97</v>
@@ -3686,10 +3686,10 @@
         <v>0.97</v>
       </c>
       <c r="L14" t="n">
-        <v>33900</v>
+        <v>39990</v>
       </c>
       <c r="M14" t="n">
-        <v>450</v>
+        <v>3630</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -3701,7 +3701,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1070.82</v>
+        <v>121359.6</v>
       </c>
     </row>
     <row r="15">
@@ -3727,7 +3727,7 @@
         <v>4770</v>
       </c>
       <c r="H15" t="n">
-        <v>390</v>
+        <v>540</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -3739,10 +3739,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>14520</v>
+        <v>19890</v>
       </c>
       <c r="M15" t="n">
-        <v>240</v>
+        <v>3330</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>405.92</v>
+        <v>46004.04</v>
       </c>
     </row>
     <row r="16">
@@ -3780,7 +3780,7 @@
         <v>3180</v>
       </c>
       <c r="H16" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -3792,10 +3792,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>7500</v>
+        <v>13230</v>
       </c>
       <c r="M16" t="n">
-        <v>810</v>
+        <v>2430</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -3807,7 +3807,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>322.49</v>
+        <v>36548.64</v>
       </c>
     </row>
     <row r="17">
@@ -3833,7 +3833,7 @@
         <v>630</v>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -3845,10 +3845,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1860</v>
+        <v>4380</v>
       </c>
       <c r="M17" t="n">
-        <v>60</v>
+        <v>840</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>115.37</v>
+        <v>13075.38</v>
       </c>
     </row>
     <row r="18">
@@ -3886,7 +3886,7 @@
         <v>120</v>
       </c>
       <c r="H18" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -3898,10 +3898,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>3810</v>
+        <v>5130</v>
       </c>
       <c r="M18" t="n">
-        <v>2610</v>
+        <v>3360</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -3913,7 +3913,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>57.7</v>
+        <v>6539.22</v>
       </c>
     </row>
     <row r="19">
@@ -3951,10 +3951,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>660</v>
+        <v>1590</v>
       </c>
       <c r="M19" t="n">
-        <v>30</v>
+        <v>1200</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -3966,7 +3966,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>20.98</v>
+        <v>2377.62</v>
       </c>
     </row>
     <row r="20">
@@ -3992,7 +3992,7 @@
         <v>60</v>
       </c>
       <c r="H20" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -4004,10 +4004,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>750</v>
+        <v>2550</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1380</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -4019,7 +4019,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>8.42</v>
+        <v>954.72</v>
       </c>
     </row>
     <row r="21">
@@ -4045,7 +4045,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -4057,10 +4057,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>30</v>
+        <v>480</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -4072,7 +4072,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.92</v>
+        <v>217.26</v>
       </c>
     </row>
     <row r="22">
@@ -4110,7 +4110,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -4125,7 +4125,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.49</v>
+        <v>55.08</v>
       </c>
     </row>
     <row r="23">
@@ -4163,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>8310600</v>
+        <v>10095840</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -4501,13 +4501,13 @@
         <v>48216.11</v>
       </c>
       <c r="L5" t="n">
-        <v>771120</v>
+        <v>669060</v>
       </c>
       <c r="M5" t="n">
-        <v>47670</v>
+        <v>34650</v>
       </c>
       <c r="N5" t="n">
-        <v>255</v>
+        <v>1326</v>
       </c>
       <c r="O5" t="n">
         <v>255</v>
@@ -4516,7 +4516,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>6928.74</v>
+        <v>785257.2</v>
       </c>
     </row>
     <row r="6">
@@ -4542,7 +4542,7 @@
         <v>22275</v>
       </c>
       <c r="H6" t="n">
-        <v>9649530</v>
+        <v>11696400</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -4554,22 +4554,22 @@
         <v>221561.03</v>
       </c>
       <c r="L6" t="n">
-        <v>1418580</v>
+        <v>1174824</v>
       </c>
       <c r="M6" t="n">
-        <v>252000</v>
+        <v>133560</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1275</v>
       </c>
       <c r="O6" t="n">
-        <v>2550</v>
+        <v>1275</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>256292.1</v>
+        <v>29046438</v>
       </c>
     </row>
     <row r="7">
@@ -4595,7 +4595,7 @@
         <v>67068</v>
       </c>
       <c r="H7" t="n">
-        <v>13606470</v>
+        <v>11109870</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -4607,22 +4607,22 @@
         <v>309787.28</v>
       </c>
       <c r="L7" t="n">
-        <v>2860920</v>
+        <v>2151360</v>
       </c>
       <c r="M7" t="n">
-        <v>904050</v>
+        <v>470400</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>49980</v>
+        <v>42840</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>456321.6</v>
+        <v>51716448</v>
       </c>
     </row>
     <row r="8">
@@ -4648,7 +4648,7 @@
         <v>534924</v>
       </c>
       <c r="H8" t="n">
-        <v>18459450</v>
+        <v>16133850</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -4660,22 +4660,22 @@
         <v>393109.38</v>
       </c>
       <c r="L8" t="n">
-        <v>4708152</v>
+        <v>4182894</v>
       </c>
       <c r="M8" t="n">
-        <v>1172325</v>
+        <v>415800</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>27540</v>
+        <v>32130</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>701784</v>
+        <v>79535520</v>
       </c>
     </row>
     <row r="9">
@@ -4701,7 +4701,7 @@
         <v>881280</v>
       </c>
       <c r="H9" t="n">
-        <v>21033000</v>
+        <v>29583000</v>
       </c>
       <c r="I9" t="n">
         <v>155961.87</v>
@@ -4713,10 +4713,10 @@
         <v>389904.68</v>
       </c>
       <c r="L9" t="n">
-        <v>6714090</v>
+        <v>6031746</v>
       </c>
       <c r="M9" t="n">
-        <v>918750</v>
+        <v>536550</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -4728,7 +4728,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>735855.1899999999</v>
+        <v>83396921.76000001</v>
       </c>
     </row>
     <row r="10">
@@ -4754,7 +4754,7 @@
         <v>981720</v>
       </c>
       <c r="H10" t="n">
-        <v>18126000</v>
+        <v>15732000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -4766,22 +4766,22 @@
         <v>84487.44</v>
       </c>
       <c r="L10" t="n">
-        <v>6992730</v>
+        <v>7564644</v>
       </c>
       <c r="M10" t="n">
-        <v>749700</v>
+        <v>365925</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>14280</v>
+        <v>28560</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>777438</v>
+        <v>88109640</v>
       </c>
     </row>
     <row r="11">
@@ -4807,7 +4807,7 @@
         <v>1033560</v>
       </c>
       <c r="H11" t="n">
-        <v>24282000</v>
+        <v>21717000</v>
       </c>
       <c r="I11" t="n">
         <v>349020.53</v>
@@ -4819,22 +4819,22 @@
         <v>130882.7</v>
       </c>
       <c r="L11" t="n">
-        <v>9703800</v>
+        <v>9196200</v>
       </c>
       <c r="M11" t="n">
-        <v>510300</v>
+        <v>888300</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>17340</v>
+        <v>8670</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>717271.2</v>
+        <v>81290736</v>
       </c>
     </row>
     <row r="12">
@@ -4860,7 +4860,7 @@
         <v>1671840</v>
       </c>
       <c r="H12" t="n">
-        <v>28386000</v>
+        <v>30951000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -4872,22 +4872,22 @@
         <v>270068.47</v>
       </c>
       <c r="L12" t="n">
-        <v>16518600</v>
+        <v>16475400</v>
       </c>
       <c r="M12" t="n">
-        <v>408975</v>
+        <v>1157100</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>30600</v>
+        <v>40800</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1055284.2</v>
+        <v>119598876</v>
       </c>
     </row>
     <row r="13">
@@ -4913,7 +4913,7 @@
         <v>1590840</v>
       </c>
       <c r="H13" t="n">
-        <v>8721000</v>
+        <v>11457000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -4925,10 +4925,10 @@
         <v>230519.61</v>
       </c>
       <c r="L13" t="n">
-        <v>12906000</v>
+        <v>14774400</v>
       </c>
       <c r="M13" t="n">
-        <v>136500</v>
+        <v>1186500</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -4940,7 +4940,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1110429</v>
+        <v>125848620</v>
       </c>
     </row>
     <row r="14">
@@ -4966,7 +4966,7 @@
         <v>905580</v>
       </c>
       <c r="H14" t="n">
-        <v>4104000</v>
+        <v>4617000</v>
       </c>
       <c r="I14" t="n">
         <v>188785.73</v>
@@ -4978,10 +4978,10 @@
         <v>47196.43</v>
       </c>
       <c r="L14" t="n">
-        <v>6102000</v>
+        <v>7198200</v>
       </c>
       <c r="M14" t="n">
-        <v>157500</v>
+        <v>1270500</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -4993,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>642492</v>
+        <v>72815760</v>
       </c>
     </row>
     <row r="15">
@@ -5019,7 +5019,7 @@
         <v>257580</v>
       </c>
       <c r="H15" t="n">
-        <v>2223000</v>
+        <v>3078000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -5031,10 +5031,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>2613600</v>
+        <v>3580200</v>
       </c>
       <c r="M15" t="n">
-        <v>84000</v>
+        <v>1165500</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -5046,7 +5046,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>243550.8</v>
+        <v>27602424</v>
       </c>
     </row>
     <row r="16">
@@ -5072,7 +5072,7 @@
         <v>171720</v>
       </c>
       <c r="H16" t="n">
-        <v>684000</v>
+        <v>855000</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -5084,10 +5084,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1350000</v>
+        <v>2381400</v>
       </c>
       <c r="M16" t="n">
-        <v>283500</v>
+        <v>850500</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -5099,7 +5099,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>193492.8</v>
+        <v>21929184</v>
       </c>
     </row>
     <row r="17">
@@ -5125,7 +5125,7 @@
         <v>34020</v>
       </c>
       <c r="H17" t="n">
-        <v>342000</v>
+        <v>855000</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -5137,10 +5137,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>334800</v>
+        <v>788400</v>
       </c>
       <c r="M17" t="n">
-        <v>21000</v>
+        <v>294000</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -5152,7 +5152,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>69222.60000000001</v>
+        <v>7845228</v>
       </c>
     </row>
     <row r="18">
@@ -5178,7 +5178,7 @@
         <v>6480</v>
       </c>
       <c r="H18" t="n">
-        <v>342000</v>
+        <v>684000</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -5190,10 +5190,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>685800</v>
+        <v>923400</v>
       </c>
       <c r="M18" t="n">
-        <v>913500</v>
+        <v>1176000</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -5205,7 +5205,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>34619.4</v>
+        <v>3923532</v>
       </c>
     </row>
     <row r="19">
@@ -5243,10 +5243,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>118800</v>
+        <v>286200</v>
       </c>
       <c r="M19" t="n">
-        <v>10500</v>
+        <v>420000</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -5258,7 +5258,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>12587.4</v>
+        <v>1426572</v>
       </c>
     </row>
     <row r="20">
@@ -5284,7 +5284,7 @@
         <v>3240</v>
       </c>
       <c r="H20" t="n">
-        <v>342000</v>
+        <v>171000</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -5296,10 +5296,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>135000</v>
+        <v>459000</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>483000</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -5311,7 +5311,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>5054.4</v>
+        <v>572832</v>
       </c>
     </row>
     <row r="21">
@@ -5337,7 +5337,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>513000</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -5349,10 +5349,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>5400</v>
+        <v>86400</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>105000</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -5364,7 +5364,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1150.2</v>
+        <v>130356</v>
       </c>
     </row>
     <row r="22">
@@ -5402,7 +5402,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -5417,7 +5417,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>291.6</v>
+        <v>33048</v>
       </c>
     </row>
     <row r="23">
@@ -5455,7 +5455,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -5728,7 +5728,7 @@
         <v>48120</v>
       </c>
       <c r="H4" t="n">
-        <v>8340</v>
+        <v>9750</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -5740,22 +5740,22 @@
         <v>40</v>
       </c>
       <c r="L4" t="n">
-        <v>145890</v>
+        <v>165240</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>9690</v>
+        <v>9600</v>
       </c>
       <c r="O4" t="n">
-        <v>20370</v>
+        <v>21390</v>
       </c>
       <c r="P4" t="n">
-        <v>11490</v>
+        <v>7950</v>
       </c>
       <c r="Q4" t="n">
-        <v>27167.25</v>
+        <v>142985.52</v>
       </c>
     </row>
     <row r="5">
@@ -5781,7 +5781,7 @@
         <v>18630</v>
       </c>
       <c r="H5" t="n">
-        <v>2640</v>
+        <v>3930</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
         <v>15</v>
       </c>
       <c r="L5" t="n">
-        <v>58680</v>
+        <v>76530</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>11550</v>
+        <v>12690</v>
       </c>
       <c r="O5" t="n">
-        <v>9000</v>
+        <v>13620</v>
       </c>
       <c r="P5" t="n">
-        <v>9150</v>
+        <v>11970</v>
       </c>
       <c r="Q5" t="n">
-        <v>12040.52</v>
+        <v>63371.16</v>
       </c>
     </row>
     <row r="6">
@@ -5834,7 +5834,7 @@
         <v>2280</v>
       </c>
       <c r="H6" t="n">
-        <v>360</v>
+        <v>630</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -5846,22 +5846,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>11220</v>
+        <v>17160</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
+        <v>2610</v>
+      </c>
+      <c r="O6" t="n">
         <v>1290</v>
       </c>
-      <c r="O6" t="n">
-        <v>420</v>
-      </c>
       <c r="P6" t="n">
-        <v>6000</v>
+        <v>8790</v>
       </c>
       <c r="Q6" t="n">
-        <v>1327.85</v>
+        <v>6988.68</v>
       </c>
     </row>
     <row r="7">
@@ -5887,7 +5887,7 @@
         <v>630</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -5899,7 +5899,7 @@
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>3090</v>
+        <v>4890</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -5911,10 +5911,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>5610</v>
+        <v>8730</v>
       </c>
       <c r="Q7" t="n">
-        <v>105.06</v>
+        <v>552.96</v>
       </c>
     </row>
     <row r="8">
@@ -5952,7 +5952,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>480</v>
+        <v>1920</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -5964,10 +5964,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>5220</v>
+        <v>9960</v>
       </c>
       <c r="Q8" t="n">
-        <v>48.02</v>
+        <v>252.72</v>
       </c>
     </row>
     <row r="9">
@@ -6005,7 +6005,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>180</v>
+        <v>1020</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -6017,10 +6017,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>4290</v>
+        <v>10080</v>
       </c>
       <c r="Q9" t="n">
-        <v>24.42</v>
+        <v>128.52</v>
       </c>
     </row>
     <row r="10">
@@ -6058,7 +6058,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -6070,10 +6070,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2010</v>
+        <v>5490</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.52</v>
+        <v>65.88</v>
       </c>
     </row>
     <row r="11">
@@ -7073,7 +7073,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>950.4</v>
+        <v>1414.8</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -7085,22 +7085,22 @@
         <v>4.96</v>
       </c>
       <c r="L5" t="n">
-        <v>12322.8</v>
+        <v>16071.3</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>115.5</v>
+        <v>126.9</v>
       </c>
       <c r="O5" t="n">
-        <v>450</v>
+        <v>681</v>
       </c>
       <c r="P5" t="n">
-        <v>183</v>
+        <v>239.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>602.03</v>
+        <v>3168.56</v>
       </c>
     </row>
     <row r="6">
@@ -7126,7 +7126,7 @@
         <v>114</v>
       </c>
       <c r="H6" t="n">
-        <v>205.2</v>
+        <v>359.1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -7138,22 +7138,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>4151.4</v>
+        <v>6349.2</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>64.5</v>
+        <v>130.5</v>
       </c>
       <c r="O6" t="n">
-        <v>105</v>
+        <v>322.5</v>
       </c>
       <c r="P6" t="n">
-        <v>900</v>
+        <v>1318.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>995.89</v>
+        <v>5241.51</v>
       </c>
     </row>
     <row r="7">
@@ -7179,7 +7179,7 @@
         <v>94.5</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>175.2</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -7191,7 +7191,7 @@
         <v>0.64</v>
       </c>
       <c r="L7" t="n">
-        <v>1854</v>
+        <v>2934</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -7203,10 +7203,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1402.5</v>
+        <v>2182.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>84.05</v>
+        <v>442.37</v>
       </c>
     </row>
     <row r="8">
@@ -7244,7 +7244,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>340.8</v>
+        <v>1363.2</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -7256,10 +7256,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1983.6</v>
+        <v>3784.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>45.62</v>
+        <v>240.08</v>
       </c>
     </row>
     <row r="9">
@@ -7297,7 +7297,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>145.8</v>
+        <v>826.2</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -7309,10 +7309,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2145</v>
+        <v>5040</v>
       </c>
       <c r="Q9" t="n">
-        <v>23.69</v>
+        <v>124.66</v>
       </c>
     </row>
     <row r="10">
@@ -7350,7 +7350,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>186.9</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -7362,10 +7362,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1708.5</v>
+        <v>4666.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.52</v>
+        <v>65.88</v>
       </c>
     </row>
     <row r="11">
@@ -8365,7 +8365,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>5417280</v>
+        <v>8064360</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -8377,22 +8377,22 @@
         <v>241080.54</v>
       </c>
       <c r="L5" t="n">
-        <v>2218104</v>
+        <v>2892834</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>19635</v>
+        <v>21573</v>
       </c>
       <c r="O5" t="n">
-        <v>76500</v>
+        <v>115770</v>
       </c>
       <c r="P5" t="n">
-        <v>11895</v>
+        <v>15561</v>
       </c>
       <c r="Q5" t="n">
-        <v>361215.61</v>
+        <v>1901134.8</v>
       </c>
     </row>
     <row r="6">
@@ -8418,7 +8418,7 @@
         <v>6156</v>
       </c>
       <c r="H6" t="n">
-        <v>1169640</v>
+        <v>2046870</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -8430,22 +8430,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>747252</v>
+        <v>1142856</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>10965</v>
+        <v>22185</v>
       </c>
       <c r="O6" t="n">
-        <v>17850</v>
+        <v>54825</v>
       </c>
       <c r="P6" t="n">
-        <v>58500</v>
+        <v>85702.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>597532.14</v>
+        <v>3144906</v>
       </c>
     </row>
     <row r="7">
@@ -8471,7 +8471,7 @@
         <v>5103</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>998640</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -8483,7 +8483,7 @@
         <v>30978.73</v>
       </c>
       <c r="L7" t="n">
-        <v>333720</v>
+        <v>528120</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -8495,10 +8495,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>91162.5</v>
+        <v>141862.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>50429.95</v>
+        <v>265420.8</v>
       </c>
     </row>
     <row r="8">
@@ -8536,7 +8536,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>61344</v>
+        <v>245376</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -8548,10 +8548,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>128934</v>
+        <v>246012</v>
       </c>
       <c r="Q8" t="n">
-        <v>27369.58</v>
+        <v>144050.4</v>
       </c>
     </row>
     <row r="9">
@@ -8589,7 +8589,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>26244</v>
+        <v>148716</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -8601,10 +8601,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>139425</v>
+        <v>327600</v>
       </c>
       <c r="Q9" t="n">
-        <v>14211.74</v>
+        <v>74798.64</v>
       </c>
     </row>
     <row r="10">
@@ -8642,7 +8642,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>33642</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -8654,10 +8654,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>111052.5</v>
+        <v>303322.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>7510.32</v>
+        <v>39528</v>
       </c>
     </row>
     <row r="11">
@@ -9604,7 +9604,7 @@
         <v>86910</v>
       </c>
       <c r="H4" t="n">
-        <v>5280</v>
+        <v>6210</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -9616,13 +9616,13 @@
         <v>37</v>
       </c>
       <c r="L4" t="n">
-        <v>138300</v>
+        <v>159630</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>22890</v>
+        <v>23520</v>
       </c>
       <c r="O4" t="n">
         <v>32850</v>
@@ -9631,7 +9631,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>33305.37</v>
+        <v>180726.84</v>
       </c>
     </row>
     <row r="5">
@@ -9657,7 +9657,7 @@
         <v>25860</v>
       </c>
       <c r="H5" t="n">
-        <v>3810</v>
+        <v>4290</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -9669,22 +9669,22 @@
         <v>11</v>
       </c>
       <c r="L5" t="n">
-        <v>48690</v>
+        <v>56400</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>8730</v>
+        <v>11580</v>
       </c>
       <c r="O5" t="n">
-        <v>28770</v>
+        <v>28080</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>9424.299999999999</v>
+        <v>51139.62</v>
       </c>
     </row>
     <row r="6">
@@ -9710,7 +9710,7 @@
         <v>7980</v>
       </c>
       <c r="H6" t="n">
-        <v>1440</v>
+        <v>1890</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -9722,22 +9722,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>13890</v>
+        <v>21840</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4080</v>
+        <v>4650</v>
       </c>
       <c r="O6" t="n">
-        <v>25440</v>
+        <v>26430</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1538.56</v>
+        <v>8348.76</v>
       </c>
     </row>
     <row r="7">
@@ -9763,7 +9763,7 @@
         <v>2910</v>
       </c>
       <c r="H7" t="n">
-        <v>240</v>
+        <v>570</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -9775,22 +9775,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3780</v>
+        <v>7740</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1650</v>
+        <v>3240</v>
       </c>
       <c r="O7" t="n">
-        <v>11970</v>
+        <v>15960</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>320.32</v>
+        <v>1738.17</v>
       </c>
     </row>
     <row r="8">
@@ -9816,7 +9816,7 @@
         <v>780</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -9828,22 +9828,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2040</v>
+        <v>3510</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>270</v>
+        <v>900</v>
       </c>
       <c r="O8" t="n">
-        <v>2790</v>
+        <v>5250</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>118.65</v>
+        <v>643.86</v>
       </c>
     </row>
     <row r="9">
@@ -9881,22 +9881,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="O9" t="n">
-        <v>510</v>
+        <v>960</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.97</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="10">
@@ -10949,7 +10949,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1371.6</v>
+        <v>1544.4</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -10961,22 +10961,22 @@
         <v>3.64</v>
       </c>
       <c r="L5" t="n">
-        <v>10224.9</v>
+        <v>11844</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>87.3</v>
+        <v>115.8</v>
       </c>
       <c r="O5" t="n">
-        <v>1438.5</v>
+        <v>1404</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>471.22</v>
+        <v>2556.98</v>
       </c>
     </row>
     <row r="6">
@@ -11002,7 +11002,7 @@
         <v>399</v>
       </c>
       <c r="H6" t="n">
-        <v>820.8</v>
+        <v>1077.3</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -11014,22 +11014,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>5139.3</v>
+        <v>8080.8</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>204</v>
+        <v>232.5</v>
       </c>
       <c r="O6" t="n">
-        <v>6360</v>
+        <v>6607.5</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1153.92</v>
+        <v>6261.57</v>
       </c>
     </row>
     <row r="7">
@@ -11055,7 +11055,7 @@
         <v>436.5</v>
       </c>
       <c r="H7" t="n">
-        <v>175.2</v>
+        <v>416.1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -11067,22 +11067,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>2268</v>
+        <v>4644</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>115.5</v>
+        <v>226.8</v>
       </c>
       <c r="O7" t="n">
-        <v>4189.5</v>
+        <v>5586</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>256.26</v>
+        <v>1390.54</v>
       </c>
     </row>
     <row r="8">
@@ -11108,7 +11108,7 @@
         <v>507</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -11120,22 +11120,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1448.4</v>
+        <v>2492.1</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>54</v>
+        <v>180</v>
       </c>
       <c r="O8" t="n">
-        <v>1255.5</v>
+        <v>2362.5</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>112.72</v>
+        <v>611.67</v>
       </c>
     </row>
     <row r="9">
@@ -11173,22 +11173,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>97.2</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O9" t="n">
-        <v>280.5</v>
+        <v>528</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.76</v>
+        <v>36.67</v>
       </c>
     </row>
     <row r="10">
@@ -12241,7 +12241,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>7818120</v>
+        <v>8803080</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -12253,22 +12253,22 @@
         <v>176792.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1840482</v>
+        <v>2131920</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>14841</v>
+        <v>19686</v>
       </c>
       <c r="O5" t="n">
-        <v>244545</v>
+        <v>238680</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>282729.04</v>
+        <v>1534188.6</v>
       </c>
     </row>
     <row r="6">
@@ -12294,7 +12294,7 @@
         <v>21546</v>
       </c>
       <c r="H6" t="n">
-        <v>4678560</v>
+        <v>6140610</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -12306,22 +12306,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>925074</v>
+        <v>1454544</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>34680</v>
+        <v>39525</v>
       </c>
       <c r="O6" t="n">
-        <v>1081200</v>
+        <v>1123275</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>692350.74</v>
+        <v>3756942</v>
       </c>
     </row>
     <row r="7">
@@ -12347,7 +12347,7 @@
         <v>23571</v>
       </c>
       <c r="H7" t="n">
-        <v>998640</v>
+        <v>2371770</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -12359,22 +12359,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>408240</v>
+        <v>835920</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>19635</v>
+        <v>38556</v>
       </c>
       <c r="O7" t="n">
-        <v>712215</v>
+        <v>949620</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>153753.55</v>
+        <v>834321.6</v>
       </c>
     </row>
     <row r="8">
@@ -12400,7 +12400,7 @@
         <v>27378</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>290700</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -12412,22 +12412,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>260712</v>
+        <v>448578</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>9180</v>
+        <v>30600</v>
       </c>
       <c r="O8" t="n">
-        <v>213435</v>
+        <v>401625</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>67632.89</v>
+        <v>367000.2</v>
       </c>
     </row>
     <row r="9">
@@ -12465,22 +12465,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>17496</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3060</v>
       </c>
       <c r="O9" t="n">
-        <v>47685</v>
+        <v>89760</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4054.21</v>
+        <v>21999.6</v>
       </c>
     </row>
     <row r="10">
@@ -13480,7 +13480,7 @@
         <v>83580</v>
       </c>
       <c r="H4" t="n">
-        <v>7050</v>
+        <v>8010</v>
       </c>
       <c r="I4" t="n">
         <v>5</v>
@@ -13492,19 +13492,19 @@
         <v>131</v>
       </c>
       <c r="L4" t="n">
-        <v>172410</v>
+        <v>177570</v>
       </c>
       <c r="M4" t="n">
-        <v>12150</v>
+        <v>150</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>33960</v>
+        <v>37530</v>
       </c>
       <c r="P4" t="n">
-        <v>17850</v>
+        <v>3450</v>
       </c>
       <c r="Q4" t="n">
         <v>35556.99</v>
@@ -13533,7 +13533,7 @@
         <v>67140</v>
       </c>
       <c r="H5" t="n">
-        <v>6210</v>
+        <v>6480</v>
       </c>
       <c r="I5" t="n">
         <v>4</v>
@@ -13545,19 +13545,19 @@
         <v>88</v>
       </c>
       <c r="L5" t="n">
-        <v>162240</v>
+        <v>152640</v>
       </c>
       <c r="M5" t="n">
-        <v>18450</v>
+        <v>1170</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>31470</v>
+        <v>37620</v>
       </c>
       <c r="P5" t="n">
-        <v>29010</v>
+        <v>10860</v>
       </c>
       <c r="Q5" t="n">
         <v>29786.82</v>
@@ -13586,7 +13586,7 @@
         <v>68070</v>
       </c>
       <c r="H6" t="n">
-        <v>7710</v>
+        <v>7350</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -13598,19 +13598,19 @@
         <v>76</v>
       </c>
       <c r="L6" t="n">
-        <v>156300</v>
+        <v>134850</v>
       </c>
       <c r="M6" t="n">
-        <v>14250</v>
+        <v>2100</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>20880</v>
+        <v>22020</v>
       </c>
       <c r="P6" t="n">
-        <v>30270</v>
+        <v>17340</v>
       </c>
       <c r="Q6" t="n">
         <v>30273.29</v>
@@ -13639,7 +13639,7 @@
         <v>88650</v>
       </c>
       <c r="H7" t="n">
-        <v>11820</v>
+        <v>12450</v>
       </c>
       <c r="I7" t="n">
         <v>2</v>
@@ -13651,19 +13651,19 @@
         <v>72</v>
       </c>
       <c r="L7" t="n">
-        <v>202470</v>
+        <v>189180</v>
       </c>
       <c r="M7" t="n">
-        <v>9450</v>
+        <v>4350</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>19920</v>
+        <v>19290</v>
       </c>
       <c r="P7" t="n">
-        <v>33510</v>
+        <v>23580</v>
       </c>
       <c r="Q7" t="n">
         <v>41668.09</v>
@@ -13692,7 +13692,7 @@
         <v>58440</v>
       </c>
       <c r="H8" t="n">
-        <v>2610</v>
+        <v>3270</v>
       </c>
       <c r="I8" t="n">
         <v>2</v>
@@ -13704,19 +13704,19 @@
         <v>42</v>
       </c>
       <c r="L8" t="n">
-        <v>127230</v>
+        <v>123270</v>
       </c>
       <c r="M8" t="n">
-        <v>5790</v>
+        <v>6060</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>18450</v>
+        <v>18150</v>
       </c>
       <c r="P8" t="n">
-        <v>35340</v>
+        <v>30540</v>
       </c>
       <c r="Q8" t="n">
         <v>34431.84</v>
@@ -13745,7 +13745,7 @@
         <v>34140</v>
       </c>
       <c r="H9" t="n">
-        <v>270</v>
+        <v>450</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -13757,19 +13757,19 @@
         <v>34</v>
       </c>
       <c r="L9" t="n">
-        <v>74640</v>
+        <v>84270</v>
       </c>
       <c r="M9" t="n">
-        <v>3540</v>
+        <v>13770</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>27210</v>
+        <v>26220</v>
       </c>
       <c r="P9" t="n">
-        <v>32580</v>
+        <v>31590</v>
       </c>
       <c r="Q9" t="n">
         <v>29058.74</v>
@@ -13810,19 +13810,19 @@
         <v>5</v>
       </c>
       <c r="L10" t="n">
-        <v>39240</v>
+        <v>45450</v>
       </c>
       <c r="M10" t="n">
-        <v>1800</v>
+        <v>8910</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>10920</v>
+        <v>16410</v>
       </c>
       <c r="P10" t="n">
-        <v>36990</v>
+        <v>40650</v>
       </c>
       <c r="Q10" t="n">
         <v>16158.01</v>
@@ -13863,19 +13863,19 @@
         <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>10200</v>
+        <v>24720</v>
       </c>
       <c r="M11" t="n">
-        <v>780</v>
+        <v>10620</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>930</v>
+        <v>1950</v>
       </c>
       <c r="P11" t="n">
-        <v>32310</v>
+        <v>35730</v>
       </c>
       <c r="Q11" t="n">
         <v>1949.65</v>
@@ -13904,7 +13904,7 @@
         <v>1230</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -13916,19 +13916,19 @@
         <v>2</v>
       </c>
       <c r="L12" t="n">
-        <v>4740</v>
+        <v>34740</v>
       </c>
       <c r="M12" t="n">
-        <v>390</v>
+        <v>9750</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P12" t="n">
-        <v>31080</v>
+        <v>50100</v>
       </c>
       <c r="Q12" t="n">
         <v>427.54</v>
@@ -13969,10 +13969,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>3300</v>
+        <v>19650</v>
       </c>
       <c r="M13" t="n">
-        <v>270</v>
+        <v>5580</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -13981,7 +13981,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>23820</v>
+        <v>42060</v>
       </c>
       <c r="Q13" t="n">
         <v>224.65</v>
@@ -14022,10 +14022,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1050</v>
+        <v>6180</v>
       </c>
       <c r="M14" t="n">
-        <v>360</v>
+        <v>8790</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -14034,7 +14034,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>13500</v>
+        <v>22860</v>
       </c>
       <c r="Q14" t="n">
         <v>137.49</v>
@@ -14075,10 +14075,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>900</v>
+        <v>3780</v>
       </c>
       <c r="M15" t="n">
-        <v>180</v>
+        <v>1260</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -14087,7 +14087,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>10860</v>
+        <v>11610</v>
       </c>
       <c r="Q15" t="n">
         <v>14.84</v>
@@ -14128,10 +14128,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>240</v>
+        <v>5970</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -14140,7 +14140,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>12690</v>
+        <v>21240</v>
       </c>
       <c r="Q16" t="n">
         <v>22.21</v>
@@ -14181,10 +14181,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>390</v>
+        <v>3060</v>
       </c>
       <c r="M17" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -14193,7 +14193,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>10230</v>
+        <v>23160</v>
       </c>
       <c r="Q17" t="n">
         <v>13.39</v>
@@ -14234,10 +14234,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>600</v>
+        <v>2670</v>
       </c>
       <c r="M18" t="n">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -14246,7 +14246,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>3840</v>
+        <v>8880</v>
       </c>
       <c r="Q18" t="n">
         <v>6.47</v>
@@ -14287,7 +14287,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>360</v>
+        <v>1200</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -14299,7 +14299,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>690</v>
+        <v>1230</v>
       </c>
       <c r="Q19" t="n">
         <v>2.01</v>
@@ -14340,7 +14340,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -14825,7 +14825,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>19353.6</v>
+        <v>21157.2</v>
       </c>
       <c r="I5" t="n">
         <v>1.66</v>
@@ -14837,22 +14837,22 @@
         <v>86.72</v>
       </c>
       <c r="L5" t="n">
-        <v>186612.3</v>
+        <v>197731.8</v>
       </c>
       <c r="M5" t="n">
-        <v>1011</v>
+        <v>774.6</v>
       </c>
       <c r="N5" t="n">
-        <v>752.1</v>
+        <v>868.8</v>
       </c>
       <c r="O5" t="n">
-        <v>9120</v>
+        <v>10416</v>
       </c>
       <c r="P5" t="n">
-        <v>1049.4</v>
+        <v>679.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>6866.05</v>
+        <v>71152.22</v>
       </c>
     </row>
     <row r="6">
@@ -14878,7 +14878,7 @@
         <v>11764.5</v>
       </c>
       <c r="H6" t="n">
-        <v>26180.1</v>
+        <v>26556.3</v>
       </c>
       <c r="I6" t="n">
         <v>0.51</v>
@@ -14890,22 +14890,22 @@
         <v>83.66</v>
       </c>
       <c r="L6" t="n">
-        <v>212809.2</v>
+        <v>212631.6</v>
       </c>
       <c r="M6" t="n">
-        <v>2704.8</v>
+        <v>1833.6</v>
       </c>
       <c r="N6" t="n">
-        <v>1347</v>
+        <v>1899</v>
       </c>
       <c r="O6" t="n">
-        <v>28605</v>
+        <v>31260</v>
       </c>
       <c r="P6" t="n">
-        <v>7695</v>
+        <v>5620.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>71299.50999999999</v>
+        <v>738869.92</v>
       </c>
     </row>
     <row r="7">
@@ -14931,7 +14931,7 @@
         <v>31635</v>
       </c>
       <c r="H7" t="n">
-        <v>31163.7</v>
+        <v>33047.1</v>
       </c>
       <c r="I7" t="n">
         <v>1.28</v>
@@ -14943,22 +14943,22 @@
         <v>96.98</v>
       </c>
       <c r="L7" t="n">
-        <v>320040</v>
+        <v>319932</v>
       </c>
       <c r="M7" t="n">
-        <v>8263.5</v>
+        <v>9145.5</v>
       </c>
       <c r="N7" t="n">
-        <v>678.3</v>
+        <v>1010.1</v>
       </c>
       <c r="O7" t="n">
-        <v>29253</v>
+        <v>31426.5</v>
       </c>
       <c r="P7" t="n">
-        <v>15450</v>
+        <v>11130</v>
       </c>
       <c r="Q7" t="n">
-        <v>74666.92</v>
+        <v>773766.04</v>
       </c>
     </row>
     <row r="8">
@@ -14984,7 +14984,7 @@
         <v>114328.5</v>
       </c>
       <c r="H8" t="n">
-        <v>23460</v>
+        <v>24403.5</v>
       </c>
       <c r="I8" t="n">
         <v>2.21</v>
@@ -14996,22 +14996,22 @@
         <v>75.06999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>313962</v>
+        <v>311427.3</v>
       </c>
       <c r="M8" t="n">
-        <v>10230</v>
+        <v>14388</v>
       </c>
       <c r="N8" t="n">
-        <v>426</v>
+        <v>870</v>
       </c>
       <c r="O8" t="n">
-        <v>27351</v>
+        <v>29092.5</v>
       </c>
       <c r="P8" t="n">
-        <v>26334</v>
+        <v>20964.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>74444.81</v>
+        <v>771464.3199999999</v>
       </c>
     </row>
     <row r="9">
@@ -15037,7 +15037,7 @@
         <v>132829.5</v>
       </c>
       <c r="H9" t="n">
-        <v>9450</v>
+        <v>12090</v>
       </c>
       <c r="I9" t="n">
         <v>0.8</v>
@@ -15049,22 +15049,22 @@
         <v>88.33</v>
       </c>
       <c r="L9" t="n">
-        <v>305183.7</v>
+        <v>318159.9</v>
       </c>
       <c r="M9" t="n">
-        <v>8001</v>
+        <v>23394</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O9" t="n">
-        <v>30244.5</v>
+        <v>35392.5</v>
       </c>
       <c r="P9" t="n">
-        <v>33885</v>
+        <v>31200</v>
       </c>
       <c r="Q9" t="n">
-        <v>72656.25</v>
+        <v>752929.71</v>
       </c>
     </row>
     <row r="10">
@@ -15090,7 +15090,7 @@
         <v>141930</v>
       </c>
       <c r="H10" t="n">
-        <v>3720</v>
+        <v>3480</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -15102,22 +15102,22 @@
         <v>51.33</v>
       </c>
       <c r="L10" t="n">
-        <v>266519.4</v>
+        <v>293246.1</v>
       </c>
       <c r="M10" t="n">
-        <v>7905</v>
+        <v>20374.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>23520</v>
+        <v>32991</v>
       </c>
       <c r="P10" t="n">
-        <v>65433</v>
+        <v>65764.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>61927.73</v>
+        <v>641751.1</v>
       </c>
     </row>
     <row r="11">
@@ -15143,7 +15143,7 @@
         <v>78990</v>
       </c>
       <c r="H11" t="n">
-        <v>4680</v>
+        <v>4500</v>
       </c>
       <c r="I11" t="n">
         <v>2.7</v>
@@ -15155,22 +15155,22 @@
         <v>31.45</v>
       </c>
       <c r="L11" t="n">
-        <v>187320</v>
+        <v>224910</v>
       </c>
       <c r="M11" t="n">
-        <v>5508</v>
+        <v>22464</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>10429.5</v>
+        <v>19354.5</v>
       </c>
       <c r="P11" t="n">
-        <v>65313</v>
+        <v>80379</v>
       </c>
       <c r="Q11" t="n">
-        <v>40121.43</v>
+        <v>415774.47</v>
       </c>
     </row>
     <row r="12">
@@ -15196,7 +15196,7 @@
         <v>60480</v>
       </c>
       <c r="H12" t="n">
-        <v>5040</v>
+        <v>5850</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -15208,22 +15208,22 @@
         <v>15.76</v>
       </c>
       <c r="L12" t="n">
-        <v>151590</v>
+        <v>198930</v>
       </c>
       <c r="M12" t="n">
-        <v>3591</v>
+        <v>20577</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4590</v>
+        <v>12540</v>
       </c>
       <c r="P12" t="n">
-        <v>59610</v>
+        <v>98670</v>
       </c>
       <c r="Q12" t="n">
-        <v>28053</v>
+        <v>290710.56</v>
       </c>
     </row>
     <row r="13">
@@ -15249,7 +15249,7 @@
         <v>50400</v>
       </c>
       <c r="H13" t="n">
-        <v>1530</v>
+        <v>2070</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -15261,22 +15261,22 @@
         <v>5.7</v>
       </c>
       <c r="L13" t="n">
-        <v>102240</v>
+        <v>138930</v>
       </c>
       <c r="M13" t="n">
-        <v>3210</v>
+        <v>16170</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2520</v>
+        <v>3720</v>
       </c>
       <c r="P13" t="n">
-        <v>42420</v>
+        <v>70260</v>
       </c>
       <c r="Q13" t="n">
-        <v>19369.3</v>
+        <v>200722.14</v>
       </c>
     </row>
     <row r="14">
@@ -15302,7 +15302,7 @@
         <v>24180</v>
       </c>
       <c r="H14" t="n">
-        <v>720</v>
+        <v>810</v>
       </c>
       <c r="I14" t="n">
         <v>0.97</v>
@@ -15314,22 +15314,22 @@
         <v>0.97</v>
       </c>
       <c r="L14" t="n">
-        <v>43560</v>
+        <v>60330</v>
       </c>
       <c r="M14" t="n">
-        <v>1710</v>
+        <v>17430</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3330</v>
+        <v>3030</v>
       </c>
       <c r="P14" t="n">
-        <v>28560</v>
+        <v>38100</v>
       </c>
       <c r="Q14" t="n">
-        <v>9466.25</v>
+        <v>98097.8</v>
       </c>
     </row>
     <row r="15">
@@ -15355,7 +15355,7 @@
         <v>6420</v>
       </c>
       <c r="H15" t="n">
-        <v>390</v>
+        <v>540</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -15367,22 +15367,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>18390</v>
+        <v>32130</v>
       </c>
       <c r="M15" t="n">
-        <v>930</v>
+        <v>6750</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>1080</v>
+        <v>1920</v>
       </c>
       <c r="P15" t="n">
-        <v>28320</v>
+        <v>29640</v>
       </c>
       <c r="Q15" t="n">
-        <v>3346.88</v>
+        <v>34683.44</v>
       </c>
     </row>
     <row r="16">
@@ -15408,7 +15408,7 @@
         <v>3900</v>
       </c>
       <c r="H16" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -15420,22 +15420,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>8700</v>
+        <v>25650</v>
       </c>
       <c r="M16" t="n">
-        <v>840</v>
+        <v>3570</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="P16" t="n">
-        <v>40200</v>
+        <v>57780</v>
       </c>
       <c r="Q16" t="n">
-        <v>2368.82</v>
+        <v>24547.87</v>
       </c>
     </row>
     <row r="17">
@@ -15461,7 +15461,7 @@
         <v>1320</v>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -15473,22 +15473,22 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>2460</v>
+        <v>9900</v>
       </c>
       <c r="M17" t="n">
-        <v>180</v>
+        <v>1860</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="P17" t="n">
-        <v>20940</v>
+        <v>32760</v>
       </c>
       <c r="Q17" t="n">
-        <v>1192.33</v>
+        <v>12356.05</v>
       </c>
     </row>
     <row r="18">
@@ -15514,7 +15514,7 @@
         <v>360</v>
       </c>
       <c r="H18" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -15526,10 +15526,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>4620</v>
+        <v>9210</v>
       </c>
       <c r="M18" t="n">
-        <v>3480</v>
+        <v>4440</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -15538,10 +15538,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>21000</v>
+        <v>30150</v>
       </c>
       <c r="Q18" t="n">
-        <v>579.54</v>
+        <v>6005.7</v>
       </c>
     </row>
     <row r="19">
@@ -15579,22 +15579,22 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1140</v>
+        <v>4200</v>
       </c>
       <c r="M19" t="n">
+        <v>1230</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
         <v>150</v>
       </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>60</v>
-      </c>
       <c r="P19" t="n">
-        <v>19350</v>
+        <v>31620</v>
       </c>
       <c r="Q19" t="n">
-        <v>267.62</v>
+        <v>2773.29</v>
       </c>
     </row>
     <row r="20">
@@ -15620,7 +15620,7 @@
         <v>3660</v>
       </c>
       <c r="H20" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -15632,10 +15632,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>750</v>
+        <v>2760</v>
       </c>
       <c r="M20" t="n">
-        <v>30</v>
+        <v>1500</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -15644,10 +15644,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2760</v>
+        <v>7440</v>
       </c>
       <c r="Q20" t="n">
-        <v>82.92</v>
+        <v>859.28</v>
       </c>
     </row>
     <row r="21">
@@ -15673,7 +15673,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -15685,10 +15685,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>30</v>
+        <v>480</v>
       </c>
       <c r="M21" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -15697,10 +15697,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="Q21" t="n">
-        <v>17.63</v>
+        <v>182.73</v>
       </c>
     </row>
     <row r="22">
@@ -15738,7 +15738,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -15753,7 +15753,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.34</v>
+        <v>24.29</v>
       </c>
     </row>
     <row r="23">
@@ -15791,10 +15791,10 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M23" t="n">
-        <v>210</v>
+        <v>330</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -15806,7 +15806,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>8.15</v>
+        <v>84.42</v>
       </c>
     </row>
     <row r="24">
@@ -16117,7 +16117,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2235.6</v>
+        <v>2332.8</v>
       </c>
       <c r="I5" t="n">
         <v>1.32</v>
@@ -16129,19 +16129,19 @@
         <v>29.13</v>
       </c>
       <c r="L5" t="n">
-        <v>34070.4</v>
+        <v>32054.4</v>
       </c>
       <c r="M5" t="n">
-        <v>369</v>
+        <v>23.4</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1573.5</v>
+        <v>1881</v>
       </c>
       <c r="P5" t="n">
-        <v>580.2</v>
+        <v>217.2</v>
       </c>
       <c r="Q5" t="n">
         <v>1489.34</v>
@@ -16170,7 +16170,7 @@
         <v>3403.5</v>
       </c>
       <c r="H6" t="n">
-        <v>4394.7</v>
+        <v>4189.5</v>
       </c>
       <c r="I6" t="n">
         <v>0.51</v>
@@ -16182,19 +16182,19 @@
         <v>38.53</v>
       </c>
       <c r="L6" t="n">
-        <v>57831</v>
+        <v>49894.5</v>
       </c>
       <c r="M6" t="n">
-        <v>1140</v>
+        <v>168</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>5220</v>
+        <v>5505</v>
       </c>
       <c r="P6" t="n">
-        <v>4540.5</v>
+        <v>2601</v>
       </c>
       <c r="Q6" t="n">
         <v>22704.96</v>
@@ -16223,7 +16223,7 @@
         <v>13297.5</v>
       </c>
       <c r="H7" t="n">
-        <v>8628.6</v>
+        <v>9088.5</v>
       </c>
       <c r="I7" t="n">
         <v>1.28</v>
@@ -16235,19 +16235,19 @@
         <v>45.94</v>
       </c>
       <c r="L7" t="n">
-        <v>121482</v>
+        <v>113508</v>
       </c>
       <c r="M7" t="n">
-        <v>3307.5</v>
+        <v>1522.5</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>6972</v>
+        <v>6751.5</v>
       </c>
       <c r="P7" t="n">
-        <v>8377.5</v>
+        <v>5895</v>
       </c>
       <c r="Q7" t="n">
         <v>33334.47</v>
@@ -16276,7 +16276,7 @@
         <v>37986</v>
       </c>
       <c r="H8" t="n">
-        <v>2218.5</v>
+        <v>2779.5</v>
       </c>
       <c r="I8" t="n">
         <v>1.47</v>
@@ -16288,19 +16288,19 @@
         <v>30.91</v>
       </c>
       <c r="L8" t="n">
-        <v>90333.3</v>
+        <v>87521.7</v>
       </c>
       <c r="M8" t="n">
-        <v>3184.5</v>
+        <v>3333</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>8302.5</v>
+        <v>8167.5</v>
       </c>
       <c r="P8" t="n">
-        <v>13429.2</v>
+        <v>11605.2</v>
       </c>
       <c r="Q8" t="n">
         <v>32710.24</v>
@@ -16329,7 +16329,7 @@
         <v>29019</v>
       </c>
       <c r="H9" t="n">
-        <v>270</v>
+        <v>450</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -16341,19 +16341,19 @@
         <v>27.3</v>
       </c>
       <c r="L9" t="n">
-        <v>60458.4</v>
+        <v>68258.7</v>
       </c>
       <c r="M9" t="n">
-        <v>2478</v>
+        <v>9639</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>14965.5</v>
+        <v>14421</v>
       </c>
       <c r="P9" t="n">
-        <v>16290</v>
+        <v>15795</v>
       </c>
       <c r="Q9" t="n">
         <v>28186.98</v>
@@ -16394,19 +16394,19 @@
         <v>4.35</v>
       </c>
       <c r="L10" t="n">
-        <v>34923.6</v>
+        <v>40450.5</v>
       </c>
       <c r="M10" t="n">
-        <v>1530</v>
+        <v>7573.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>7644</v>
+        <v>11487</v>
       </c>
       <c r="P10" t="n">
-        <v>31441.5</v>
+        <v>34552.5</v>
       </c>
       <c r="Q10" t="n">
         <v>16158.01</v>
@@ -16447,19 +16447,19 @@
         <v>1.8</v>
       </c>
       <c r="L11" t="n">
-        <v>10200</v>
+        <v>24720</v>
       </c>
       <c r="M11" t="n">
-        <v>702</v>
+        <v>9558</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>790.5</v>
+        <v>1657.5</v>
       </c>
       <c r="P11" t="n">
-        <v>29079</v>
+        <v>32157</v>
       </c>
       <c r="Q11" t="n">
         <v>1949.65</v>
@@ -16488,7 +16488,7 @@
         <v>1230</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -16500,19 +16500,19 @@
         <v>1.85</v>
       </c>
       <c r="L12" t="n">
-        <v>4740</v>
+        <v>34740</v>
       </c>
       <c r="M12" t="n">
-        <v>370.5</v>
+        <v>9262.5</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P12" t="n">
-        <v>31080</v>
+        <v>50100</v>
       </c>
       <c r="Q12" t="n">
         <v>427.54</v>
@@ -16553,10 +16553,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>3300</v>
+        <v>19650</v>
       </c>
       <c r="M13" t="n">
-        <v>270</v>
+        <v>5580</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -16565,7 +16565,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>23820</v>
+        <v>42060</v>
       </c>
       <c r="Q13" t="n">
         <v>224.65</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1050</v>
+        <v>6180</v>
       </c>
       <c r="M14" t="n">
-        <v>360</v>
+        <v>8790</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -16618,7 +16618,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>13500</v>
+        <v>22860</v>
       </c>
       <c r="Q14" t="n">
         <v>137.49</v>
@@ -16659,10 +16659,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>900</v>
+        <v>3780</v>
       </c>
       <c r="M15" t="n">
-        <v>180</v>
+        <v>1260</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -16671,7 +16671,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>10860</v>
+        <v>11610</v>
       </c>
       <c r="Q15" t="n">
         <v>14.84</v>
@@ -16712,10 +16712,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>240</v>
+        <v>5970</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -16724,7 +16724,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>12690</v>
+        <v>21240</v>
       </c>
       <c r="Q16" t="n">
         <v>22.21</v>
@@ -16765,10 +16765,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>390</v>
+        <v>3060</v>
       </c>
       <c r="M17" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -16777,7 +16777,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>10230</v>
+        <v>23160</v>
       </c>
       <c r="Q17" t="n">
         <v>13.39</v>
@@ -16818,10 +16818,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>600</v>
+        <v>2670</v>
       </c>
       <c r="M18" t="n">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -16830,7 +16830,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>3840</v>
+        <v>8880</v>
       </c>
       <c r="Q18" t="n">
         <v>6.47</v>
@@ -16871,7 +16871,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>360</v>
+        <v>1200</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -16883,7 +16883,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>690</v>
+        <v>1230</v>
       </c>
       <c r="Q19" t="n">
         <v>2.01</v>
@@ -16924,7 +16924,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -17409,7 +17409,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>12742920</v>
+        <v>13296960</v>
       </c>
       <c r="I5" t="n">
         <v>257152.58</v>
@@ -17421,19 +17421,19 @@
         <v>1414339.17</v>
       </c>
       <c r="L5" t="n">
-        <v>6132672</v>
+        <v>5769792</v>
       </c>
       <c r="M5" t="n">
-        <v>129150</v>
+        <v>8190</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>267495</v>
+        <v>319770</v>
       </c>
       <c r="P5" t="n">
-        <v>37713</v>
+        <v>14118</v>
       </c>
       <c r="Q5" t="n">
         <v>893604.64</v>
@@ -17462,7 +17462,7 @@
         <v>183789</v>
       </c>
       <c r="H6" t="n">
-        <v>25049790</v>
+        <v>23880150</v>
       </c>
       <c r="I6" t="n">
         <v>98471.57000000001</v>
@@ -17474,19 +17474,19 @@
         <v>1870959.79</v>
       </c>
       <c r="L6" t="n">
-        <v>10409580</v>
+        <v>8981010</v>
       </c>
       <c r="M6" t="n">
-        <v>399000</v>
+        <v>58800</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>887400</v>
+        <v>935850</v>
       </c>
       <c r="P6" t="n">
-        <v>295132.5</v>
+        <v>169065</v>
       </c>
       <c r="Q6" t="n">
         <v>13622978.52</v>
@@ -17515,7 +17515,7 @@
         <v>718065</v>
       </c>
       <c r="H7" t="n">
-        <v>49183020</v>
+        <v>51804450</v>
       </c>
       <c r="I7" t="n">
         <v>247829.82</v>
@@ -17527,19 +17527,19 @@
         <v>2230468.42</v>
       </c>
       <c r="L7" t="n">
-        <v>21866760</v>
+        <v>20431440</v>
       </c>
       <c r="M7" t="n">
-        <v>1157625</v>
+        <v>532875</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1185240</v>
+        <v>1147755</v>
       </c>
       <c r="P7" t="n">
-        <v>544537.5</v>
+        <v>383175</v>
       </c>
       <c r="Q7" t="n">
         <v>20000684.16</v>
@@ -17568,7 +17568,7 @@
         <v>2051244</v>
       </c>
       <c r="H8" t="n">
-        <v>12645450</v>
+        <v>15843150</v>
       </c>
       <c r="I8" t="n">
         <v>285897.73</v>
@@ -17580,19 +17580,19 @@
         <v>1500963.07</v>
       </c>
       <c r="L8" t="n">
-        <v>16259994</v>
+        <v>15753906</v>
       </c>
       <c r="M8" t="n">
-        <v>1114575</v>
+        <v>1166550</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1411425</v>
+        <v>1388475</v>
       </c>
       <c r="P8" t="n">
-        <v>872898</v>
+        <v>754338</v>
       </c>
       <c r="Q8" t="n">
         <v>19626146.75</v>
@@ -17621,7 +17621,7 @@
         <v>1567026</v>
       </c>
       <c r="H9" t="n">
-        <v>1539000</v>
+        <v>2565000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -17633,19 +17633,19 @@
         <v>1325675.91</v>
       </c>
       <c r="L9" t="n">
-        <v>10882512</v>
+        <v>12286566</v>
       </c>
       <c r="M9" t="n">
-        <v>867300</v>
+        <v>3373650</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2544135</v>
+        <v>2451570</v>
       </c>
       <c r="P9" t="n">
-        <v>1058850</v>
+        <v>1026675</v>
       </c>
       <c r="Q9" t="n">
         <v>16912188.31</v>
@@ -17686,19 +17686,19 @@
         <v>211218.6</v>
       </c>
       <c r="L10" t="n">
-        <v>6286248</v>
+        <v>7281090</v>
       </c>
       <c r="M10" t="n">
-        <v>535500</v>
+        <v>2650725</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1299480</v>
+        <v>1952790</v>
       </c>
       <c r="P10" t="n">
-        <v>2043697.5</v>
+        <v>2245912.5</v>
       </c>
       <c r="Q10" t="n">
         <v>9694803.6</v>
@@ -17739,19 +17739,19 @@
         <v>87255.13</v>
       </c>
       <c r="L11" t="n">
-        <v>1836000</v>
+        <v>4449600</v>
       </c>
       <c r="M11" t="n">
-        <v>245700</v>
+        <v>3345300</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>134385</v>
+        <v>281775</v>
       </c>
       <c r="P11" t="n">
-        <v>1890135</v>
+        <v>2090205</v>
       </c>
       <c r="Q11" t="n">
         <v>1169791.2</v>
@@ -17780,7 +17780,7 @@
         <v>66420</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>513000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -17792,19 +17792,19 @@
         <v>90022.82000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>853200</v>
+        <v>6253200</v>
       </c>
       <c r="M12" t="n">
-        <v>129675</v>
+        <v>3241875</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>5100</v>
       </c>
       <c r="P12" t="n">
-        <v>2020200</v>
+        <v>3256500</v>
       </c>
       <c r="Q12" t="n">
         <v>256523.76</v>
@@ -17845,10 +17845,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>594000</v>
+        <v>3537000</v>
       </c>
       <c r="M13" t="n">
-        <v>94500</v>
+        <v>1953000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -17857,7 +17857,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1548300</v>
+        <v>2733900</v>
       </c>
       <c r="Q13" t="n">
         <v>134790.48</v>
@@ -17898,10 +17898,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>189000</v>
+        <v>1112400</v>
       </c>
       <c r="M14" t="n">
-        <v>126000</v>
+        <v>3076500</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -17910,7 +17910,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>877500</v>
+        <v>1485900</v>
       </c>
       <c r="Q14" t="n">
         <v>82494.72</v>
@@ -17951,10 +17951,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>162000</v>
+        <v>680400</v>
       </c>
       <c r="M15" t="n">
-        <v>63000</v>
+        <v>441000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -17963,7 +17963,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>705900</v>
+        <v>754650</v>
       </c>
       <c r="Q15" t="n">
         <v>8905.68</v>
@@ -18004,10 +18004,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>43200</v>
+        <v>1074600</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>136500</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -18016,7 +18016,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>824850</v>
+        <v>1380600</v>
       </c>
       <c r="Q16" t="n">
         <v>13325.04</v>
@@ -18057,10 +18057,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>70200</v>
+        <v>550800</v>
       </c>
       <c r="M17" t="n">
-        <v>10500</v>
+        <v>63000</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -18069,7 +18069,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>664950</v>
+        <v>1505400</v>
       </c>
       <c r="Q17" t="n">
         <v>8035.2</v>
@@ -18110,10 +18110,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>108000</v>
+        <v>480600</v>
       </c>
       <c r="M18" t="n">
-        <v>105000</v>
+        <v>126000</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -18122,7 +18122,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>249600</v>
+        <v>577200</v>
       </c>
       <c r="Q18" t="n">
         <v>3883.68</v>
@@ -18163,7 +18163,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>64800</v>
+        <v>216000</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -18175,7 +18175,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>44850</v>
+        <v>79950</v>
       </c>
       <c r="Q19" t="n">
         <v>1205.28</v>
@@ -18216,7 +18216,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>37800</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -18648,7 +18648,7 @@
         <v>107370</v>
       </c>
       <c r="H4" t="n">
-        <v>13620</v>
+        <v>16080</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -18660,22 +18660,22 @@
         <v>48</v>
       </c>
       <c r="L4" t="n">
-        <v>345870</v>
+        <v>388860</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>17640</v>
+        <v>14280</v>
       </c>
       <c r="O4" t="n">
-        <v>55260</v>
+        <v>54990</v>
       </c>
       <c r="P4" t="n">
-        <v>7650</v>
+        <v>2970</v>
       </c>
       <c r="Q4" t="n">
-        <v>34239.02</v>
+        <v>392322.15</v>
       </c>
     </row>
     <row r="5">
@@ -18701,7 +18701,7 @@
         <v>30540</v>
       </c>
       <c r="H5" t="n">
-        <v>2940</v>
+        <v>4830</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -18713,22 +18713,22 @@
         <v>15</v>
       </c>
       <c r="L5" t="n">
-        <v>112080</v>
+        <v>141480</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>25470</v>
+        <v>30000</v>
       </c>
       <c r="O5" t="n">
-        <v>34710</v>
+        <v>47760</v>
       </c>
       <c r="P5" t="n">
-        <v>6510</v>
+        <v>8340</v>
       </c>
       <c r="Q5" t="n">
-        <v>11163.14</v>
+        <v>127910.97</v>
       </c>
     </row>
     <row r="6">
@@ -18754,7 +18754,7 @@
         <v>4140</v>
       </c>
       <c r="H6" t="n">
-        <v>330</v>
+        <v>450</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -18766,22 +18766,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>18780</v>
+        <v>30120</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>5580</v>
+        <v>10080</v>
       </c>
       <c r="O6" t="n">
-        <v>7560</v>
+        <v>9960</v>
       </c>
       <c r="P6" t="n">
-        <v>3870</v>
+        <v>7950</v>
       </c>
       <c r="Q6" t="n">
-        <v>1099.01</v>
+        <v>12592.8</v>
       </c>
     </row>
     <row r="7">
@@ -18819,22 +18819,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3090</v>
+        <v>7830</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>150</v>
+        <v>420</v>
       </c>
       <c r="O7" t="n">
-        <v>1800</v>
+        <v>3120</v>
       </c>
       <c r="P7" t="n">
-        <v>3630</v>
+        <v>8790</v>
       </c>
       <c r="Q7" t="n">
-        <v>144.29</v>
+        <v>1653.3</v>
       </c>
     </row>
     <row r="8">
@@ -18872,7 +18872,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>480</v>
+        <v>1140</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -18881,13 +18881,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>390</v>
+        <v>840</v>
       </c>
       <c r="P8" t="n">
-        <v>1710</v>
+        <v>6000</v>
       </c>
       <c r="Q8" t="n">
-        <v>11.84</v>
+        <v>135.63</v>
       </c>
     </row>
     <row r="9">
@@ -18925,7 +18925,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -18937,10 +18937,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.09</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="10">
@@ -18978,7 +18978,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -19031,7 +19031,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -19993,7 +19993,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1058.4</v>
+        <v>1738.8</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -20005,22 +20005,22 @@
         <v>4.96</v>
       </c>
       <c r="L5" t="n">
-        <v>23536.8</v>
+        <v>29710.8</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>254.7</v>
+        <v>300</v>
       </c>
       <c r="O5" t="n">
-        <v>1735.5</v>
+        <v>2388</v>
       </c>
       <c r="P5" t="n">
-        <v>130.2</v>
+        <v>166.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>558.16</v>
+        <v>6395.55</v>
       </c>
     </row>
     <row r="6">
@@ -20046,7 +20046,7 @@
         <v>207</v>
       </c>
       <c r="H6" t="n">
-        <v>188.1</v>
+        <v>256.5</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -20058,22 +20058,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>6948.6</v>
+        <v>11144.4</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>279</v>
+        <v>504</v>
       </c>
       <c r="O6" t="n">
-        <v>1890</v>
+        <v>2490</v>
       </c>
       <c r="P6" t="n">
-        <v>580.5</v>
+        <v>1192.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>824.26</v>
+        <v>9444.6</v>
       </c>
     </row>
     <row r="7">
@@ -20111,22 +20111,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1854</v>
+        <v>4698</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>10.5</v>
+        <v>29.4</v>
       </c>
       <c r="O7" t="n">
-        <v>630</v>
+        <v>1092</v>
       </c>
       <c r="P7" t="n">
-        <v>907.5</v>
+        <v>2197.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>115.43</v>
+        <v>1322.64</v>
       </c>
     </row>
     <row r="8">
@@ -20164,7 +20164,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>340.8</v>
+        <v>809.4</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -20173,13 +20173,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>175.5</v>
+        <v>378</v>
       </c>
       <c r="P8" t="n">
-        <v>649.8</v>
+        <v>2280</v>
       </c>
       <c r="Q8" t="n">
-        <v>11.24</v>
+        <v>128.85</v>
       </c>
     </row>
     <row r="9">
@@ -20217,7 +20217,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>48.6</v>
+        <v>121.5</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -20229,10 +20229,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.08</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="10">
@@ -20270,7 +20270,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>160.2</v>
+        <v>133.5</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -20323,7 +20323,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -21285,7 +21285,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>6032880</v>
+        <v>9911160</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -21297,22 +21297,22 @@
         <v>241080.54</v>
       </c>
       <c r="L5" t="n">
-        <v>4236624</v>
+        <v>5347944</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>43299</v>
+        <v>51000</v>
       </c>
       <c r="O5" t="n">
-        <v>295035</v>
+        <v>405960</v>
       </c>
       <c r="P5" t="n">
-        <v>8463</v>
+        <v>10842</v>
       </c>
       <c r="Q5" t="n">
-        <v>334894.18</v>
+        <v>3837329.1</v>
       </c>
     </row>
     <row r="6">
@@ -21338,7 +21338,7 @@
         <v>11178</v>
       </c>
       <c r="H6" t="n">
-        <v>1072170</v>
+        <v>1462050</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -21350,22 +21350,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1250748</v>
+        <v>2005992</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>47430</v>
+        <v>85680</v>
       </c>
       <c r="O6" t="n">
-        <v>321300</v>
+        <v>423300</v>
       </c>
       <c r="P6" t="n">
-        <v>37732.5</v>
+        <v>77512.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>494553.6</v>
+        <v>5666760</v>
       </c>
     </row>
     <row r="7">
@@ -21403,22 +21403,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>333720</v>
+        <v>845640</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1785</v>
+        <v>4998</v>
       </c>
       <c r="O7" t="n">
-        <v>107100</v>
+        <v>185640</v>
       </c>
       <c r="P7" t="n">
-        <v>58987.5</v>
+        <v>142837.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>69258.24000000001</v>
+        <v>793584</v>
       </c>
     </row>
     <row r="8">
@@ -21456,7 +21456,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>61344</v>
+        <v>145692</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -21465,13 +21465,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>29835</v>
+        <v>64260</v>
       </c>
       <c r="P8" t="n">
-        <v>42237</v>
+        <v>148200</v>
       </c>
       <c r="Q8" t="n">
-        <v>6746.98</v>
+        <v>77309.10000000001</v>
       </c>
     </row>
     <row r="9">
@@ -21509,7 +21509,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>8748</v>
+        <v>21870</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -21521,10 +21521,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>975</v>
+        <v>2925</v>
       </c>
       <c r="Q9" t="n">
-        <v>50.28</v>
+        <v>576.1799999999999</v>
       </c>
     </row>
     <row r="10">
@@ -21562,7 +21562,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>28836</v>
+        <v>24030</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -21615,7 +21615,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>16200</v>
+        <v>32400</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -22577,7 +22577,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>110315520</v>
+        <v>120596040</v>
       </c>
       <c r="I5" t="n">
         <v>321440.72</v>
@@ -22589,22 +22589,22 @@
         <v>4210873.43</v>
       </c>
       <c r="L5" t="n">
-        <v>33590214</v>
+        <v>35591724</v>
       </c>
       <c r="M5" t="n">
-        <v>353850</v>
+        <v>271110</v>
       </c>
       <c r="N5" t="n">
-        <v>127857</v>
+        <v>147696</v>
       </c>
       <c r="O5" t="n">
-        <v>1550400</v>
+        <v>1770720</v>
       </c>
       <c r="P5" t="n">
-        <v>68211</v>
+        <v>44148</v>
       </c>
       <c r="Q5" t="n">
-        <v>4119630.3</v>
+        <v>42691330.12</v>
       </c>
     </row>
     <row r="6">
@@ -22630,7 +22630,7 @@
         <v>635283</v>
       </c>
       <c r="H6" t="n">
-        <v>149226570</v>
+        <v>151370910</v>
       </c>
       <c r="I6" t="n">
         <v>98471.57000000001</v>
@@ -22642,22 +22642,22 @@
         <v>4061952.18</v>
       </c>
       <c r="L6" t="n">
-        <v>38305656</v>
+        <v>38273688</v>
       </c>
       <c r="M6" t="n">
-        <v>946680</v>
+        <v>641760</v>
       </c>
       <c r="N6" t="n">
-        <v>228990</v>
+        <v>322830</v>
       </c>
       <c r="O6" t="n">
-        <v>4862850</v>
+        <v>5314200</v>
       </c>
       <c r="P6" t="n">
-        <v>500175</v>
+        <v>365332.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>42779706.12</v>
+        <v>443321954.55</v>
       </c>
     </row>
     <row r="7">
@@ -22683,7 +22683,7 @@
         <v>1708290</v>
       </c>
       <c r="H7" t="n">
-        <v>177633090</v>
+        <v>188368470</v>
       </c>
       <c r="I7" t="n">
         <v>247829.82</v>
@@ -22695,22 +22695,22 @@
         <v>4708766.66</v>
       </c>
       <c r="L7" t="n">
-        <v>57607200</v>
+        <v>57587760</v>
       </c>
       <c r="M7" t="n">
-        <v>2892225</v>
+        <v>3200925</v>
       </c>
       <c r="N7" t="n">
-        <v>115311</v>
+        <v>171717</v>
       </c>
       <c r="O7" t="n">
-        <v>4973010</v>
+        <v>5342505</v>
       </c>
       <c r="P7" t="n">
-        <v>1004250</v>
+        <v>723450</v>
       </c>
       <c r="Q7" t="n">
-        <v>44800150.46</v>
+        <v>464259623.76</v>
       </c>
     </row>
     <row r="8">
@@ -22736,7 +22736,7 @@
         <v>6173739</v>
       </c>
       <c r="H8" t="n">
-        <v>133722000</v>
+        <v>139099950</v>
       </c>
       <c r="I8" t="n">
         <v>428846.59</v>
@@ -22748,22 +22748,22 @@
         <v>3645196.03</v>
       </c>
       <c r="L8" t="n">
-        <v>56513160</v>
+        <v>56056914</v>
       </c>
       <c r="M8" t="n">
-        <v>3580500</v>
+        <v>5035800</v>
       </c>
       <c r="N8" t="n">
-        <v>72420</v>
+        <v>147900</v>
       </c>
       <c r="O8" t="n">
-        <v>4649670</v>
+        <v>4945725</v>
       </c>
       <c r="P8" t="n">
-        <v>1711710</v>
+        <v>1362699</v>
       </c>
       <c r="Q8" t="n">
-        <v>44666883.32</v>
+        <v>462878589.28</v>
       </c>
     </row>
     <row r="9">
@@ -22789,7 +22789,7 @@
         <v>7172793</v>
       </c>
       <c r="H9" t="n">
-        <v>53865000</v>
+        <v>68913000</v>
       </c>
       <c r="I9" t="n">
         <v>155961.87</v>
@@ -22801,22 +22801,22 @@
         <v>4288951.48</v>
       </c>
       <c r="L9" t="n">
-        <v>54933066</v>
+        <v>57268782</v>
       </c>
       <c r="M9" t="n">
-        <v>2800350</v>
+        <v>8187900</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3060</v>
       </c>
       <c r="O9" t="n">
-        <v>5141565</v>
+        <v>6016725</v>
       </c>
       <c r="P9" t="n">
-        <v>2202525</v>
+        <v>2028000</v>
       </c>
       <c r="Q9" t="n">
-        <v>43593751.56</v>
+        <v>451757828.69</v>
       </c>
     </row>
     <row r="10">
@@ -22842,7 +22842,7 @@
         <v>7664220</v>
       </c>
       <c r="H10" t="n">
-        <v>21204000</v>
+        <v>19836000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -22854,22 +22854,22 @@
         <v>2492379.48</v>
       </c>
       <c r="L10" t="n">
-        <v>47973492</v>
+        <v>52784298</v>
       </c>
       <c r="M10" t="n">
-        <v>2766750</v>
+        <v>7131075</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3998400</v>
+        <v>5608470</v>
       </c>
       <c r="P10" t="n">
-        <v>4253145</v>
+        <v>4274692.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>37156639.68</v>
+        <v>385050661.2</v>
       </c>
     </row>
     <row r="11">
@@ -22895,7 +22895,7 @@
         <v>4265460</v>
       </c>
       <c r="H11" t="n">
-        <v>26676000</v>
+        <v>25650000</v>
       </c>
       <c r="I11" t="n">
         <v>523530.79</v>
@@ -22907,22 +22907,22 @@
         <v>1526964.81</v>
       </c>
       <c r="L11" t="n">
-        <v>33717600</v>
+        <v>40483800</v>
       </c>
       <c r="M11" t="n">
-        <v>1927800</v>
+        <v>7862400</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1773015</v>
+        <v>3290265</v>
       </c>
       <c r="P11" t="n">
-        <v>4245345</v>
+        <v>5224635</v>
       </c>
       <c r="Q11" t="n">
-        <v>24072856.56</v>
+        <v>249464682.9</v>
       </c>
     </row>
     <row r="12">
@@ -22948,7 +22948,7 @@
         <v>3265920</v>
       </c>
       <c r="H12" t="n">
-        <v>28728000</v>
+        <v>33345000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -22960,22 +22960,22 @@
         <v>765194</v>
       </c>
       <c r="L12" t="n">
-        <v>27286200</v>
+        <v>35807400</v>
       </c>
       <c r="M12" t="n">
-        <v>1256850</v>
+        <v>7201950</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>780300</v>
+        <v>2131800</v>
       </c>
       <c r="P12" t="n">
-        <v>3874650</v>
+        <v>6413550</v>
       </c>
       <c r="Q12" t="n">
-        <v>16831802.16</v>
+        <v>174426336.9</v>
       </c>
     </row>
     <row r="13">
@@ -23001,7 +23001,7 @@
         <v>2721600</v>
       </c>
       <c r="H13" t="n">
-        <v>8721000</v>
+        <v>11799000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -23013,22 +23013,22 @@
         <v>276623.53</v>
       </c>
       <c r="L13" t="n">
-        <v>18403200</v>
+        <v>25007400</v>
       </c>
       <c r="M13" t="n">
-        <v>1123500</v>
+        <v>5659500</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>428400</v>
+        <v>632400</v>
       </c>
       <c r="P13" t="n">
-        <v>2757300</v>
+        <v>4566900</v>
       </c>
       <c r="Q13" t="n">
-        <v>11621577.6</v>
+        <v>120433284</v>
       </c>
     </row>
     <row r="14">
@@ -23054,7 +23054,7 @@
         <v>1305720</v>
       </c>
       <c r="H14" t="n">
-        <v>4104000</v>
+        <v>4617000</v>
       </c>
       <c r="I14" t="n">
         <v>188785.73</v>
@@ -23066,22 +23066,22 @@
         <v>47196.43</v>
       </c>
       <c r="L14" t="n">
-        <v>7840800</v>
+        <v>10859400</v>
       </c>
       <c r="M14" t="n">
-        <v>598500</v>
+        <v>6100500</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>566100</v>
+        <v>515100</v>
       </c>
       <c r="P14" t="n">
-        <v>1856400</v>
+        <v>2476500</v>
       </c>
       <c r="Q14" t="n">
-        <v>5679748.08</v>
+        <v>58858679.7</v>
       </c>
     </row>
     <row r="15">
@@ -23107,7 +23107,7 @@
         <v>346680</v>
       </c>
       <c r="H15" t="n">
-        <v>2223000</v>
+        <v>3078000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -23119,22 +23119,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>3310200</v>
+        <v>5783400</v>
       </c>
       <c r="M15" t="n">
-        <v>325500</v>
+        <v>2362500</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>183600</v>
+        <v>326400</v>
       </c>
       <c r="P15" t="n">
-        <v>1840800</v>
+        <v>1926600</v>
       </c>
       <c r="Q15" t="n">
-        <v>2008130.4</v>
+        <v>20810061</v>
       </c>
     </row>
     <row r="16">
@@ -23160,7 +23160,7 @@
         <v>210600</v>
       </c>
       <c r="H16" t="n">
-        <v>684000</v>
+        <v>855000</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -23172,22 +23172,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1566000</v>
+        <v>4617000</v>
       </c>
       <c r="M16" t="n">
-        <v>294000</v>
+        <v>1249500</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>5100</v>
+        <v>30600</v>
       </c>
       <c r="P16" t="n">
-        <v>2613000</v>
+        <v>3755700</v>
       </c>
       <c r="Q16" t="n">
-        <v>1421292.96</v>
+        <v>14728721.4</v>
       </c>
     </row>
     <row r="17">
@@ -23213,7 +23213,7 @@
         <v>71280</v>
       </c>
       <c r="H17" t="n">
-        <v>342000</v>
+        <v>855000</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -23225,22 +23225,22 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>442800</v>
+        <v>1782000</v>
       </c>
       <c r="M17" t="n">
-        <v>63000</v>
+        <v>651000</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>10200</v>
+        <v>20400</v>
       </c>
       <c r="P17" t="n">
-        <v>1361100</v>
+        <v>2129400</v>
       </c>
       <c r="Q17" t="n">
-        <v>715400.64</v>
+        <v>7413627.6</v>
       </c>
     </row>
     <row r="18">
@@ -23266,7 +23266,7 @@
         <v>19440</v>
       </c>
       <c r="H18" t="n">
-        <v>342000</v>
+        <v>684000</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -23278,10 +23278,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>831600</v>
+        <v>1657800</v>
       </c>
       <c r="M18" t="n">
-        <v>1218000</v>
+        <v>1554000</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -23290,10 +23290,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1365000</v>
+        <v>1959750</v>
       </c>
       <c r="Q18" t="n">
-        <v>347723.28</v>
+        <v>3603422.7</v>
       </c>
     </row>
     <row r="19">
@@ -23331,22 +23331,22 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>205200</v>
+        <v>756000</v>
       </c>
       <c r="M19" t="n">
-        <v>52500</v>
+        <v>430500</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>10200</v>
+        <v>25500</v>
       </c>
       <c r="P19" t="n">
-        <v>1257750</v>
+        <v>2055300</v>
       </c>
       <c r="Q19" t="n">
-        <v>160570.08</v>
+        <v>1663972.2</v>
       </c>
     </row>
     <row r="20">
@@ -23372,7 +23372,7 @@
         <v>197640</v>
       </c>
       <c r="H20" t="n">
-        <v>342000</v>
+        <v>171000</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -23384,10 +23384,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>135000</v>
+        <v>496800</v>
       </c>
       <c r="M20" t="n">
-        <v>10500</v>
+        <v>525000</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -23396,10 +23396,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>179400</v>
+        <v>483600</v>
       </c>
       <c r="Q20" t="n">
-        <v>49751.28</v>
+        <v>515567.7</v>
       </c>
     </row>
     <row r="21">
@@ -23425,7 +23425,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>513000</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -23437,10 +23437,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>5400</v>
+        <v>86400</v>
       </c>
       <c r="M21" t="n">
-        <v>21000</v>
+        <v>105000</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -23449,10 +23449,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>7800</v>
       </c>
       <c r="Q21" t="n">
-        <v>10579.68</v>
+        <v>109636.2</v>
       </c>
     </row>
     <row r="22">
@@ -23490,7 +23490,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -23505,7 +23505,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1406.16</v>
+        <v>14571.9</v>
       </c>
     </row>
     <row r="23">
@@ -23543,10 +23543,10 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="M23" t="n">
-        <v>73500</v>
+        <v>115500</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -23558,7 +23558,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>4888.08</v>
+        <v>50654.7</v>
       </c>
     </row>
     <row r="24">
@@ -23816,7 +23816,7 @@
         <v>49410</v>
       </c>
       <c r="H4" t="n">
-        <v>2880</v>
+        <v>2640</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
@@ -23828,22 +23828,22 @@
         <v>72</v>
       </c>
       <c r="L4" t="n">
-        <v>135660</v>
+        <v>118080</v>
       </c>
       <c r="M4" t="n">
-        <v>45390</v>
+        <v>45510</v>
       </c>
       <c r="N4" t="n">
-        <v>14220</v>
+        <v>12210</v>
       </c>
       <c r="O4" t="n">
-        <v>17130</v>
+        <v>19860</v>
       </c>
       <c r="P4" t="n">
-        <v>1860</v>
+        <v>510</v>
       </c>
       <c r="Q4" t="n">
-        <v>10300.24</v>
+        <v>100982.7</v>
       </c>
     </row>
     <row r="5">
@@ -23869,7 +23869,7 @@
         <v>60120</v>
       </c>
       <c r="H5" t="n">
-        <v>8430</v>
+        <v>7170</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -23881,22 +23881,22 @@
         <v>69</v>
       </c>
       <c r="L5" t="n">
-        <v>165450</v>
+        <v>152400</v>
       </c>
       <c r="M5" t="n">
-        <v>18300</v>
+        <v>28860</v>
       </c>
       <c r="N5" t="n">
         <v>20910</v>
       </c>
       <c r="O5" t="n">
-        <v>20250</v>
+        <v>19500</v>
       </c>
       <c r="P5" t="n">
-        <v>2760</v>
+        <v>1290</v>
       </c>
       <c r="Q5" t="n">
-        <v>18281.42</v>
+        <v>179229.6</v>
       </c>
     </row>
     <row r="6">
@@ -23922,7 +23922,7 @@
         <v>63840</v>
       </c>
       <c r="H6" t="n">
-        <v>13020</v>
+        <v>13230</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -23934,22 +23934,22 @@
         <v>53</v>
       </c>
       <c r="L6" t="n">
-        <v>168420</v>
+        <v>158070</v>
       </c>
       <c r="M6" t="n">
-        <v>7230</v>
+        <v>13470</v>
       </c>
       <c r="N6" t="n">
-        <v>13590</v>
+        <v>16230</v>
       </c>
       <c r="O6" t="n">
-        <v>19020</v>
+        <v>22290</v>
       </c>
       <c r="P6" t="n">
-        <v>3240</v>
+        <v>1020</v>
       </c>
       <c r="Q6" t="n">
-        <v>21941.12</v>
+        <v>215109</v>
       </c>
     </row>
     <row r="7">
@@ -23975,7 +23975,7 @@
         <v>62670</v>
       </c>
       <c r="H7" t="n">
-        <v>12570</v>
+        <v>13470</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -23987,22 +23987,22 @@
         <v>57</v>
       </c>
       <c r="L7" t="n">
-        <v>179910</v>
+        <v>183120</v>
       </c>
       <c r="M7" t="n">
-        <v>4560</v>
+        <v>13830</v>
       </c>
       <c r="N7" t="n">
-        <v>6660</v>
+        <v>8700</v>
       </c>
       <c r="O7" t="n">
-        <v>20790</v>
+        <v>19890</v>
       </c>
       <c r="P7" t="n">
-        <v>4080</v>
+        <v>1710</v>
       </c>
       <c r="Q7" t="n">
-        <v>22870.13</v>
+        <v>224217</v>
       </c>
     </row>
     <row r="8">
@@ -24028,7 +24028,7 @@
         <v>84120</v>
       </c>
       <c r="H8" t="n">
-        <v>20130</v>
+        <v>20250</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -24040,22 +24040,22 @@
         <v>48</v>
       </c>
       <c r="L8" t="n">
-        <v>236760</v>
+        <v>231420</v>
       </c>
       <c r="M8" t="n">
-        <v>5010</v>
+        <v>12540</v>
       </c>
       <c r="N8" t="n">
-        <v>1770</v>
+        <v>2700</v>
       </c>
       <c r="O8" t="n">
-        <v>22950</v>
+        <v>23640</v>
       </c>
       <c r="P8" t="n">
-        <v>6030</v>
+        <v>3990</v>
       </c>
       <c r="Q8" t="n">
-        <v>23823.2</v>
+        <v>233560.8</v>
       </c>
     </row>
     <row r="9">
@@ -24081,7 +24081,7 @@
         <v>96510</v>
       </c>
       <c r="H9" t="n">
-        <v>5160</v>
+        <v>6090</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -24093,22 +24093,22 @@
         <v>65</v>
       </c>
       <c r="L9" t="n">
-        <v>238920</v>
+        <v>246510</v>
       </c>
       <c r="M9" t="n">
-        <v>3780</v>
+        <v>10410</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>19320</v>
+        <v>21690</v>
       </c>
       <c r="P9" t="n">
-        <v>9150</v>
+        <v>6300</v>
       </c>
       <c r="Q9" t="n">
-        <v>28272.1</v>
+        <v>277177.5</v>
       </c>
     </row>
     <row r="10">
@@ -24134,7 +24134,7 @@
         <v>96750</v>
       </c>
       <c r="H10" t="n">
-        <v>480</v>
+        <v>630</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -24146,22 +24146,22 @@
         <v>52</v>
       </c>
       <c r="L10" t="n">
-        <v>208200</v>
+        <v>223980</v>
       </c>
       <c r="M10" t="n">
-        <v>4710</v>
+        <v>8880</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>20850</v>
+        <v>24660</v>
       </c>
       <c r="P10" t="n">
-        <v>12240</v>
+        <v>6300</v>
       </c>
       <c r="Q10" t="n">
-        <v>29891.09</v>
+        <v>293049.9</v>
       </c>
     </row>
     <row r="11">
@@ -24187,7 +24187,7 @@
         <v>56610</v>
       </c>
       <c r="H11" t="n">
-        <v>360</v>
+        <v>450</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -24199,22 +24199,22 @@
         <v>30</v>
       </c>
       <c r="L11" t="n">
-        <v>121080</v>
+        <v>141390</v>
       </c>
       <c r="M11" t="n">
-        <v>3540</v>
+        <v>6270</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>11190</v>
+        <v>19410</v>
       </c>
       <c r="P11" t="n">
-        <v>15780</v>
+        <v>8790</v>
       </c>
       <c r="Q11" t="n">
-        <v>24997.87</v>
+        <v>245077.2</v>
       </c>
     </row>
     <row r="12">
@@ -24240,7 +24240,7 @@
         <v>27870</v>
       </c>
       <c r="H12" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -24252,22 +24252,22 @@
         <v>9</v>
       </c>
       <c r="L12" t="n">
-        <v>54450</v>
+        <v>68700</v>
       </c>
       <c r="M12" t="n">
-        <v>2130</v>
+        <v>4920</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4500</v>
+        <v>12390</v>
       </c>
       <c r="P12" t="n">
-        <v>14310</v>
+        <v>15420</v>
       </c>
       <c r="Q12" t="n">
-        <v>15453.24</v>
+        <v>151502.4</v>
       </c>
     </row>
     <row r="13">
@@ -24305,22 +24305,22 @@
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>27270</v>
+        <v>36060</v>
       </c>
       <c r="M13" t="n">
-        <v>2520</v>
+        <v>4590</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2520</v>
+        <v>3720</v>
       </c>
       <c r="P13" t="n">
-        <v>12450</v>
+        <v>12630</v>
       </c>
       <c r="Q13" t="n">
-        <v>8640.67</v>
+        <v>84712.5</v>
       </c>
     </row>
     <row r="14">
@@ -24358,22 +24358,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>8070</v>
+        <v>13440</v>
       </c>
       <c r="M14" t="n">
-        <v>870</v>
+        <v>4620</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3330</v>
+        <v>3030</v>
       </c>
       <c r="P14" t="n">
-        <v>12780</v>
+        <v>11490</v>
       </c>
       <c r="Q14" t="n">
-        <v>3436.53</v>
+        <v>33691.5</v>
       </c>
     </row>
     <row r="15">
@@ -24411,22 +24411,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>3030</v>
+        <v>8520</v>
       </c>
       <c r="M15" t="n">
-        <v>510</v>
+        <v>2100</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>1080</v>
+        <v>1920</v>
       </c>
       <c r="P15" t="n">
-        <v>16860</v>
+        <v>16950</v>
       </c>
       <c r="Q15" t="n">
-        <v>1047.62</v>
+        <v>10270.8</v>
       </c>
     </row>
     <row r="16">
@@ -24464,22 +24464,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>960</v>
+        <v>6450</v>
       </c>
       <c r="M16" t="n">
-        <v>30</v>
+        <v>750</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="P16" t="n">
-        <v>27510</v>
+        <v>36540</v>
       </c>
       <c r="Q16" t="n">
-        <v>493.98</v>
+        <v>4842.9</v>
       </c>
     </row>
     <row r="17">
@@ -24517,22 +24517,22 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>210</v>
+        <v>2460</v>
       </c>
       <c r="M17" t="n">
-        <v>90</v>
+        <v>840</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="P17" t="n">
-        <v>10710</v>
+        <v>9600</v>
       </c>
       <c r="Q17" t="n">
-        <v>194.89</v>
+        <v>1910.7</v>
       </c>
     </row>
     <row r="18">
@@ -24570,10 +24570,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>210</v>
+        <v>1410</v>
       </c>
       <c r="M18" t="n">
-        <v>570</v>
+        <v>720</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -24582,10 +24582,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>17190</v>
+        <v>21300</v>
       </c>
       <c r="Q18" t="n">
-        <v>129.16</v>
+        <v>1266.3</v>
       </c>
     </row>
     <row r="19">
@@ -24623,22 +24623,22 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>120</v>
+        <v>1410</v>
       </c>
       <c r="M19" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="P19" t="n">
-        <v>18660</v>
+        <v>30390</v>
       </c>
       <c r="Q19" t="n">
-        <v>108.51</v>
+        <v>1063.8</v>
       </c>
     </row>
     <row r="20">
@@ -24679,7 +24679,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -24688,10 +24688,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2760</v>
+        <v>7440</v>
       </c>
       <c r="Q20" t="n">
-        <v>24.6</v>
+        <v>241.2</v>
       </c>
     </row>
     <row r="21">
@@ -24732,7 +24732,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -24741,10 +24741,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="Q21" t="n">
-        <v>7.99</v>
+        <v>78.3</v>
       </c>
     </row>
     <row r="22">
@@ -24797,7 +24797,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.28</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="23">
@@ -24838,7 +24838,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>210</v>
+        <v>330</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -24850,7 +24850,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.7</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="24">
@@ -25161,7 +25161,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>3034.8</v>
+        <v>2581.2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -25173,22 +25173,22 @@
         <v>22.84</v>
       </c>
       <c r="L5" t="n">
-        <v>34744.5</v>
+        <v>32004</v>
       </c>
       <c r="M5" t="n">
-        <v>366</v>
+        <v>577.2</v>
       </c>
       <c r="N5" t="n">
         <v>209.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1012.5</v>
+        <v>975</v>
       </c>
       <c r="P5" t="n">
-        <v>55.2</v>
+        <v>25.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>914.0700000000001</v>
+        <v>8961.48</v>
       </c>
     </row>
     <row r="6">
@@ -25214,7 +25214,7 @@
         <v>3192</v>
       </c>
       <c r="H6" t="n">
-        <v>7421.4</v>
+        <v>7541.1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -25226,22 +25226,22 @@
         <v>26.87</v>
       </c>
       <c r="L6" t="n">
-        <v>62315.4</v>
+        <v>58485.9</v>
       </c>
       <c r="M6" t="n">
-        <v>578.4</v>
+        <v>1077.6</v>
       </c>
       <c r="N6" t="n">
-        <v>679.5</v>
+        <v>811.5</v>
       </c>
       <c r="O6" t="n">
-        <v>4755</v>
+        <v>5572.5</v>
       </c>
       <c r="P6" t="n">
-        <v>486</v>
+        <v>153</v>
       </c>
       <c r="Q6" t="n">
-        <v>16455.84</v>
+        <v>161331.75</v>
       </c>
     </row>
     <row r="7">
@@ -25267,7 +25267,7 @@
         <v>9400.5</v>
       </c>
       <c r="H7" t="n">
-        <v>9176.1</v>
+        <v>9833.1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -25279,22 +25279,22 @@
         <v>36.37</v>
       </c>
       <c r="L7" t="n">
-        <v>107946</v>
+        <v>109872</v>
       </c>
       <c r="M7" t="n">
-        <v>1596</v>
+        <v>4840.5</v>
       </c>
       <c r="N7" t="n">
-        <v>466.2</v>
+        <v>609</v>
       </c>
       <c r="O7" t="n">
-        <v>7276.5</v>
+        <v>6961.5</v>
       </c>
       <c r="P7" t="n">
-        <v>1020</v>
+        <v>427.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>18296.11</v>
+        <v>179373.6</v>
       </c>
     </row>
     <row r="8">
@@ -25320,7 +25320,7 @@
         <v>54678</v>
       </c>
       <c r="H8" t="n">
-        <v>17110.5</v>
+        <v>17212.5</v>
       </c>
       <c r="I8" t="n">
         <v>0.74</v>
@@ -25332,22 +25332,22 @@
         <v>35.33</v>
       </c>
       <c r="L8" t="n">
-        <v>168099.6</v>
+        <v>164308.2</v>
       </c>
       <c r="M8" t="n">
-        <v>2755.5</v>
+        <v>6897</v>
       </c>
       <c r="N8" t="n">
-        <v>354</v>
+        <v>540</v>
       </c>
       <c r="O8" t="n">
-        <v>10327.5</v>
+        <v>10638</v>
       </c>
       <c r="P8" t="n">
-        <v>2291.4</v>
+        <v>1516.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>22632.04</v>
+        <v>221882.76</v>
       </c>
     </row>
     <row r="9">
@@ -25373,7 +25373,7 @@
         <v>82033.5</v>
       </c>
       <c r="H9" t="n">
-        <v>5160</v>
+        <v>6090</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -25385,22 +25385,22 @@
         <v>52.2</v>
       </c>
       <c r="L9" t="n">
-        <v>193525.2</v>
+        <v>199673.1</v>
       </c>
       <c r="M9" t="n">
-        <v>2646</v>
+        <v>7287</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>10626</v>
+        <v>11929.5</v>
       </c>
       <c r="P9" t="n">
-        <v>4575</v>
+        <v>3150</v>
       </c>
       <c r="Q9" t="n">
-        <v>27423.94</v>
+        <v>268862.18</v>
       </c>
     </row>
     <row r="10">
@@ -25426,7 +25426,7 @@
         <v>96750</v>
       </c>
       <c r="H10" t="n">
-        <v>480</v>
+        <v>630</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -25438,22 +25438,22 @@
         <v>45.24</v>
       </c>
       <c r="L10" t="n">
-        <v>185298</v>
+        <v>199342.2</v>
       </c>
       <c r="M10" t="n">
-        <v>4003.5</v>
+        <v>7548</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>14595</v>
+        <v>17262</v>
       </c>
       <c r="P10" t="n">
-        <v>10404</v>
+        <v>5355</v>
       </c>
       <c r="Q10" t="n">
-        <v>29891.09</v>
+        <v>293049.9</v>
       </c>
     </row>
     <row r="11">
@@ -25479,7 +25479,7 @@
         <v>56610</v>
       </c>
       <c r="H11" t="n">
-        <v>360</v>
+        <v>450</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -25491,22 +25491,22 @@
         <v>26.96</v>
       </c>
       <c r="L11" t="n">
-        <v>121080</v>
+        <v>141390</v>
       </c>
       <c r="M11" t="n">
-        <v>3186</v>
+        <v>5643</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>9511.5</v>
+        <v>16498.5</v>
       </c>
       <c r="P11" t="n">
-        <v>14202</v>
+        <v>7911</v>
       </c>
       <c r="Q11" t="n">
-        <v>24997.87</v>
+        <v>245077.2</v>
       </c>
     </row>
     <row r="12">
@@ -25532,7 +25532,7 @@
         <v>27870</v>
       </c>
       <c r="H12" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -25544,22 +25544,22 @@
         <v>8.34</v>
       </c>
       <c r="L12" t="n">
-        <v>54450</v>
+        <v>68700</v>
       </c>
       <c r="M12" t="n">
-        <v>2023.5</v>
+        <v>4674</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4500</v>
+        <v>12390</v>
       </c>
       <c r="P12" t="n">
-        <v>14310</v>
+        <v>15420</v>
       </c>
       <c r="Q12" t="n">
-        <v>15453.24</v>
+        <v>151502.4</v>
       </c>
     </row>
     <row r="13">
@@ -25597,22 +25597,22 @@
         <v>0.95</v>
       </c>
       <c r="L13" t="n">
-        <v>27270</v>
+        <v>36060</v>
       </c>
       <c r="M13" t="n">
-        <v>2520</v>
+        <v>4590</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2520</v>
+        <v>3720</v>
       </c>
       <c r="P13" t="n">
-        <v>12450</v>
+        <v>12630</v>
       </c>
       <c r="Q13" t="n">
-        <v>8640.67</v>
+        <v>84712.5</v>
       </c>
     </row>
     <row r="14">
@@ -25650,22 +25650,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>8070</v>
+        <v>13440</v>
       </c>
       <c r="M14" t="n">
-        <v>870</v>
+        <v>4620</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3330</v>
+        <v>3030</v>
       </c>
       <c r="P14" t="n">
-        <v>12780</v>
+        <v>11490</v>
       </c>
       <c r="Q14" t="n">
-        <v>3436.53</v>
+        <v>33691.5</v>
       </c>
     </row>
     <row r="15">
@@ -25703,22 +25703,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>3030</v>
+        <v>8520</v>
       </c>
       <c r="M15" t="n">
-        <v>510</v>
+        <v>2100</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>1080</v>
+        <v>1920</v>
       </c>
       <c r="P15" t="n">
-        <v>16860</v>
+        <v>16950</v>
       </c>
       <c r="Q15" t="n">
-        <v>1047.62</v>
+        <v>10270.8</v>
       </c>
     </row>
     <row r="16">
@@ -25756,22 +25756,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>960</v>
+        <v>6450</v>
       </c>
       <c r="M16" t="n">
-        <v>30</v>
+        <v>750</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="P16" t="n">
-        <v>27510</v>
+        <v>36540</v>
       </c>
       <c r="Q16" t="n">
-        <v>493.98</v>
+        <v>4842.9</v>
       </c>
     </row>
     <row r="17">
@@ -25809,22 +25809,22 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>210</v>
+        <v>2460</v>
       </c>
       <c r="M17" t="n">
-        <v>90</v>
+        <v>840</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="P17" t="n">
-        <v>10710</v>
+        <v>9600</v>
       </c>
       <c r="Q17" t="n">
-        <v>194.89</v>
+        <v>1910.7</v>
       </c>
     </row>
     <row r="18">
@@ -25862,10 +25862,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>210</v>
+        <v>1410</v>
       </c>
       <c r="M18" t="n">
-        <v>570</v>
+        <v>720</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -25874,10 +25874,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>17190</v>
+        <v>21300</v>
       </c>
       <c r="Q18" t="n">
-        <v>129.16</v>
+        <v>1266.3</v>
       </c>
     </row>
     <row r="19">
@@ -25915,22 +25915,22 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>120</v>
+        <v>1410</v>
       </c>
       <c r="M19" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="P19" t="n">
-        <v>18660</v>
+        <v>30390</v>
       </c>
       <c r="Q19" t="n">
-        <v>108.51</v>
+        <v>1063.8</v>
       </c>
     </row>
     <row r="20">
@@ -25971,7 +25971,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -25980,10 +25980,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2760</v>
+        <v>7440</v>
       </c>
       <c r="Q20" t="n">
-        <v>24.6</v>
+        <v>241.2</v>
       </c>
     </row>
     <row r="21">
@@ -26024,7 +26024,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -26033,10 +26033,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="Q21" t="n">
-        <v>7.99</v>
+        <v>78.3</v>
       </c>
     </row>
     <row r="22">
@@ -26089,7 +26089,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.28</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="23">
@@ -26130,7 +26130,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>210</v>
+        <v>330</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -26142,7 +26142,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.7</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="24">
@@ -26453,7 +26453,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>17298360</v>
+        <v>14712840</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -26465,22 +26465,22 @@
         <v>1108970.48</v>
       </c>
       <c r="L5" t="n">
-        <v>6254010</v>
+        <v>5760720</v>
       </c>
       <c r="M5" t="n">
-        <v>128100</v>
+        <v>202020</v>
       </c>
       <c r="N5" t="n">
         <v>35547</v>
       </c>
       <c r="O5" t="n">
-        <v>172125</v>
+        <v>165750</v>
       </c>
       <c r="P5" t="n">
-        <v>3588</v>
+        <v>1677</v>
       </c>
       <c r="Q5" t="n">
-        <v>548442.58</v>
+        <v>5376888</v>
       </c>
     </row>
     <row r="6">
@@ -26506,7 +26506,7 @@
         <v>172368</v>
       </c>
       <c r="H6" t="n">
-        <v>42301980</v>
+        <v>42984270</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -26518,22 +26518,22 @@
         <v>1304748.28</v>
       </c>
       <c r="L6" t="n">
-        <v>11216772</v>
+        <v>10527462</v>
       </c>
       <c r="M6" t="n">
-        <v>202440</v>
+        <v>377160</v>
       </c>
       <c r="N6" t="n">
-        <v>115515</v>
+        <v>137955</v>
       </c>
       <c r="O6" t="n">
-        <v>808350</v>
+        <v>947325</v>
       </c>
       <c r="P6" t="n">
-        <v>31590</v>
+        <v>9945</v>
       </c>
       <c r="Q6" t="n">
-        <v>9873503.1</v>
+        <v>96799050</v>
       </c>
     </row>
     <row r="7">
@@ -26559,7 +26559,7 @@
         <v>507627</v>
       </c>
       <c r="H7" t="n">
-        <v>52303770</v>
+        <v>56048670</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -26571,22 +26571,22 @@
         <v>1765787.5</v>
       </c>
       <c r="L7" t="n">
-        <v>19430280</v>
+        <v>19776960</v>
       </c>
       <c r="M7" t="n">
-        <v>558600</v>
+        <v>1694175</v>
       </c>
       <c r="N7" t="n">
-        <v>79254</v>
+        <v>103530</v>
       </c>
       <c r="O7" t="n">
-        <v>1237005</v>
+        <v>1183455</v>
       </c>
       <c r="P7" t="n">
-        <v>66300</v>
+        <v>27787.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>10977664.32</v>
+        <v>107624160</v>
       </c>
     </row>
     <row r="8">
@@ -26612,7 +26612,7 @@
         <v>2952612</v>
       </c>
       <c r="H8" t="n">
-        <v>97529850</v>
+        <v>98111250</v>
       </c>
       <c r="I8" t="n">
         <v>142948.86</v>
@@ -26624,22 +26624,22 @@
         <v>1715386.37</v>
       </c>
       <c r="L8" t="n">
-        <v>30257928</v>
+        <v>29575476</v>
       </c>
       <c r="M8" t="n">
-        <v>964425</v>
+        <v>2413950</v>
       </c>
       <c r="N8" t="n">
-        <v>60180</v>
+        <v>91800</v>
       </c>
       <c r="O8" t="n">
-        <v>1755675</v>
+        <v>1808460</v>
       </c>
       <c r="P8" t="n">
-        <v>148941</v>
+        <v>98553</v>
       </c>
       <c r="Q8" t="n">
-        <v>13579224.91</v>
+        <v>133129656</v>
       </c>
     </row>
     <row r="9">
@@ -26665,7 +26665,7 @@
         <v>4429809</v>
       </c>
       <c r="H9" t="n">
-        <v>29412000</v>
+        <v>34713000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -26677,22 +26677,22 @@
         <v>2534380.42</v>
       </c>
       <c r="L9" t="n">
-        <v>34834536</v>
+        <v>35941158</v>
       </c>
       <c r="M9" t="n">
-        <v>926100</v>
+        <v>2550450</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1806420</v>
+        <v>2028015</v>
       </c>
       <c r="P9" t="n">
-        <v>297375</v>
+        <v>204750</v>
       </c>
       <c r="Q9" t="n">
-        <v>16454365.11</v>
+        <v>161317305</v>
       </c>
     </row>
     <row r="10">
@@ -26718,7 +26718,7 @@
         <v>5224500</v>
       </c>
       <c r="H10" t="n">
-        <v>2736000</v>
+        <v>3591000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -26730,22 +26730,22 @@
         <v>2196673.44</v>
       </c>
       <c r="L10" t="n">
-        <v>33353640</v>
+        <v>35881596</v>
       </c>
       <c r="M10" t="n">
-        <v>1401225</v>
+        <v>2641800</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2481150</v>
+        <v>2934540</v>
       </c>
       <c r="P10" t="n">
-        <v>676260</v>
+        <v>348075</v>
       </c>
       <c r="Q10" t="n">
-        <v>17934653.88</v>
+        <v>175829940</v>
       </c>
     </row>
     <row r="11">
@@ -26771,7 +26771,7 @@
         <v>3056940</v>
       </c>
       <c r="H11" t="n">
-        <v>2052000</v>
+        <v>2565000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -26783,22 +26783,22 @@
         <v>1308826.98</v>
       </c>
       <c r="L11" t="n">
-        <v>21794400</v>
+        <v>25450200</v>
       </c>
       <c r="M11" t="n">
-        <v>1115100</v>
+        <v>1975050</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1616955</v>
+        <v>2804745</v>
       </c>
       <c r="P11" t="n">
-        <v>923130</v>
+        <v>514215</v>
       </c>
       <c r="Q11" t="n">
-        <v>14998724.64</v>
+        <v>147046320</v>
       </c>
     </row>
     <row r="12">
@@ -26824,7 +26824,7 @@
         <v>1504980</v>
       </c>
       <c r="H12" t="n">
-        <v>171000</v>
+        <v>513000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -26836,22 +26836,22 @@
         <v>405102.71</v>
       </c>
       <c r="L12" t="n">
-        <v>9801000</v>
+        <v>12366000</v>
       </c>
       <c r="M12" t="n">
-        <v>708225</v>
+        <v>1635900</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>765000</v>
+        <v>2106300</v>
       </c>
       <c r="P12" t="n">
-        <v>930150</v>
+        <v>1002300</v>
       </c>
       <c r="Q12" t="n">
-        <v>9271946.880000001</v>
+        <v>90901440</v>
       </c>
     </row>
     <row r="13">
@@ -26889,22 +26889,22 @@
         <v>46103.92</v>
       </c>
       <c r="L13" t="n">
-        <v>4908600</v>
+        <v>6490800</v>
       </c>
       <c r="M13" t="n">
-        <v>882000</v>
+        <v>1606500</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>428400</v>
+        <v>632400</v>
       </c>
       <c r="P13" t="n">
-        <v>809250</v>
+        <v>820950</v>
       </c>
       <c r="Q13" t="n">
-        <v>5184405</v>
+        <v>50827500</v>
       </c>
     </row>
     <row r="14">
@@ -26942,22 +26942,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1452600</v>
+        <v>2419200</v>
       </c>
       <c r="M14" t="n">
-        <v>304500</v>
+        <v>1617000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>566100</v>
+        <v>515100</v>
       </c>
       <c r="P14" t="n">
-        <v>830700</v>
+        <v>746850</v>
       </c>
       <c r="Q14" t="n">
-        <v>2061919.8</v>
+        <v>20214900</v>
       </c>
     </row>
     <row r="15">
@@ -26995,22 +26995,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>545400</v>
+        <v>1533600</v>
       </c>
       <c r="M15" t="n">
-        <v>178500</v>
+        <v>735000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>183600</v>
+        <v>326400</v>
       </c>
       <c r="P15" t="n">
-        <v>1095900</v>
+        <v>1101750</v>
       </c>
       <c r="Q15" t="n">
-        <v>628572.96</v>
+        <v>6162480</v>
       </c>
     </row>
     <row r="16">
@@ -27048,22 +27048,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>172800</v>
+        <v>1161000</v>
       </c>
       <c r="M16" t="n">
-        <v>10500</v>
+        <v>262500</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>5100</v>
+        <v>30600</v>
       </c>
       <c r="P16" t="n">
-        <v>1788150</v>
+        <v>2375100</v>
       </c>
       <c r="Q16" t="n">
-        <v>296385.48</v>
+        <v>2905740</v>
       </c>
     </row>
     <row r="17">
@@ -27101,22 +27101,22 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>37800</v>
+        <v>442800</v>
       </c>
       <c r="M17" t="n">
-        <v>31500</v>
+        <v>294000</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>10200</v>
+        <v>20400</v>
       </c>
       <c r="P17" t="n">
-        <v>696150</v>
+        <v>624000</v>
       </c>
       <c r="Q17" t="n">
-        <v>116934.84</v>
+        <v>1146420</v>
       </c>
     </row>
     <row r="18">
@@ -27154,10 +27154,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>37800</v>
+        <v>253800</v>
       </c>
       <c r="M18" t="n">
-        <v>199500</v>
+        <v>252000</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -27166,10 +27166,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1117350</v>
+        <v>1384500</v>
       </c>
       <c r="Q18" t="n">
-        <v>77497.56</v>
+        <v>759780</v>
       </c>
     </row>
     <row r="19">
@@ -27207,22 +27207,22 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>21600</v>
+        <v>253800</v>
       </c>
       <c r="M19" t="n">
-        <v>42000</v>
+        <v>10500</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>10200</v>
+        <v>25500</v>
       </c>
       <c r="P19" t="n">
-        <v>1212900</v>
+        <v>1975350</v>
       </c>
       <c r="Q19" t="n">
-        <v>65104.56</v>
+        <v>638280</v>
       </c>
     </row>
     <row r="20">
@@ -27263,7 +27263,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>10500</v>
+        <v>42000</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -27272,10 +27272,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>179400</v>
+        <v>483600</v>
       </c>
       <c r="Q20" t="n">
-        <v>14761.44</v>
+        <v>144720</v>
       </c>
     </row>
     <row r="21">
@@ -27316,7 +27316,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -27325,10 +27325,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>7800</v>
       </c>
       <c r="Q21" t="n">
-        <v>4791.96</v>
+        <v>46980</v>
       </c>
     </row>
     <row r="22">
@@ -27381,7 +27381,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>165.24</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="23">
@@ -27422,7 +27422,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>73500</v>
+        <v>115500</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -27434,7 +27434,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>4020.84</v>
+        <v>39420</v>
       </c>
     </row>
     <row r="24">
@@ -27692,7 +27692,7 @@
         <v>133680</v>
       </c>
       <c r="H4" t="n">
-        <v>17490</v>
+        <v>18000</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -27704,7 +27704,7 @@
         <v>96</v>
       </c>
       <c r="L4" t="n">
-        <v>407070</v>
+        <v>434610</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -27713,13 +27713,13 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>61110</v>
+        <v>57000</v>
       </c>
       <c r="P4" t="n">
-        <v>630</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>43965.96</v>
+        <v>612184.3199999999</v>
       </c>
     </row>
     <row r="5">
@@ -27745,7 +27745,7 @@
         <v>110730</v>
       </c>
       <c r="H5" t="n">
-        <v>22620</v>
+        <v>23790</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -27757,7 +27757,7 @@
         <v>61</v>
       </c>
       <c r="L5" t="n">
-        <v>261780</v>
+        <v>284100</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -27766,13 +27766,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>54450</v>
+        <v>58620</v>
       </c>
       <c r="P5" t="n">
-        <v>540</v>
+        <v>30</v>
       </c>
       <c r="Q5" t="n">
-        <v>27949.05</v>
+        <v>389164.05</v>
       </c>
     </row>
     <row r="6">
@@ -27798,7 +27798,7 @@
         <v>56490</v>
       </c>
       <c r="H6" t="n">
-        <v>18180</v>
+        <v>17520</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -27810,7 +27810,7 @@
         <v>27</v>
       </c>
       <c r="L6" t="n">
-        <v>135120</v>
+        <v>142170</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -27819,13 +27819,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>34920</v>
+        <v>35760</v>
       </c>
       <c r="P6" t="n">
-        <v>1710</v>
+        <v>30</v>
       </c>
       <c r="Q6" t="n">
-        <v>13927.42</v>
+        <v>193926.15</v>
       </c>
     </row>
     <row r="7">
@@ -27851,7 +27851,7 @@
         <v>31500</v>
       </c>
       <c r="H7" t="n">
-        <v>13470</v>
+        <v>14250</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -27863,7 +27863,7 @@
         <v>12</v>
       </c>
       <c r="L7" t="n">
-        <v>79380</v>
+        <v>82920</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -27872,13 +27872,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>25380</v>
+        <v>28170</v>
       </c>
       <c r="P7" t="n">
-        <v>2610</v>
+        <v>60</v>
       </c>
       <c r="Q7" t="n">
-        <v>6887.17</v>
+        <v>95897.34</v>
       </c>
     </row>
     <row r="8">
@@ -27904,7 +27904,7 @@
         <v>10860</v>
       </c>
       <c r="H8" t="n">
-        <v>1080</v>
+        <v>1830</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -27916,7 +27916,7 @@
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>21930</v>
+        <v>25500</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -27925,13 +27925,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>10020</v>
+        <v>11370</v>
       </c>
       <c r="P8" t="n">
-        <v>4290</v>
+        <v>600</v>
       </c>
       <c r="Q8" t="n">
-        <v>1589.72</v>
+        <v>22135.41</v>
       </c>
     </row>
     <row r="9">
@@ -27957,7 +27957,7 @@
         <v>360</v>
       </c>
       <c r="H9" t="n">
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -27969,7 +27969,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>4050</v>
+        <v>5550</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -27978,13 +27978,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>4470</v>
+        <v>10260</v>
       </c>
       <c r="P9" t="n">
-        <v>4380</v>
+        <v>1800</v>
       </c>
       <c r="Q9" t="n">
-        <v>101.46</v>
+        <v>1412.73</v>
       </c>
     </row>
     <row r="10">
@@ -28022,7 +28022,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>690</v>
+        <v>2070</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -28031,13 +28031,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1320</v>
+        <v>5460</v>
       </c>
       <c r="P10" t="n">
-        <v>5880</v>
+        <v>6540</v>
       </c>
       <c r="Q10" t="n">
-        <v>26.88</v>
+        <v>374.22</v>
       </c>
     </row>
     <row r="11">
@@ -28063,7 +28063,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -28075,7 +28075,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>420</v>
+        <v>2430</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -28084,13 +28084,13 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>90</v>
+        <v>1410</v>
       </c>
       <c r="P11" t="n">
-        <v>4200</v>
+        <v>8160</v>
       </c>
       <c r="Q11" t="n">
-        <v>11.16</v>
+        <v>155.43</v>
       </c>
     </row>
     <row r="12">
@@ -28116,7 +28116,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>30</v>
+        <v>240</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -28128,7 +28128,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>30</v>
+        <v>1140</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -28140,10 +28140,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2370</v>
+        <v>6240</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.28</v>
+        <v>31.68</v>
       </c>
     </row>
     <row r="13">
@@ -28169,7 +28169,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -28181,7 +28181,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>840</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -28193,10 +28193,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1050</v>
+        <v>3870</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.36</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="14">
@@ -28234,7 +28234,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -28246,10 +28246,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>150</v>
+        <v>840</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="15">
@@ -29037,7 +29037,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>8143.2</v>
+        <v>8564.4</v>
       </c>
       <c r="I5" t="n">
         <v>0.33</v>
@@ -29049,7 +29049,7 @@
         <v>20.19</v>
       </c>
       <c r="L5" t="n">
-        <v>54973.8</v>
+        <v>59661</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -29058,13 +29058,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2722.5</v>
+        <v>2931</v>
       </c>
       <c r="P5" t="n">
-        <v>10.8</v>
+        <v>0.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>1397.45</v>
+        <v>19458.2</v>
       </c>
     </row>
     <row r="6">
@@ -29090,7 +29090,7 @@
         <v>2824.5</v>
       </c>
       <c r="H6" t="n">
-        <v>10362.6</v>
+        <v>9986.4</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -29102,7 +29102,7 @@
         <v>13.69</v>
       </c>
       <c r="L6" t="n">
-        <v>49994.4</v>
+        <v>52602.9</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -29111,13 +29111,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>8730</v>
+        <v>8940</v>
       </c>
       <c r="P6" t="n">
-        <v>256.5</v>
+        <v>4.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>10445.57</v>
+        <v>145444.61</v>
       </c>
     </row>
     <row r="7">
@@ -29143,7 +29143,7 @@
         <v>4725</v>
       </c>
       <c r="H7" t="n">
-        <v>9833.1</v>
+        <v>10402.5</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -29155,7 +29155,7 @@
         <v>7.66</v>
       </c>
       <c r="L7" t="n">
-        <v>47628</v>
+        <v>49752</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -29164,13 +29164,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>8883</v>
+        <v>9859.5</v>
       </c>
       <c r="P7" t="n">
-        <v>652.5</v>
+        <v>15</v>
       </c>
       <c r="Q7" t="n">
-        <v>5509.74</v>
+        <v>76717.87</v>
       </c>
     </row>
     <row r="8">
@@ -29196,7 +29196,7 @@
         <v>7059</v>
       </c>
       <c r="H8" t="n">
-        <v>918</v>
+        <v>1555.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -29208,7 +29208,7 @@
         <v>0.74</v>
       </c>
       <c r="L8" t="n">
-        <v>15570.3</v>
+        <v>18105</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -29217,13 +29217,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>4509</v>
+        <v>5116.5</v>
       </c>
       <c r="P8" t="n">
-        <v>1630.2</v>
+        <v>228</v>
       </c>
       <c r="Q8" t="n">
-        <v>1510.24</v>
+        <v>21028.64</v>
       </c>
     </row>
     <row r="9">
@@ -29249,7 +29249,7 @@
         <v>306</v>
       </c>
       <c r="H9" t="n">
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -29261,7 +29261,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>3280.5</v>
+        <v>4495.5</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -29270,13 +29270,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2458.5</v>
+        <v>5643</v>
       </c>
       <c r="P9" t="n">
-        <v>2190</v>
+        <v>900</v>
       </c>
       <c r="Q9" t="n">
-        <v>98.42</v>
+        <v>1370.35</v>
       </c>
     </row>
     <row r="10">
@@ -29314,7 +29314,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>614.1</v>
+        <v>1842.3</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -29323,13 +29323,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>924</v>
+        <v>3822</v>
       </c>
       <c r="P10" t="n">
-        <v>4998</v>
+        <v>5559</v>
       </c>
       <c r="Q10" t="n">
-        <v>26.88</v>
+        <v>374.22</v>
       </c>
     </row>
     <row r="11">
@@ -29355,7 +29355,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -29367,7 +29367,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>420</v>
+        <v>2430</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -29376,13 +29376,13 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>76.5</v>
+        <v>1198.5</v>
       </c>
       <c r="P11" t="n">
-        <v>3780</v>
+        <v>7344</v>
       </c>
       <c r="Q11" t="n">
-        <v>11.16</v>
+        <v>155.43</v>
       </c>
     </row>
     <row r="12">
@@ -29408,7 +29408,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>30</v>
+        <v>240</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -29420,7 +29420,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>30</v>
+        <v>1140</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -29432,10 +29432,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2370</v>
+        <v>6240</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.28</v>
+        <v>31.68</v>
       </c>
     </row>
     <row r="13">
@@ -29461,7 +29461,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -29473,7 +29473,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>840</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -29485,10 +29485,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1050</v>
+        <v>3870</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.36</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="14">
@@ -29526,7 +29526,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -29538,10 +29538,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>150</v>
+        <v>840</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="15">
@@ -30329,7 +30329,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>46416240</v>
+        <v>48817080</v>
       </c>
       <c r="I5" t="n">
         <v>64288.14</v>
@@ -30341,7 +30341,7 @@
         <v>980394.2</v>
       </c>
       <c r="L5" t="n">
-        <v>9895284</v>
+        <v>10738980</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -30350,13 +30350,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>462825</v>
+        <v>498270</v>
       </c>
       <c r="P5" t="n">
-        <v>702</v>
+        <v>39</v>
       </c>
       <c r="Q5" t="n">
-        <v>838471.64</v>
+        <v>11674921.5</v>
       </c>
     </row>
     <row r="6">
@@ -30382,7 +30382,7 @@
         <v>152523</v>
       </c>
       <c r="H6" t="n">
-        <v>59066820</v>
+        <v>56922480</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -30394,7 +30394,7 @@
         <v>664683.08</v>
       </c>
       <c r="L6" t="n">
-        <v>8998992</v>
+        <v>9468522</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -30403,13 +30403,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1484100</v>
+        <v>1519800</v>
       </c>
       <c r="P6" t="n">
-        <v>16672.5</v>
+        <v>292.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>6267340.58</v>
+        <v>87266767.5</v>
       </c>
     </row>
     <row r="7">
@@ -30435,7 +30435,7 @@
         <v>255150</v>
       </c>
       <c r="H7" t="n">
-        <v>56048670</v>
+        <v>59294250</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -30447,7 +30447,7 @@
         <v>371744.74</v>
       </c>
       <c r="L7" t="n">
-        <v>8573040</v>
+        <v>8955360</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -30456,13 +30456,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1510110</v>
+        <v>1676115</v>
       </c>
       <c r="P7" t="n">
-        <v>42412.5</v>
+        <v>975</v>
       </c>
       <c r="Q7" t="n">
-        <v>3305842.85</v>
+        <v>46030723.2</v>
       </c>
     </row>
     <row r="8">
@@ -30488,7 +30488,7 @@
         <v>381186</v>
       </c>
       <c r="H8" t="n">
-        <v>5232600</v>
+        <v>8866350</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -30500,7 +30500,7 @@
         <v>35737.22</v>
       </c>
       <c r="L8" t="n">
-        <v>2802654</v>
+        <v>3258900</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -30509,13 +30509,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>766530</v>
+        <v>869805</v>
       </c>
       <c r="P8" t="n">
-        <v>105963</v>
+        <v>14820</v>
       </c>
       <c r="Q8" t="n">
-        <v>906143.1899999999</v>
+        <v>12617183.7</v>
       </c>
     </row>
     <row r="9">
@@ -30541,7 +30541,7 @@
         <v>16524</v>
       </c>
       <c r="H9" t="n">
-        <v>1881000</v>
+        <v>2052000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -30553,7 +30553,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>590490</v>
+        <v>809190</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -30562,13 +30562,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>417945</v>
+        <v>959310</v>
       </c>
       <c r="P9" t="n">
-        <v>142350</v>
+        <v>58500</v>
       </c>
       <c r="Q9" t="n">
-        <v>59049.55</v>
+        <v>822208.86</v>
       </c>
     </row>
     <row r="10">
@@ -30606,7 +30606,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>110538</v>
+        <v>331614</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -30615,13 +30615,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>157080</v>
+        <v>649740</v>
       </c>
       <c r="P10" t="n">
-        <v>324870</v>
+        <v>361335</v>
       </c>
       <c r="Q10" t="n">
-        <v>16125.48</v>
+        <v>224532</v>
       </c>
     </row>
     <row r="11">
@@ -30647,7 +30647,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>171000</v>
+        <v>855000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -30659,7 +30659,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>75600</v>
+        <v>437400</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -30668,13 +30668,13 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>13005</v>
+        <v>203745</v>
       </c>
       <c r="P11" t="n">
-        <v>245700</v>
+        <v>477360</v>
       </c>
       <c r="Q11" t="n">
-        <v>6697.62</v>
+        <v>93258</v>
       </c>
     </row>
     <row r="12">
@@ -30700,7 +30700,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>171000</v>
+        <v>1368000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -30712,7 +30712,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>5400</v>
+        <v>205200</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -30724,10 +30724,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>154050</v>
+        <v>405600</v>
       </c>
       <c r="Q12" t="n">
-        <v>1365.12</v>
+        <v>19008</v>
       </c>
     </row>
     <row r="13">
@@ -30753,7 +30753,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>342000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -30765,7 +30765,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>151200</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -30777,10 +30777,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>68250</v>
+        <v>251550</v>
       </c>
       <c r="Q13" t="n">
-        <v>213.3</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="14">
@@ -30818,7 +30818,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>37800</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -30830,10 +30830,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>9750</v>
+        <v>54600</v>
       </c>
       <c r="Q14" t="n">
-        <v>42.66</v>
+        <v>594</v>
       </c>
     </row>
     <row r="15">
